--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Action</t>
   </si>
@@ -37,12 +37,6 @@
     <t>URL Path</t>
   </si>
   <si>
-    <t>CheckDocument.index</t>
-  </si>
-  <si>
-    <t>MyDocument.index</t>
-  </si>
-  <si>
     <t>ID_MENU</t>
   </si>
   <si>
@@ -52,69 +46,9 @@
     <t>logout</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>CountryAdministrativeAreaLevel1</t>
-  </si>
-  <si>
-    <t>CountryAdministrativeAreaLevel2</t>
-  </si>
-  <si>
-    <t>CountryAdministrativeAreaLevel3</t>
-  </si>
-  <si>
-    <t>CountryAdministrativeAreaLevel4</t>
-  </si>
-  <si>
-    <t>BusinessDocumentType</t>
-  </si>
-  <si>
-    <t>BusinessDocument</t>
-  </si>
-  <si>
-    <t>BusinessDocumentVersion</t>
-  </si>
-  <si>
-    <t>MenuManagement</t>
-  </si>
-  <si>
-    <t>WorkflowRoute?var=1</t>
-  </si>
-  <si>
-    <t>ModifyBudget</t>
-  </si>
-  <si>
     <t>ReportModifyBudgetSummary</t>
   </si>
   <si>
-    <t>ReportCFS</t>
-  </si>
-  <si>
-    <t>Periode</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Religion</t>
-  </si>
-  <si>
-    <t>BloodAglutinogenType</t>
-  </si>
-  <si>
-    <t>Timesheet</t>
-  </si>
-  <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
-    <t>ProductType</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
     <t>ReportDOSummary</t>
   </si>
   <si>
@@ -221,6 +155,51 @@
   </si>
   <si>
     <t>ReportPOtoAP</t>
+  </si>
+  <si>
+    <t>CheckDocument?var=1</t>
+  </si>
+  <si>
+    <t>dashboard?var=1</t>
+  </si>
+  <si>
+    <t>MyDocument?var=1</t>
+  </si>
+  <si>
+    <t>ModifyBudget?var=1</t>
+  </si>
+  <si>
+    <t>ReportGeneralJournalSummary</t>
+  </si>
+  <si>
+    <t>ReportInvoiceSummary</t>
+  </si>
+  <si>
+    <t>ReportInvoiceToCN</t>
+  </si>
+  <si>
+    <t>ReportTaxReconSummary</t>
+  </si>
+  <si>
+    <t>ReportTimesheetSummary</t>
+  </si>
+  <si>
+    <t>ReportMaterialReceiveSummary</t>
+  </si>
+  <si>
+    <t>ReportDoToMaterialReceive</t>
+  </si>
+  <si>
+    <t>ReportMatReceivetoMatReturn</t>
+  </si>
+  <si>
+    <t>ReportAdvanceToASF</t>
+  </si>
+  <si>
+    <t>ReportBusinessTripToBSF</t>
+  </si>
+  <si>
+    <t>Report Modify Budget Summary</t>
   </si>
 </sst>
 </file>
@@ -385,14 +364,18 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -400,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -416,7 +399,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -424,9 +406,14 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -493,10 +480,10 @@
             <v>97000000000004</v>
           </cell>
           <cell r="F5" t="str">
-            <v>Dashboard.DocumentTracking</v>
+            <v>Dashboard.Home</v>
           </cell>
           <cell r="G5" t="str">
-            <v>Document Tracking</v>
+            <v>Dashboard</v>
           </cell>
         </row>
         <row r="6">
@@ -504,10 +491,10 @@
             <v>97000000000005</v>
           </cell>
           <cell r="F6" t="str">
-            <v>Dashboard.MyDocumentTracking</v>
+            <v>Dashboard.DocumentTracking</v>
           </cell>
           <cell r="G6" t="str">
-            <v>My Document Tracking</v>
+            <v>Document Tracking</v>
           </cell>
         </row>
         <row r="7">
@@ -515,10 +502,10 @@
             <v>97000000000006</v>
           </cell>
           <cell r="F7" t="str">
-            <v>Dashboard.MyDocumentDisposition</v>
+            <v>Dashboard.MyDocumentTracking</v>
           </cell>
           <cell r="G7" t="str">
-            <v>My Document Disposition</v>
+            <v>My Document Tracking</v>
           </cell>
         </row>
         <row r="8">
@@ -526,10 +513,10 @@
             <v>97000000000007</v>
           </cell>
           <cell r="F8" t="str">
-            <v>Module.General.MasterData.Country.Transaction</v>
+            <v>Dashboard.MyDocumentDisposition</v>
           </cell>
           <cell r="G8" t="str">
-            <v>Country</v>
+            <v>My Document Disposition</v>
           </cell>
         </row>
         <row r="9">
@@ -537,10 +524,10 @@
             <v>97000000000008</v>
           </cell>
           <cell r="F9" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
+            <v>Module.General.MasterData.Country.Transaction</v>
           </cell>
           <cell r="G9" t="str">
-            <v>Province / State</v>
+            <v>Country</v>
           </cell>
         </row>
         <row r="10">
@@ -548,10 +535,10 @@
             <v>97000000000009</v>
           </cell>
           <cell r="F10" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
           </cell>
           <cell r="G10" t="str">
-            <v>Municipality / Regency</v>
+            <v>Province / State</v>
           </cell>
         </row>
         <row r="11">
@@ -559,10 +546,10 @@
             <v>97000000000010</v>
           </cell>
           <cell r="F11" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
           </cell>
           <cell r="G11" t="str">
-            <v>District</v>
+            <v>Municipality / Regency</v>
           </cell>
         </row>
         <row r="12">
@@ -570,10 +557,10 @@
             <v>97000000000011</v>
           </cell>
           <cell r="F12" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
           </cell>
           <cell r="G12" t="str">
-            <v>Urban Village / Village</v>
+            <v>District</v>
           </cell>
         </row>
         <row r="13">
@@ -581,10 +568,10 @@
             <v>97000000000012</v>
           </cell>
           <cell r="F13" t="str">
-            <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
           </cell>
           <cell r="G13" t="str">
-            <v>Business Document Type</v>
+            <v>Urban Village / Village</v>
           </cell>
         </row>
         <row r="14">
@@ -592,10 +579,10 @@
             <v>97000000000013</v>
           </cell>
           <cell r="F14" t="str">
-            <v>Module.General.MasterData.BusinessDocument.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
           </cell>
           <cell r="G14" t="str">
-            <v>Business Document</v>
+            <v>Business Document Type</v>
           </cell>
         </row>
         <row r="15">
@@ -603,10 +590,10 @@
             <v>97000000000014</v>
           </cell>
           <cell r="F15" t="str">
-            <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocument.Transaction</v>
           </cell>
           <cell r="G15" t="str">
-            <v>Business Document Version</v>
+            <v>Business Document</v>
           </cell>
         </row>
         <row r="16">
@@ -614,10 +601,10 @@
             <v>97000000000015</v>
           </cell>
           <cell r="F16" t="str">
-            <v>Module.General.MasterData.MenuManagement.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
           </cell>
           <cell r="G16" t="str">
-            <v>Menu Management</v>
+            <v>Business Document Version</v>
           </cell>
         </row>
         <row r="17">
@@ -625,10 +612,10 @@
             <v>97000000000016</v>
           </cell>
           <cell r="F17" t="str">
-            <v>Module.General.MasterData.WorkflowRoute.Transaction</v>
+            <v>Module.General.MasterData.MenuManagement.Transaction</v>
           </cell>
           <cell r="G17" t="str">
-            <v>Workflow Route</v>
+            <v>Menu Management</v>
           </cell>
         </row>
         <row r="18">
@@ -636,10 +623,10 @@
             <v>97000000000017</v>
           </cell>
           <cell r="F18" t="str">
-            <v>Module.Budgeting.Data.Budget.Transaction</v>
+            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
           </cell>
           <cell r="G18" t="str">
-            <v>Budget</v>
+            <v>Privilege Menu</v>
           </cell>
         </row>
         <row r="19">
@@ -647,10 +634,10 @@
             <v>97000000000018</v>
           </cell>
           <cell r="F19" t="str">
-            <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
+            <v>Module.General.MasterData.Workflow.Transaction</v>
           </cell>
           <cell r="G19" t="str">
-            <v>Report Modify Budget Summary</v>
+            <v>Workflow</v>
           </cell>
         </row>
         <row r="20">
@@ -658,10 +645,10 @@
             <v>97000000000019</v>
           </cell>
           <cell r="F20" t="str">
-            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
           </cell>
           <cell r="G20" t="str">
-            <v>Report Cost Financial Structure</v>
+            <v>Budget</v>
           </cell>
         </row>
         <row r="21">
@@ -669,10 +656,10 @@
             <v>97000000000020</v>
           </cell>
           <cell r="F21" t="str">
-            <v>Module.General.MasterData.Religion.Transaction</v>
+            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
           </cell>
           <cell r="G21" t="str">
-            <v>Religion</v>
+            <v>Sub Budget</v>
           </cell>
         </row>
         <row r="22">
@@ -680,10 +667,10 @@
             <v>97000000000021</v>
           </cell>
           <cell r="F22" t="str">
-            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+            <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
           </cell>
           <cell r="G22" t="str">
-            <v>Blood Aglutinogen Type</v>
+            <v>Modify Budget</v>
           </cell>
         </row>
         <row r="23">
@@ -691,10 +678,10 @@
             <v>97000000000022</v>
           </cell>
           <cell r="F23" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+            <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
           </cell>
           <cell r="G23" t="str">
-            <v>Person Work Time Sheet</v>
+            <v>Report Modify Budget Summary</v>
           </cell>
         </row>
         <row r="24">
@@ -702,10 +689,10 @@
             <v>97000000000023</v>
           </cell>
           <cell r="F24" t="str">
-            <v>Module.General.MasterData.Warehouse.Transaction</v>
+            <v>Module.Budgeting.Data.Work.Transaction</v>
           </cell>
           <cell r="G24" t="str">
-            <v>Warehouse</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="25">
@@ -713,10 +700,10 @@
             <v>97000000000024</v>
           </cell>
           <cell r="F25" t="str">
-            <v>Module.General.MasterData.ProductType.Transaction</v>
+            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
           </cell>
           <cell r="G25" t="str">
-            <v>Product Type</v>
+            <v>Report Cost Financial Structure</v>
           </cell>
         </row>
         <row r="26">
@@ -724,10 +711,10 @@
             <v>97000000000025</v>
           </cell>
           <cell r="F26" t="str">
-            <v>Module.General.MasterData.Product.Transaction</v>
+            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
           </cell>
           <cell r="G26" t="str">
-            <v>Product</v>
+            <v>Blood Aglutinogen Type</v>
           </cell>
         </row>
         <row r="27">
@@ -735,10 +722,10 @@
             <v>97000000000026</v>
           </cell>
           <cell r="F27" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+            <v>Module.General.MasterData.Person.Transaction</v>
           </cell>
           <cell r="G27" t="str">
-            <v>Report DO Summary</v>
+            <v>Person</v>
           </cell>
         </row>
         <row r="28">
@@ -746,10 +733,10 @@
             <v>97000000000027</v>
           </cell>
           <cell r="F28" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+            <v>Module.General.MasterData.Religion.Transaction</v>
           </cell>
           <cell r="G28" t="str">
-            <v>Delivery Order</v>
+            <v>Religion</v>
           </cell>
         </row>
         <row r="29">
@@ -757,10 +744,10 @@
             <v>97000000000028</v>
           </cell>
           <cell r="F29" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+            <v>Module.General.MasterData.UserRole.Transaction</v>
           </cell>
           <cell r="G29" t="str">
-            <v>Material Receive</v>
+            <v>Role</v>
           </cell>
         </row>
         <row r="30">
@@ -768,10 +755,10 @@
             <v>97000000000029</v>
           </cell>
           <cell r="F30" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
           </cell>
           <cell r="G30" t="str">
-            <v>Report Material Return Summary</v>
+            <v>Department</v>
           </cell>
         </row>
         <row r="31">
@@ -779,10 +766,10 @@
             <v>97000000000030</v>
           </cell>
           <cell r="F31" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
           </cell>
           <cell r="G31" t="str">
-            <v>Material Return</v>
+            <v>Person Work Time Sheet</v>
           </cell>
         </row>
         <row r="32">
@@ -790,10 +777,10 @@
             <v>97000000000031</v>
           </cell>
           <cell r="F32" t="str">
-            <v>Module.Finance.Data.Advance.Report.DataList</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
           </cell>
           <cell r="G32" t="str">
-            <v>Report Advance Summary</v>
+            <v>Person Work Time Sheet Summary</v>
           </cell>
         </row>
         <row r="33">
@@ -801,10 +788,10 @@
             <v>97000000000032</v>
           </cell>
           <cell r="F33" t="str">
-            <v>Module.Finance.Data.Advance.Transaction</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
           </cell>
           <cell r="G33" t="str">
-            <v>Advance Request</v>
+            <v>Sallary Allocation</v>
           </cell>
         </row>
         <row r="34">
@@ -812,10 +799,10 @@
             <v>97000000000033</v>
           </cell>
           <cell r="F34" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
           </cell>
           <cell r="G34" t="str">
-            <v>Report Advance Settlement Summary</v>
+            <v>Sallary Allocation Summary</v>
           </cell>
         </row>
         <row r="35">
@@ -823,10 +810,10 @@
             <v>97000000000034</v>
           </cell>
           <cell r="F35" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+            <v>Module.General.MasterData.Warehouse.Transaction</v>
           </cell>
           <cell r="G35" t="str">
-            <v>AdvanceSettlement</v>
+            <v>Warehouse</v>
           </cell>
         </row>
         <row r="36">
@@ -834,10 +821,10 @@
             <v>97000000000035</v>
           </cell>
           <cell r="F36" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.General.MasterData.ProductType.Transaction</v>
           </cell>
           <cell r="G36" t="str">
-            <v>Report BusinessTrip Settlement Summary</v>
+            <v>Product Type</v>
           </cell>
         </row>
         <row r="37">
@@ -845,10 +832,10 @@
             <v>97000000000036</v>
           </cell>
           <cell r="F37" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+            <v>Module.General.MasterData.Product.Transaction</v>
           </cell>
           <cell r="G37" t="str">
-            <v>BusinessTrip Settlement</v>
+            <v>Product</v>
           </cell>
         </row>
         <row r="38">
@@ -856,10 +843,10 @@
             <v>97000000000037</v>
           </cell>
           <cell r="F38" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
           </cell>
           <cell r="G38" t="str">
-            <v>Report BusinessTrip Request Summary</v>
+            <v>Delivery Order</v>
           </cell>
         </row>
         <row r="39">
@@ -867,10 +854,10 @@
             <v>97000000000038</v>
           </cell>
           <cell r="F39" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
           </cell>
           <cell r="G39" t="str">
-            <v>BusinessTrip Request</v>
+            <v>Report DO Summary</v>
           </cell>
         </row>
         <row r="40">
@@ -878,10 +865,10 @@
             <v>97000000000039</v>
           </cell>
           <cell r="F40" t="str">
-            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G40" t="str">
-            <v>Supplier</v>
+            <v>Report DO to Material Receive</v>
           </cell>
         </row>
         <row r="41">
@@ -889,10 +876,10 @@
             <v>97000000000040</v>
           </cell>
           <cell r="F41" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
           </cell>
           <cell r="G41" t="str">
-            <v>Report Purchase Requisition Summary</v>
+            <v>Material Receive</v>
           </cell>
         </row>
         <row r="42">
@@ -900,10 +887,10 @@
             <v>97000000000041</v>
           </cell>
           <cell r="F42" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G42" t="str">
-            <v>Report Purchase Requisition To Purchase Order</v>
+            <v>Report Material Receive Summary</v>
           </cell>
         </row>
         <row r="43">
@@ -911,10 +898,10 @@
             <v>97000000000042</v>
           </cell>
           <cell r="F43" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G43" t="str">
-            <v>Purchase Requisition</v>
+            <v>Report Material Receive to Material Return</v>
           </cell>
         </row>
         <row r="44">
@@ -922,10 +909,10 @@
             <v>97000000000043</v>
           </cell>
           <cell r="F44" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
           </cell>
           <cell r="G44" t="str">
-            <v>Report Purchase Order Summary</v>
+            <v>Material Return</v>
           </cell>
         </row>
         <row r="45">
@@ -933,10 +920,10 @@
             <v>97000000000044</v>
           </cell>
           <cell r="F45" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G45" t="str">
-            <v>Purchase Order</v>
+            <v>Report Material Return Summary</v>
           </cell>
         </row>
         <row r="46">
@@ -944,10 +931,10 @@
             <v>97000000000045</v>
           </cell>
           <cell r="F46" t="str">
-            <v>Module.General.MasterData.Period.Transaction</v>
+            <v>Module.Finance.Data.Advance.Transaction</v>
           </cell>
           <cell r="G46" t="str">
-            <v>Period</v>
+            <v>Advance Request</v>
           </cell>
         </row>
         <row r="47">
@@ -955,10 +942,10 @@
             <v>97000000000046</v>
           </cell>
           <cell r="F47" t="str">
-            <v>Module.General.MasterData.Currency.Transaction</v>
+            <v>Module.Finance.Data.Advance.Report.DataList</v>
           </cell>
           <cell r="G47" t="str">
-            <v>Currency</v>
+            <v>Report Advance Summary</v>
           </cell>
         </row>
         <row r="48">
@@ -966,10 +953,10 @@
             <v>97000000000047</v>
           </cell>
           <cell r="F48" t="str">
-            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G48" t="str">
-            <v>Reimbursement</v>
+            <v>Report Advance to Advance Settlement</v>
           </cell>
         </row>
         <row r="49">
@@ -977,10 +964,10 @@
             <v>97000000000048</v>
           </cell>
           <cell r="F49" t="str">
-            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
           </cell>
           <cell r="G49" t="str">
-            <v>Reimbursement Summary</v>
+            <v>AdvanceSettlement</v>
           </cell>
         </row>
         <row r="50">
@@ -988,10 +975,10 @@
             <v>97000000000049</v>
           </cell>
           <cell r="F50" t="str">
-            <v>Module.Finance.Data.DebitNote.Transaction</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G50" t="str">
-            <v>Debit Note</v>
+            <v>Report Advance Settlement Summary</v>
           </cell>
         </row>
         <row r="51">
@@ -999,10 +986,10 @@
             <v>97000000000050</v>
           </cell>
           <cell r="F51" t="str">
-            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
           </cell>
           <cell r="G51" t="str">
-            <v>Debit Note Summary</v>
+            <v>BusinessTrip Request</v>
           </cell>
         </row>
         <row r="52">
@@ -1010,10 +997,10 @@
             <v>97000000000051</v>
           </cell>
           <cell r="F52" t="str">
-            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
           </cell>
           <cell r="G52" t="str">
-            <v>Reimbursement to Debit Note</v>
+            <v>Report BusinessTrip Request Summary</v>
           </cell>
         </row>
         <row r="53">
@@ -1021,10 +1008,10 @@
             <v>97000000000052</v>
           </cell>
           <cell r="F53" t="str">
-            <v>Module.Finance.Data.CreditNote.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G53" t="str">
-            <v>Credit Note</v>
+            <v>Report BusinessTrip to BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="54">
@@ -1032,10 +1019,10 @@
             <v>97000000000053</v>
           </cell>
           <cell r="F54" t="str">
-            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
           </cell>
           <cell r="G54" t="str">
-            <v>Credit Note Summary</v>
+            <v>BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="55">
@@ -1043,10 +1030,10 @@
             <v>97000000000054</v>
           </cell>
           <cell r="F55" t="str">
-            <v>Module.Finance.Data.Loan.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G55" t="str">
-            <v>Loan</v>
+            <v>Report BusinessTrip Settlement Summary</v>
           </cell>
         </row>
         <row r="56">
@@ -1054,10 +1041,10 @@
             <v>97000000000055</v>
           </cell>
           <cell r="F56" t="str">
-            <v>Module.Finance.Data.Loan.Report.DataList</v>
+            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
           </cell>
           <cell r="G56" t="str">
-            <v>Loan Summary</v>
+            <v>Supplier</v>
           </cell>
         </row>
         <row r="57">
@@ -1065,10 +1052,10 @@
             <v>97000000000056</v>
           </cell>
           <cell r="F57" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
           </cell>
           <cell r="G57" t="str">
-            <v>Loan Settlement</v>
+            <v>Purchase Requisition</v>
           </cell>
         </row>
         <row r="58">
@@ -1076,10 +1063,10 @@
             <v>97000000000057</v>
           </cell>
           <cell r="F58" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
           </cell>
           <cell r="G58" t="str">
-            <v>Loan Settlement Summary</v>
+            <v>Report Purchase Requisition Summary</v>
           </cell>
         </row>
         <row r="59">
@@ -1087,10 +1074,10 @@
             <v>97000000000058</v>
           </cell>
           <cell r="F59" t="str">
-            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G59" t="str">
-            <v>Loan to Loan Settlement</v>
+            <v>Report Purchase Requisition To Purchase Order</v>
           </cell>
         </row>
         <row r="60">
@@ -1098,10 +1085,10 @@
             <v>97000000000059</v>
           </cell>
           <cell r="F60" t="str">
-            <v>Module.Finance.Data.CashBank.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
           </cell>
           <cell r="G60" t="str">
-            <v>Cash &amp; Bank</v>
+            <v>Purchase Order</v>
           </cell>
         </row>
         <row r="61">
@@ -1109,10 +1096,10 @@
             <v>97000000000060</v>
           </cell>
           <cell r="F61" t="str">
-            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G61" t="str">
-            <v>Cash &amp; Bank Report</v>
+            <v>Report Purchase Order Summary</v>
           </cell>
         </row>
         <row r="62">
@@ -1120,10 +1107,10 @@
             <v>97000000000061</v>
           </cell>
           <cell r="F62" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
           </cell>
           <cell r="G62" t="str">
-            <v>Account Payable</v>
+            <v>Purchase Order to Account Payable</v>
           </cell>
         </row>
         <row r="63">
@@ -1131,10 +1118,10 @@
             <v>97000000000062</v>
           </cell>
           <cell r="F63" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+            <v>Module.General.MasterData.Bank.Transaction</v>
           </cell>
           <cell r="G63" t="str">
-            <v>Account Payable Summary</v>
+            <v>Bank</v>
           </cell>
         </row>
         <row r="64">
@@ -1142,10 +1129,384 @@
             <v>97000000000063</v>
           </cell>
           <cell r="F64" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+            <v>Module.General.MasterData.BankAccount.Transaction</v>
           </cell>
           <cell r="G64" t="str">
-            <v>Purchase Order to Account Payable</v>
+            <v>Bank Account</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="E65">
+            <v>97000000000064</v>
+          </cell>
+          <cell r="F65" t="str">
+            <v>Module.General.MasterData.Currency.Transaction</v>
+          </cell>
+          <cell r="G65" t="str">
+            <v>Currency</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="E66">
+            <v>97000000000065</v>
+          </cell>
+          <cell r="F66" t="str">
+            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+          </cell>
+          <cell r="G66" t="str">
+            <v>Exchange Rate</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="E67">
+            <v>97000000000066</v>
+          </cell>
+          <cell r="F67" t="str">
+            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+          </cell>
+          <cell r="G67" t="str">
+            <v>Exchange Rate Summary</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="E68">
+            <v>97000000000067</v>
+          </cell>
+          <cell r="F68" t="str">
+            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+          </cell>
+          <cell r="G68" t="str">
+            <v>Payment Term</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="E69">
+            <v>97000000000068</v>
+          </cell>
+          <cell r="F69" t="str">
+            <v>Module.General.MasterData.Period.Transaction</v>
+          </cell>
+          <cell r="G69" t="str">
+            <v>Period</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="E70">
+            <v>97000000000069</v>
+          </cell>
+          <cell r="F70" t="str">
+            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+          </cell>
+          <cell r="G70" t="str">
+            <v>Asset Category</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="E71">
+            <v>97000000000070</v>
+          </cell>
+          <cell r="F71" t="str">
+            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+          </cell>
+          <cell r="G71" t="str">
+            <v>Chart of Account</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="E72">
+            <v>97000000000071</v>
+          </cell>
+          <cell r="F72" t="str">
+            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+          </cell>
+          <cell r="G72" t="str">
+            <v>Depreciation Method</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="E73">
+            <v>97000000000072</v>
+          </cell>
+          <cell r="F73" t="str">
+            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+          </cell>
+          <cell r="G73" t="str">
+            <v>Depreciation Rate Years</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="E74">
+            <v>97000000000073</v>
+          </cell>
+          <cell r="F74" t="str">
+            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+          </cell>
+          <cell r="G74" t="str">
+            <v>Value Added Tax</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="E75">
+            <v>97000000000074</v>
+          </cell>
+          <cell r="F75" t="str">
+            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+          </cell>
+          <cell r="G75" t="str">
+            <v>General Journal</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="E76">
+            <v>97000000000075</v>
+          </cell>
+          <cell r="F76" t="str">
+            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+          </cell>
+          <cell r="G76" t="str">
+            <v>General Journal Summary</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="E77">
+            <v>97000000000076</v>
+          </cell>
+          <cell r="F77" t="str">
+            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+          </cell>
+          <cell r="G77" t="str">
+            <v>Reimbursement</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="E78">
+            <v>97000000000077</v>
+          </cell>
+          <cell r="F78" t="str">
+            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+          </cell>
+          <cell r="G78" t="str">
+            <v>Reimbursement Summary</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="E79">
+            <v>97000000000078</v>
+          </cell>
+          <cell r="F79" t="str">
+            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G79" t="str">
+            <v>Reimbursement to Debit Note</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="E80">
+            <v>97000000000079</v>
+          </cell>
+          <cell r="F80" t="str">
+            <v>Module.Finance.Data.DebitNote.Transaction</v>
+          </cell>
+          <cell r="G80" t="str">
+            <v>Debit Note</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="E81">
+            <v>97000000000080</v>
+          </cell>
+          <cell r="F81" t="str">
+            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G81" t="str">
+            <v>Debit Note Summary</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="E82">
+            <v>97000000000081</v>
+          </cell>
+          <cell r="F82" t="str">
+            <v>Module.Finance.Data.CreditNote.Transaction</v>
+          </cell>
+          <cell r="G82" t="str">
+            <v>Credit Note</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="E83">
+            <v>97000000000082</v>
+          </cell>
+          <cell r="F83" t="str">
+            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G83" t="str">
+            <v>Credit Note Summary</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="E84">
+            <v>97000000000083</v>
+          </cell>
+          <cell r="F84" t="str">
+            <v>Module.Finance.Data.Loan.Transaction</v>
+          </cell>
+          <cell r="G84" t="str">
+            <v>Loan</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="E85">
+            <v>97000000000084</v>
+          </cell>
+          <cell r="F85" t="str">
+            <v>Module.Finance.Data.Loan.Report.DataList</v>
+          </cell>
+          <cell r="G85" t="str">
+            <v>Loan Summary</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="E86">
+            <v>97000000000085</v>
+          </cell>
+          <cell r="F86" t="str">
+            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G86" t="str">
+            <v>Loan to Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="E87">
+            <v>97000000000086</v>
+          </cell>
+          <cell r="F87" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+          </cell>
+          <cell r="G87" t="str">
+            <v>Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="E88">
+            <v>97000000000087</v>
+          </cell>
+          <cell r="F88" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G88" t="str">
+            <v>Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="E89">
+            <v>97000000000088</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>Module.Finance.Data.CashBank.Transaction</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>Cash &amp; Bank</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="E90">
+            <v>97000000000089</v>
+          </cell>
+          <cell r="F90" t="str">
+            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+          </cell>
+          <cell r="G90" t="str">
+            <v>Cash &amp; Bank Summary</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="E91">
+            <v>97000000000090</v>
+          </cell>
+          <cell r="F91" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+          </cell>
+          <cell r="G91" t="str">
+            <v>Account Payable</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="E92">
+            <v>97000000000091</v>
+          </cell>
+          <cell r="F92" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+          </cell>
+          <cell r="G92" t="str">
+            <v>Account Payable Summary</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="E93">
+            <v>97000000000092</v>
+          </cell>
+          <cell r="F93" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+          </cell>
+          <cell r="G93" t="str">
+            <v>Sales Invoice</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="E94">
+            <v>97000000000093</v>
+          </cell>
+          <cell r="F94" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+          </cell>
+          <cell r="G94" t="str">
+            <v>Sales Invoice Summary</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="E95">
+            <v>97000000000094</v>
+          </cell>
+          <cell r="F95" t="str">
+            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G95" t="str">
+            <v>Sales Invoice to Credit Note</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="E96">
+            <v>97000000000095</v>
+          </cell>
+          <cell r="F96" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+          </cell>
+          <cell r="G96" t="str">
+            <v>Tax Reconciliation</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="E97">
+            <v>97000000000096</v>
+          </cell>
+          <cell r="F97" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+          </cell>
+          <cell r="G97" t="str">
+            <v>Tax Reconciliation Summary</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="E98">
+            <v>97000000000097</v>
+          </cell>
+          <cell r="F98" t="str">
+            <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Customer</v>
           </cell>
         </row>
       </sheetData>
@@ -1441,19 +1802,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:O65"/>
+  <dimension ref="B1:O98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" style="16" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="40.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -1464,9 +1825,9 @@
       <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="21"/>
       <c r="F1" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>0</v>
@@ -1490,15 +1851,15 @@
         <v>97000000000001</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>System.Login</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
         <v>Login</v>
       </c>
-      <c r="F2" s="18">
-        <f t="shared" ref="F2:F64" si="0">IF(EXACT(B2, ""), F1, B2)</f>
+      <c r="F2" s="17">
+        <f t="shared" ref="F2:F65" si="0">IF(EXACT(B2, ""), F1, B2)</f>
         <v>97000000000001</v>
       </c>
       <c r="H2" s="4"/>
@@ -1507,2438 +1868,3332 @@
         <v>Execute</v>
       </c>
       <c r="J2" s="3" t="str">
-        <f>IF(EXACT(F2, ""), "", IF(EXACT(H2, ""), "Execute", SUBSTITUTE(H2, " ", "")))</f>
-        <v>Execute</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>9</v>
+        <f t="shared" ref="J2:J65" si="1">IF(EXACT(F2, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C2)), D2, IF(EXACT(H2, ""), "Execute", H2)), " ", ""), "&amp;", "")
+)</f>
+        <v>Execute</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="M2" s="6">
         <f>IF(ISNUMBER(M1), M1+1, 256000000000001)</f>
         <v>256000000000001</v>
       </c>
-      <c r="O2" s="16" t="str">
+      <c r="O2" s="15" t="str">
         <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F2, ""), "null", CONCATENATE($F2)), ", ", IF(EXACT($F2, ""),"null", CONCATENATE("'", $J2, "'")), ", ", IF(EXACT($F2, ""), "null", CONCATENATE("'", $I2, "'")), ", ", IF(EXACT($K2, ""), "null", CONCATENATE("'", $K2, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000001, 'Execute', 'Execute', 'login');</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
-        <f t="shared" ref="B3:B64" si="1">IF(ISNUMBER(B2), B2+1, 97000000000001)</f>
+        <f t="shared" ref="B3:B66" si="2">IF(ISNUMBER(B2), B2+1, 97000000000001)</f>
         <v>97000000000002</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>System.Logout</v>
       </c>
       <c r="D3" s="3" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
         <v>Logout</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <f t="shared" si="0"/>
         <v>97000000000002</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I64" si="2">IF(EXACT(F3, ""), "", IF(EXACT(H3, ""), "Execute", H3))</f>
+        <f t="shared" ref="I3:I65" si="3">IF(EXACT(F3, ""), "", IF(EXACT(H3, ""), "Execute", H3))</f>
         <v>Execute</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3:J64" si="3">IF(EXACT(F3, ""), "", IF(EXACT(H3, ""), "Execute", SUBSTITUTE(H3, " ", "")))</f>
-        <v>Execute</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="M3" s="6">
         <f>IF(ISNUMBER(M2), M2+1, 256000000000001)</f>
         <v>256000000000002</v>
       </c>
-      <c r="O3" s="16" t="str">
-        <f t="shared" ref="O3:O64" si="4">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F3, ""), "null", CONCATENATE($F3)), ", ", IF(EXACT($F3, ""),"null", CONCATENATE("'", $J3, "'")), ", ", IF(EXACT($F3, ""), "null", CONCATENATE("'", $I3, "'")), ", ", IF(EXACT($K3, ""), "null", CONCATENATE("'", $K3, "'")), ");")</f>
+      <c r="O3" s="15" t="str">
+        <f t="shared" ref="O3:O65" si="4">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F3, ""), "null", CONCATENATE($F3)), ", ", IF(EXACT($F3, ""),"null", CONCATENATE("'", $J3, "'")), ", ", IF(EXACT($F3, ""), "null", CONCATENATE("'", $I3, "'")), ", ", IF(EXACT($K3, ""), "null", CONCATENATE("'", $K3, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000002, 'Execute', 'Execute', 'logout');</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000003</v>
       </c>
       <c r="C4" s="10" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>System.Lock</v>
       </c>
       <c r="D4" s="11" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
         <v>Lock</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="20">
         <f t="shared" si="0"/>
         <v>97000000000003</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="14"/>
       <c r="I4" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J4" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K4" s="20"/>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K4" s="19"/>
       <c r="M4" s="6">
-        <f t="shared" ref="M4:M64" si="5">IF(ISNUMBER(M3), M3+1, 256000000000001)</f>
+        <f t="shared" ref="M4:M65" si="5">IF(ISNUMBER(M3), M3+1, 256000000000001)</f>
         <v>256000000000003</v>
       </c>
-      <c r="O4" s="16" t="str">
+      <c r="O4" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000003, 'Execute', 'Execute', null);</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000004</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Dashboard.DocumentTracking</v>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Dashboard.Home</v>
       </c>
       <c r="D5" s="3" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Document Tracking</v>
-      </c>
-      <c r="F5" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Dashboard</v>
+      </c>
+      <c r="F5" s="17">
+        <f>IF(EXACT(B5, ""), F3, B5)</f>
         <v>97000000000004</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I5" si="6">IF(EXACT(F5, ""), "", IF(EXACT(H5, ""), "Execute", H5))</f>
         <v>Execute</v>
       </c>
       <c r="J5" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" si="5"/>
         <v>256000000000004</v>
       </c>
-      <c r="O5" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000004, 'Execute', 'Execute', 'CheckDocument.index');</v>
+      <c r="O5" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000004, 'Execute', 'Execute', 'dashboard?var=1');</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000005</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Dashboard.MyDocumentTracking</v>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="D6" s="3" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>My Document Tracking</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Document Tracking</v>
+      </c>
+      <c r="F6" s="17">
+        <f>IF(EXACT(B6, ""), F4, B6)</f>
         <v>97000000000005</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J6" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="5"/>
         <v>256000000000005</v>
       </c>
-      <c r="O6" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000005, 'Execute', 'Execute', 'MyDocument.index');</v>
+      <c r="O6" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000005, 'Execute', 'Execute', 'CheckDocument?var=1');</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B7" s="9">
-        <f t="shared" si="1"/>
+      <c r="B7" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000006</v>
       </c>
-      <c r="C7" s="10" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Dashboard.MyDocumentDisposition</v>
-      </c>
-      <c r="D7" s="11" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>My Document Disposition</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="C7" s="2" t="str">
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Dashboard.MyDocumentTracking</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>My Document Tracking</v>
+      </c>
+      <c r="F7" s="17">
         <f t="shared" si="0"/>
         <v>97000000000006</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J7" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K7" s="20"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>48</v>
+      </c>
       <c r="M7" s="6">
         <f t="shared" si="5"/>
         <v>256000000000006</v>
       </c>
-      <c r="O7" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000006, 'Execute', 'Execute', null);</v>
+      <c r="O7" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000006, 'Execute', 'Execute', 'MyDocument?var=1');</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="12">
-        <f t="shared" si="1"/>
+      <c r="B8" s="9">
+        <f t="shared" si="2"/>
         <v>97000000000007</v>
       </c>
-      <c r="C8" s="13" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Country.Transaction</v>
-      </c>
-      <c r="D8" s="14" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Country</v>
-      </c>
-      <c r="F8" s="18">
+      <c r="C8" s="10" t="str">
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Dashboard.MyDocumentDisposition</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>My Document Disposition</v>
+      </c>
+      <c r="F8" s="20">
         <f t="shared" si="0"/>
         <v>97000000000007</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J8" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>11</v>
-      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J8" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K8" s="19"/>
       <c r="M8" s="6">
         <f t="shared" si="5"/>
         <v>256000000000007</v>
       </c>
-      <c r="O8" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000007, 'Execute', 'Execute', 'Country');</v>
+      <c r="O8" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000007, 'Execute', 'Execute', null);</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="7">
-        <f t="shared" si="1"/>
+      <c r="B9" s="12">
+        <f t="shared" si="2"/>
         <v>97000000000008</v>
       </c>
-      <c r="C9" s="2" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
-      </c>
-      <c r="D9" s="3" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Province / State</v>
-      </c>
-      <c r="F9" s="18">
+      <c r="C9" s="13" t="str">
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Country.Transaction</v>
+      </c>
+      <c r="D9" s="13" t="str">
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Country</v>
+      </c>
+      <c r="F9" s="17">
         <f t="shared" si="0"/>
         <v>97000000000008</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J9" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>12</v>
-      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J9" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K9" s="25"/>
       <c r="M9" s="6">
         <f t="shared" si="5"/>
         <v>256000000000008</v>
       </c>
-      <c r="O9" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000008, 'Execute', 'Execute', 'CountryAdministrativeAreaLevel1');</v>
+      <c r="O9" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000008, 'Execute', 'Execute', null);</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000009</v>
       </c>
-      <c r="C10" s="2" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
+      <c r="C10" s="3" t="str">
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="D10" s="3" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Municipality / Regency</v>
-      </c>
-      <c r="F10" s="18">
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Province / State</v>
+      </c>
+      <c r="F10" s="17">
         <f t="shared" si="0"/>
         <v>97000000000009</v>
       </c>
-      <c r="G10" s="17"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="4"/>
       <c r="I10" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J10" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>13</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K10" s="18"/>
       <c r="M10" s="6">
         <f t="shared" si="5"/>
         <v>256000000000009</v>
       </c>
-      <c r="O10" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000009, 'Execute', 'Execute', 'CountryAdministrativeAreaLevel2');</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000009, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000010</v>
       </c>
-      <c r="C11" s="2" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+      <c r="C11" s="3" t="str">
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
       </c>
       <c r="D11" s="3" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>District</v>
-      </c>
-      <c r="F11" s="18">
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Municipality / Regency</v>
+      </c>
+      <c r="F11" s="17">
         <f t="shared" si="0"/>
         <v>97000000000010</v>
       </c>
+      <c r="G11" s="16"/>
       <c r="H11" s="4"/>
       <c r="I11" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J11" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>14</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K11" s="18"/>
       <c r="M11" s="6">
         <f t="shared" si="5"/>
         <v>256000000000010</v>
       </c>
-      <c r="O11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000010, 'Execute', 'Execute', 'CountryAdministrativeAreaLevel3');</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="9">
-        <f t="shared" si="1"/>
+      <c r="O11" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000010, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000011</v>
       </c>
-      <c r="C12" s="10" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
-      </c>
-      <c r="D12" s="11" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Urban Village / Village</v>
-      </c>
-      <c r="F12" s="22">
+      <c r="C12" s="3" t="str">
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>District</v>
+      </c>
+      <c r="F12" s="17">
         <f t="shared" si="0"/>
         <v>97000000000011</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J12" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>15</v>
-      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K12" s="18"/>
       <c r="M12" s="6">
         <f t="shared" si="5"/>
         <v>256000000000011</v>
       </c>
-      <c r="O12" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000011, 'Execute', 'Execute', 'CountryAdministrativeAreaLevel4');</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O12" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000011, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000012</v>
       </c>
-      <c r="C13" s="2" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
+      <c r="C13" s="3" t="str">
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
       </c>
       <c r="D13" s="3" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Business Document Type</v>
-      </c>
-      <c r="F13" s="18">
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Urban Village / Village</v>
+      </c>
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>97000000000012</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J13" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>16</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K13" s="18"/>
       <c r="M13" s="6">
         <f t="shared" si="5"/>
         <v>256000000000012</v>
       </c>
-      <c r="O13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000012, 'Execute', 'Execute', 'BusinessDocumentType');</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000012, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000013</v>
       </c>
-      <c r="C14" s="2" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
+      <c r="C14" s="3" t="str">
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="D14" s="3" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Business Document</v>
-      </c>
-      <c r="F14" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Business Document Type</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" ref="F14:F77" si="7">IF(EXACT(B14, ""), F13, B14)</f>
         <v>97000000000013</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J14" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K14" s="19" t="s">
-        <v>17</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K14" s="18"/>
       <c r="M14" s="6">
         <f t="shared" si="5"/>
         <v>256000000000013</v>
       </c>
-      <c r="O14" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000013, 'Execute', 'Execute', 'BusinessDocument');</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000013, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000014</v>
       </c>
-      <c r="C15" s="2" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
+      <c r="C15" s="3" t="str">
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="D15" s="3" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Business Document Version</v>
-      </c>
-      <c r="F15" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Business Document</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000014</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J15" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>18</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K15" s="18"/>
       <c r="M15" s="6">
         <f t="shared" si="5"/>
         <v>256000000000014</v>
       </c>
-      <c r="O15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000014, 'Execute', 'Execute', 'BusinessDocumentVersion');</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000014, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000015</v>
       </c>
-      <c r="C16" s="2" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.MenuManagement.Transaction</v>
+      <c r="C16" s="3" t="str">
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="D16" s="3" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Menu Management</v>
-      </c>
-      <c r="F16" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Business Document Version</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000015</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J16" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>19</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K16" s="18"/>
       <c r="M16" s="6">
         <f t="shared" si="5"/>
         <v>256000000000015</v>
       </c>
-      <c r="O16" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000015, 'Execute', 'Execute', 'MenuManagement');</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="9">
-        <f t="shared" si="1"/>
+      <c r="O16" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000015, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000016</v>
       </c>
-      <c r="C17" s="10" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.WorkflowRoute.Transaction</v>
-      </c>
-      <c r="D17" s="11" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Workflow Route</v>
-      </c>
-      <c r="F17" s="22">
-        <f t="shared" si="0"/>
+      <c r="C17" s="3" t="str">
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.MenuManagement.Transaction</v>
+      </c>
+      <c r="D17" s="3" t="str">
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Menu Management</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000016</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J17" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>20</v>
-      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K17" s="18"/>
       <c r="M17" s="6">
         <f t="shared" si="5"/>
         <v>256000000000016</v>
       </c>
-      <c r="O17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000016, 'Execute', 'Execute', 'WorkflowRoute?var=1');</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O17" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000016, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000017</v>
       </c>
-      <c r="C18" s="2" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.Budget.Transaction</v>
+      <c r="C18" s="3" t="str">
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="D18" s="3" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Budget</v>
-      </c>
-      <c r="F18" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Privilege Menu</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000017</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J18" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>21</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K18" s="18"/>
       <c r="M18" s="6">
         <f t="shared" si="5"/>
         <v>256000000000017</v>
       </c>
-      <c r="O18" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000017, 'Execute', 'Execute', 'ModifyBudget');</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="7">
-        <f t="shared" si="1"/>
+      <c r="O18" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000017, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="9">
+        <f t="shared" si="2"/>
         <v>97000000000018</v>
       </c>
-      <c r="C19" s="2" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
-      </c>
-      <c r="D19" s="3" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Modify Budget Summary</v>
-      </c>
-      <c r="F19" s="18">
-        <f t="shared" si="0"/>
+      <c r="C19" s="11" t="str">
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
+      </c>
+      <c r="D19" s="11" t="str">
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Workflow</v>
+      </c>
+      <c r="F19" s="20">
+        <f t="shared" si="7"/>
         <v>97000000000018</v>
       </c>
-      <c r="H19" s="4" t="str">
-        <f>D19</f>
-        <v>Report Modify Budget Summary</v>
-      </c>
-      <c r="I19" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Modify Budget Summary</v>
-      </c>
-      <c r="J19" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportModifyBudgetSummary</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>22</v>
-      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J19" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K19" s="19"/>
       <c r="M19" s="6">
         <f t="shared" si="5"/>
         <v>256000000000018</v>
       </c>
-      <c r="O19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000018, 'ReportModifyBudgetSummary', 'Report Modify Budget Summary', 'ReportModifyBudgetSummary');</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="9">
-        <f t="shared" si="1"/>
+      <c r="O19" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000018, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000019</v>
       </c>
-      <c r="C20" s="10" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
-      </c>
-      <c r="D20" s="11" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Cost Financial Structure</v>
-      </c>
-      <c r="F20" s="22">
-        <f t="shared" si="0"/>
+      <c r="C20" s="3" t="str">
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+      </c>
+      <c r="D20" s="3" t="str">
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Budget</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000019</v>
       </c>
-      <c r="H20" s="15" t="str">
-        <f>D20</f>
-        <v>Report Cost Financial Structure</v>
-      </c>
-      <c r="I20" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Cost Financial Structure</v>
-      </c>
-      <c r="J20" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportCostFinancialStructure</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>23</v>
-      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K20" s="18"/>
       <c r="M20" s="6">
         <f t="shared" si="5"/>
         <v>256000000000019</v>
       </c>
-      <c r="O20" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000019, 'ReportCostFinancialStructure', 'Report Cost Financial Structure', 'ReportCFS');</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O20" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000019, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000020</v>
       </c>
-      <c r="C21" s="2" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Religion.Transaction</v>
+      <c r="C21" s="3" t="str">
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Religion</v>
-      </c>
-      <c r="F21" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sub Budget</v>
+      </c>
+      <c r="F21" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000020</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J21" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>26</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K21" s="18"/>
       <c r="M21" s="6">
         <f t="shared" si="5"/>
         <v>256000000000020</v>
       </c>
-      <c r="O21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000020, 'Execute', 'Execute', 'Religion');</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O21" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000020, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000021</v>
       </c>
-      <c r="C22" s="2" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+      <c r="C22" s="3" t="str">
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Blood Aglutinogen Type</v>
-      </c>
-      <c r="F22" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Modify Budget</v>
+      </c>
+      <c r="F22" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000021</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J22" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>27</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" si="5"/>
         <v>256000000000021</v>
       </c>
-      <c r="O22" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000021, 'Execute', 'Execute', 'BloodAglutinogenType');</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="9">
-        <f t="shared" si="1"/>
+      <c r="O22" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000021, 'Execute', 'Execute', 'ModifyBudget?var=1');</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000022</v>
       </c>
-      <c r="C23" s="10" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
-      </c>
-      <c r="D23" s="11" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Person Work Time Sheet</v>
-      </c>
-      <c r="F23" s="22">
-        <f t="shared" si="0"/>
+      <c r="C23" s="3" t="str">
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Modify Budget Summary</v>
+      </c>
+      <c r="F23" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000022</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J23" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>28</v>
+      <c r="H23" s="4" t="str">
+        <f>D23</f>
+        <v>Report Modify Budget Summary</v>
+      </c>
+      <c r="I23" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Report Modify Budget Summary</v>
+      </c>
+      <c r="J23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>ReportModifyBudgetSummary</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>9</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="5"/>
         <v>256000000000022</v>
       </c>
-      <c r="O23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000022, 'Execute', 'Execute', 'Timesheet');</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000022, 'ReportModifyBudgetSummary', 'Report Modify Budget Summary', 'ReportModifyBudgetSummary');</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000023</v>
       </c>
-      <c r="C24" s="2" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+      <c r="C24" s="3" t="str">
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Warehouse</v>
-      </c>
-      <c r="F24" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Work</v>
+      </c>
+      <c r="F24" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000023</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J24" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>29</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K24" s="18"/>
       <c r="M24" s="6">
         <f t="shared" si="5"/>
         <v>256000000000023</v>
       </c>
-      <c r="O24" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000023, 'Execute', 'Execute', 'Warehouse');</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="7">
-        <f t="shared" si="1"/>
+      <c r="O24" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000023, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="9">
+        <f t="shared" si="2"/>
         <v>97000000000024</v>
       </c>
-      <c r="C25" s="2" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
-      </c>
-      <c r="D25" s="3" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Product Type</v>
-      </c>
-      <c r="F25" s="18">
-        <f t="shared" si="0"/>
+      <c r="C25" s="11" t="str">
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+      </c>
+      <c r="D25" s="11" t="str">
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Cost Financial Structure</v>
+      </c>
+      <c r="F25" s="20">
+        <f t="shared" si="7"/>
         <v>97000000000024</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J25" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>30</v>
-      </c>
+      <c r="H25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Report Modify Budget Summary</v>
+      </c>
+      <c r="J25" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ReportCostFinancialStructure</v>
+      </c>
+      <c r="K25" s="19"/>
       <c r="M25" s="6">
         <f t="shared" si="5"/>
         <v>256000000000024</v>
       </c>
-      <c r="O25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000024, 'Execute', 'Execute', 'ProductType');</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O25" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000024, 'ReportCostFinancialStructure', 'Report Modify Budget Summary', null);</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000025</v>
       </c>
-      <c r="C26" s="2" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Product.Transaction</v>
+      <c r="C26" s="3" t="str">
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="F26" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Blood Aglutinogen Type</v>
+      </c>
+      <c r="F26" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000025</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J26" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K26" s="19" t="s">
-        <v>31</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K26" s="18"/>
       <c r="M26" s="6">
         <f t="shared" si="5"/>
         <v>256000000000025</v>
       </c>
-      <c r="O26" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000025, 'Execute', 'Execute', 'Product');</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O26" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000025, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000026</v>
       </c>
-      <c r="C27" s="2" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+      <c r="C27" s="3" t="str">
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report DO Summary</v>
-      </c>
-      <c r="F27" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Person</v>
+      </c>
+      <c r="F27" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000026</v>
       </c>
-      <c r="H27" s="4" t="str">
-        <f>D27</f>
-        <v>Report DO Summary</v>
-      </c>
+      <c r="H27" s="4"/>
       <c r="I27" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report DO Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J27" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportDOSummary</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>32</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K27" s="18"/>
       <c r="M27" s="6">
         <f t="shared" si="5"/>
         <v>256000000000026</v>
       </c>
-      <c r="O27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000026, 'ReportDOSummary', 'Report DO Summary', 'ReportDOSummary');</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O27" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000026, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000027</v>
       </c>
-      <c r="C28" s="2" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+      <c r="C28" s="3" t="str">
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="D28" s="3" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Delivery Order</v>
-      </c>
-      <c r="F28" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Religion</v>
+      </c>
+      <c r="F28" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000027</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J28" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>33</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K28" s="18"/>
       <c r="M28" s="6">
         <f t="shared" si="5"/>
         <v>256000000000027</v>
       </c>
-      <c r="O28" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000027, 'Execute', 'Execute', 'DeliveryOrder?var=1');</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O28" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000027, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000028</v>
       </c>
-      <c r="C29" s="2" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+      <c r="C29" s="3" t="str">
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="D29" s="3" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Material Receive</v>
-      </c>
-      <c r="F29" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Role</v>
+      </c>
+      <c r="F29" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000028</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J29" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>34</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K29" s="18"/>
       <c r="M29" s="6">
         <f t="shared" si="5"/>
         <v>256000000000028</v>
       </c>
-      <c r="O29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000028, 'Execute', 'Execute', 'MaterialReceive?var=1');</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O29" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000028, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000029</v>
       </c>
-      <c r="C30" s="2" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+      <c r="C30" s="3" t="str">
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="D30" s="3" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Material Return Summary</v>
-      </c>
-      <c r="F30" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Department</v>
+      </c>
+      <c r="F30" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000029</v>
       </c>
-      <c r="H30" s="4" t="str">
-        <f>D30</f>
-        <v>Report Material Return Summary</v>
-      </c>
+      <c r="H30" s="4"/>
       <c r="I30" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Material Return Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J30" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportMaterialReturnSummary</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>35</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K30" s="18"/>
       <c r="M30" s="6">
         <f t="shared" si="5"/>
         <v>256000000000029</v>
       </c>
-      <c r="O30" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000029, 'ReportMaterialReturnSummary', 'Report Material Return Summary', 'ReportMatReturnSummary');</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="9">
-        <f t="shared" si="1"/>
+      <c r="O30" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000029, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000030</v>
       </c>
-      <c r="C31" s="10" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
-      </c>
-      <c r="D31" s="11" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Material Return</v>
-      </c>
-      <c r="F31" s="22">
-        <f t="shared" si="0"/>
+      <c r="C31" s="3" t="str">
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Person Work Time Sheet</v>
+      </c>
+      <c r="F31" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000030</v>
       </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J31" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K31" s="20" t="s">
-        <v>36</v>
-      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K31" s="18"/>
       <c r="M31" s="6">
         <f t="shared" si="5"/>
         <v>256000000000030</v>
       </c>
-      <c r="O31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000030, 'Execute', 'Execute', 'MaterialReturn?var=1');</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O31" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000030, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000031</v>
       </c>
-      <c r="C32" s="2" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+      <c r="C32" s="3" t="str">
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="D32" s="3" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Advance Summary</v>
-      </c>
-      <c r="F32" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Person Work Time Sheet Summary</v>
+      </c>
+      <c r="F32" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000031</v>
       </c>
-      <c r="H32" s="4" t="str">
-        <f>D32</f>
-        <v>Report Advance Summary</v>
-      </c>
+      <c r="H32" s="4"/>
       <c r="I32" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Advance Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J32" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportAdvanceSummary</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>PersonWorkTimeSheetSummary</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="M32" s="6">
         <f t="shared" si="5"/>
         <v>256000000000031</v>
       </c>
-      <c r="O32" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000031, 'ReportAdvanceSummary', 'Report Advance Summary', 'ReportAdvanceSummary');</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O32" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000031, 'PersonWorkTimeSheetSummary', 'Execute', 'ReportTimesheetSummary');</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000032</v>
       </c>
-      <c r="C33" s="2" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+      <c r="C33" s="3" t="str">
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="D33" s="3" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Advance Request</v>
-      </c>
-      <c r="F33" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sallary Allocation</v>
+      </c>
+      <c r="F33" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000032</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J33" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>38</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K33" s="18"/>
       <c r="M33" s="6">
         <f t="shared" si="5"/>
         <v>256000000000032</v>
       </c>
-      <c r="O33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000032, 'Execute', 'Execute', 'AdvanceRequest?var=1');</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="7">
-        <f t="shared" si="1"/>
+      <c r="O33" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000032, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="9">
+        <f t="shared" si="2"/>
         <v>97000000000033</v>
       </c>
-      <c r="C34" s="2" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
-      </c>
-      <c r="D34" s="3" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Advance Settlement Summary</v>
-      </c>
-      <c r="F34" s="18">
-        <f t="shared" si="0"/>
+      <c r="C34" s="11" t="str">
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+      </c>
+      <c r="D34" s="11" t="str">
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sallary Allocation Summary</v>
+      </c>
+      <c r="F34" s="20">
+        <f t="shared" si="7"/>
         <v>97000000000033</v>
       </c>
-      <c r="H34" s="4" t="str">
-        <f>D34</f>
-        <v>Report Advance Settlement Summary</v>
-      </c>
-      <c r="I34" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Advance Settlement Summary</v>
-      </c>
-      <c r="J34" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportAdvanceSettlementSummary</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>39</v>
-      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J34" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>SallaryAllocationSummary</v>
+      </c>
+      <c r="K34" s="19"/>
       <c r="M34" s="6">
         <f t="shared" si="5"/>
         <v>256000000000033</v>
       </c>
-      <c r="O34" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000033, 'ReportAdvanceSettlementSummary', 'Report Advance Settlement Summary', 'ReportAdvanceSettlementSummary');</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O34" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000033, 'SallaryAllocationSummary', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000034</v>
       </c>
-      <c r="C35" s="2" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+      <c r="C35" s="3" t="str">
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="D35" s="3" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>AdvanceSettlement</v>
-      </c>
-      <c r="F35" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Warehouse</v>
+      </c>
+      <c r="F35" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000034</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J35" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>40</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K35" s="18"/>
       <c r="M35" s="6">
         <f t="shared" si="5"/>
         <v>256000000000034</v>
       </c>
-      <c r="O35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000034, 'Execute', 'Execute', 'AdvanceSettlement?var=1');</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O35" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000034, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000035</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+      <c r="C36" s="3" t="str">
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report BusinessTrip Settlement Summary</v>
-      </c>
-      <c r="F36" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Product Type</v>
+      </c>
+      <c r="F36" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000035</v>
       </c>
-      <c r="H36" s="4" t="str">
-        <f>D36</f>
-        <v>Report BusinessTrip Settlement Summary</v>
-      </c>
+      <c r="H36" s="4"/>
       <c r="I36" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report BusinessTrip Settlement Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J36" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportBusinessTripSettlementSummary</v>
-      </c>
-      <c r="K36" s="19" t="s">
-        <v>41</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K36" s="18"/>
       <c r="M36" s="6">
         <f t="shared" si="5"/>
         <v>256000000000035</v>
       </c>
-      <c r="O36" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000035, 'ReportBusinessTripSettlementSummary', 'Report BusinessTrip Settlement Summary', 'ReportBusinessTripSettlementSummary');</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O36" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000035, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000036</v>
       </c>
-      <c r="C37" s="2" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+      <c r="C37" s="3" t="str">
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="D37" s="3" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>BusinessTrip Settlement</v>
-      </c>
-      <c r="F37" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="F37" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000036</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J37" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>42</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K37" s="18"/>
       <c r="M37" s="6">
         <f t="shared" si="5"/>
         <v>256000000000036</v>
       </c>
-      <c r="O37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000036, 'Execute', 'Execute', 'BusinessTripSettlement?var=1');</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O37" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000036, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000037</v>
       </c>
-      <c r="C38" s="2" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+      <c r="C38" s="3" t="str">
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="D38" s="3" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report BusinessTrip Request Summary</v>
-      </c>
-      <c r="F38" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Delivery Order</v>
+      </c>
+      <c r="F38" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000037</v>
       </c>
-      <c r="H38" s="4" t="str">
-        <f>D38</f>
-        <v>Report BusinessTrip Request Summary</v>
-      </c>
+      <c r="H38" s="4"/>
       <c r="I38" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report BusinessTrip Request Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J38" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportBusinessTripRequestSummary</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>43</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>11</v>
       </c>
       <c r="M38" s="6">
         <f t="shared" si="5"/>
         <v>256000000000037</v>
       </c>
-      <c r="O38" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000037, 'ReportBusinessTripRequestSummary', 'Report BusinessTrip Request Summary', 'ReportBusinessTripRequestSummary');</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="9">
-        <f t="shared" si="1"/>
+      <c r="O38" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000037, 'Execute', 'Execute', 'DeliveryOrder?var=1');</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="7">
+        <f t="shared" si="2"/>
         <v>97000000000038</v>
       </c>
-      <c r="C39" s="10" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
-      </c>
-      <c r="D39" s="11" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>BusinessTrip Request</v>
-      </c>
-      <c r="F39" s="22">
-        <f t="shared" si="0"/>
+      <c r="C39" s="3" t="str">
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report DO Summary</v>
+      </c>
+      <c r="F39" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000038</v>
       </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J39" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>44</v>
+      <c r="H39" s="4"/>
+      <c r="I39" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J39" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>ReportDOSummary</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>10</v>
       </c>
       <c r="M39" s="6">
         <f t="shared" si="5"/>
         <v>256000000000038</v>
       </c>
-      <c r="O39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000038, 'Execute', 'Execute', 'BusinessTripRequest?var=1');</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O39" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000038, 'ReportDOSummary', 'Execute', 'ReportDOSummary');</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000039</v>
       </c>
-      <c r="C40" s="2" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+      <c r="C40" s="3" t="str">
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="D40" s="3" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Supplier</v>
-      </c>
-      <c r="F40" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report DO to Material Receive</v>
+      </c>
+      <c r="F40" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000039</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J40" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K40" s="19" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>ReportDOtoMaterialReceive</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="M40" s="6">
         <f t="shared" si="5"/>
         <v>256000000000039</v>
       </c>
-      <c r="O40" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000039, 'Execute', 'Execute', 'Supplier');</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O40" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000039, 'ReportDOtoMaterialReceive', 'Execute', 'ReportDoToMaterialReceive');</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000040</v>
       </c>
-      <c r="C41" s="2" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+      <c r="C41" s="3" t="str">
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="D41" s="3" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Purchase Requisition Summary</v>
-      </c>
-      <c r="F41" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Material Receive</v>
+      </c>
+      <c r="F41" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000040</v>
       </c>
-      <c r="H41" s="4" t="str">
-        <f>D41</f>
-        <v>Report Purchase Requisition Summary</v>
-      </c>
+      <c r="H41" s="4"/>
       <c r="I41" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Purchase Requisition Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J41" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportPurchaseRequisitionSummary</v>
-      </c>
-      <c r="K41" s="19" t="s">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="5"/>
         <v>256000000000040</v>
       </c>
-      <c r="O41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000040, 'ReportPurchaseRequisitionSummary', 'Report Purchase Requisition Summary', 'ReportPurchaseRequisitionSummary');</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O41" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000040, 'Execute', 'Execute', 'MaterialReceive?var=1');</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000041</v>
       </c>
-      <c r="C42" s="2" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+      <c r="C42" s="3" t="str">
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="D42" s="3" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Purchase Requisition To Purchase Order</v>
-      </c>
-      <c r="F42" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Material Receive Summary</v>
+      </c>
+      <c r="F42" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000041</v>
       </c>
-      <c r="H42" s="4" t="str">
-        <f>D42</f>
-        <v>Report Purchase Requisition To Purchase Order</v>
-      </c>
+      <c r="H42" s="4"/>
       <c r="I42" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J42" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportPurchaseRequisitionToPurchaseOrder</v>
-      </c>
-      <c r="K42" s="19" t="s">
-        <v>47</v>
+        <f t="shared" si="1"/>
+        <v>ReportMaterialReceiveSummary</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="M42" s="6">
         <f t="shared" si="5"/>
         <v>256000000000041</v>
       </c>
-      <c r="O42" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000041, 'ReportPurchaseRequisitionToPurchaseOrder', 'Report Purchase Requisition To Purchase Order', 'ReportPurchaseRequisitionToPurchaseOrder');</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O42" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000041, 'ReportMaterialReceiveSummary', 'Execute', 'ReportMaterialReceiveSummary');</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000042</v>
       </c>
-      <c r="C43" s="2" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+      <c r="C43" s="3" t="str">
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="D43" s="3" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Purchase Requisition</v>
-      </c>
-      <c r="F43" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Material Receive to Material Return</v>
+      </c>
+      <c r="F43" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000042</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J43" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K43" s="19" t="s">
-        <v>48</v>
+        <f t="shared" si="1"/>
+        <v>ReportMaterialReceivetoMaterialReturn</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="5"/>
         <v>256000000000042</v>
       </c>
-      <c r="O43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000042, 'Execute', 'Execute', 'PurchaseRequisition?var=1');</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O43" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000042, 'ReportMaterialReceivetoMaterialReturn', 'Execute', 'ReportMatReceivetoMatReturn');</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000043</v>
       </c>
-      <c r="C44" s="2" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+      <c r="C44" s="3" t="str">
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="D44" s="3" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Report Purchase Order Summary</v>
-      </c>
-      <c r="F44" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Material Return</v>
+      </c>
+      <c r="F44" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000043</v>
       </c>
-      <c r="H44" s="4" t="str">
-        <f>D44</f>
-        <v>Report Purchase Order Summary</v>
-      </c>
+      <c r="H44" s="4"/>
       <c r="I44" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Report Purchase Order Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J44" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReportPurchaseOrderSummary</v>
-      </c>
-      <c r="K44" s="19" t="s">
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="M44" s="6">
         <f t="shared" si="5"/>
         <v>256000000000043</v>
       </c>
-      <c r="O44" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000043, 'ReportPurchaseOrderSummary', 'Report Purchase Order Summary', 'ReportPurchaseOrderSummary');</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O44" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000043, 'Execute', 'Execute', 'MaterialReturn?var=1');</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000044</v>
       </c>
-      <c r="C45" s="10" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+      <c r="C45" s="11" t="str">
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="D45" s="11" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Purchase Order</v>
-      </c>
-      <c r="F45" s="22">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Material Return Summary</v>
+      </c>
+      <c r="F45" s="20">
+        <f t="shared" si="7"/>
         <v>97000000000044</v>
       </c>
-      <c r="H45" s="15"/>
+      <c r="H45" s="14"/>
       <c r="I45" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J45" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K45" s="20" t="s">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>ReportMaterialReturnSummary</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="5"/>
         <v>256000000000044</v>
       </c>
-      <c r="O45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000044, 'Execute', 'Execute', 'PurchaseOrder?var=1');</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O45" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000044, 'ReportMaterialReturnSummary', 'Execute', 'ReportMatReturnSummary');</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000045</v>
       </c>
-      <c r="C46" s="2" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Period.Transaction</v>
+      <c r="C46" s="3" t="str">
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="D46" s="3" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Period</v>
-      </c>
-      <c r="F46" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Advance Request</v>
+      </c>
+      <c r="F46" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000045</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J46" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="M46" s="6">
         <f t="shared" si="5"/>
         <v>256000000000045</v>
       </c>
-      <c r="O46" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000045, 'Execute', 'Execute', 'Periode');</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O46" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000045, 'Execute', 'Execute', 'AdvanceRequest?var=1');</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000046</v>
       </c>
-      <c r="C47" s="2" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+      <c r="C47" s="3" t="str">
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="D47" s="3" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Currency</v>
-      </c>
-      <c r="F47" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Advance Summary</v>
+      </c>
+      <c r="F47" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000046</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J47" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K47" s="19" t="s">
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>ReportAdvanceSummary</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>15</v>
       </c>
       <c r="M47" s="6">
         <f t="shared" si="5"/>
         <v>256000000000046</v>
       </c>
-      <c r="O47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000046, 'Execute', 'Execute', 'Currency');</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O47" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000046, 'ReportAdvanceSummary', 'Execute', 'ReportAdvanceSummary');</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000047</v>
       </c>
-      <c r="C48" s="2" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      <c r="C48" s="3" t="str">
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D48" s="3" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Reimbursement</v>
-      </c>
-      <c r="F48" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Advance to Advance Settlement</v>
+      </c>
+      <c r="F48" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000047</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J48" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K48" s="19" t="s">
-        <v>51</v>
+        <f t="shared" si="1"/>
+        <v>ReportAdvancetoAdvanceSettlement</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="M48" s="6">
         <f t="shared" si="5"/>
         <v>256000000000047</v>
       </c>
-      <c r="O48" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000047, 'Execute', 'Execute', 'Reimbursement?var=1');</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O48" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000047, 'ReportAdvancetoAdvanceSettlement', 'Execute', 'ReportAdvanceToASF');</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000048</v>
       </c>
-      <c r="C49" s="2" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      <c r="C49" s="3" t="str">
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="D49" s="3" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Reimbursement Summary</v>
-      </c>
-      <c r="F49" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>AdvanceSettlement</v>
+      </c>
+      <c r="F49" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000048</v>
       </c>
-      <c r="H49" s="4" t="str">
-        <f>D49</f>
-        <v>Reimbursement Summary</v>
-      </c>
+      <c r="H49" s="4"/>
       <c r="I49" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Reimbursement Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J49" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>ReimbursementSummary</v>
-      </c>
-      <c r="K49" s="19" t="s">
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="M49" s="6">
         <f t="shared" si="5"/>
         <v>256000000000048</v>
       </c>
-      <c r="O49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000048, 'ReimbursementSummary', 'Reimbursement Summary', 'ReportReimbursementSummary');</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O49" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000048, 'Execute', 'Execute', 'AdvanceSettlement?var=1');</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000049</v>
       </c>
-      <c r="C50" s="2" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+      <c r="C50" s="3" t="str">
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D50" s="3" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Debit Note</v>
-      </c>
-      <c r="F50" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Advance Settlement Summary</v>
+      </c>
+      <c r="F50" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000049</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J50" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K50" s="19" t="s">
-        <v>53</v>
+        <f t="shared" si="1"/>
+        <v>ReportAdvanceSettlementSummary</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="M50" s="6">
         <f t="shared" si="5"/>
         <v>256000000000049</v>
       </c>
-      <c r="O50" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000049, 'Execute', 'Execute', 'DebitNote?var=1');</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O50" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000049, 'ReportAdvanceSettlementSummary', 'Execute', 'ReportAdvanceSettlementSummary');</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000050</v>
       </c>
-      <c r="C51" s="2" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+      <c r="C51" s="3" t="str">
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="D51" s="3" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Debit Note Summary</v>
-      </c>
-      <c r="F51" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>BusinessTrip Request</v>
+      </c>
+      <c r="F51" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000050</v>
       </c>
-      <c r="H51" s="4" t="str">
-        <f>D51</f>
-        <v>Debit Note Summary</v>
-      </c>
+      <c r="H51" s="4"/>
       <c r="I51" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Debit Note Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J51" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>DebitNoteSummary</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" si="5"/>
         <v>256000000000050</v>
       </c>
-      <c r="O51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000050, 'DebitNoteSummary', 'Debit Note Summary', 'ReportDebitNoteSummary');</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O51" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000050, 'Execute', 'Execute', 'BusinessTripRequest?var=1');</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000051</v>
       </c>
-      <c r="C52" s="2" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      <c r="C52" s="3" t="str">
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="D52" s="3" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Reimbursement to Debit Note</v>
-      </c>
-      <c r="F52" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report BusinessTrip Request Summary</v>
+      </c>
+      <c r="F52" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000051</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J52" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>55</v>
+        <f t="shared" si="1"/>
+        <v>ReportBusinessTripRequestSummary</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="M52" s="6">
         <f t="shared" si="5"/>
         <v>256000000000051</v>
       </c>
-      <c r="O52" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000051, 'Execute', 'Execute', 'ReportRemToDN');</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O52" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000051, 'ReportBusinessTripRequestSummary', 'Execute', 'ReportBusinessTripRequestSummary');</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000052</v>
       </c>
-      <c r="C53" s="2" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+      <c r="C53" s="3" t="str">
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="D53" s="3" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Credit Note</v>
-      </c>
-      <c r="F53" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
+      </c>
+      <c r="F53" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000052</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J53" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K53" s="19" t="s">
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>ReportBusinessTriptoBusinessTripSettlement</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>59</v>
       </c>
       <c r="M53" s="6">
         <f t="shared" si="5"/>
         <v>256000000000052</v>
       </c>
-      <c r="O53" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000052, 'Execute', 'Execute', 'CreditNote?var=1');</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O53" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000052, 'ReportBusinessTriptoBusinessTripSettlement', 'Execute', 'ReportBusinessTripToBSF');</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000053</v>
       </c>
-      <c r="C54" s="2" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+      <c r="C54" s="3" t="str">
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="D54" s="3" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Credit Note Summary</v>
-      </c>
-      <c r="F54" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>BusinessTrip Settlement</v>
+      </c>
+      <c r="F54" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000053</v>
       </c>
-      <c r="H54" s="4" t="str">
-        <f>D54</f>
-        <v>Credit Note Summary</v>
-      </c>
+      <c r="H54" s="4"/>
       <c r="I54" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Credit Note Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J54" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>CreditNoteSummary</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>57</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="M54" s="6">
         <f t="shared" si="5"/>
         <v>256000000000053</v>
       </c>
-      <c r="O54" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000053, 'CreditNoteSummary', 'Credit Note Summary', 'ReportCreditNoteSummary');</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="7">
-        <f t="shared" si="1"/>
+      <c r="O54" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000053, 'Execute', 'Execute', 'BusinessTripSettlement?var=1');</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="9">
+        <f t="shared" si="2"/>
         <v>97000000000054</v>
       </c>
-      <c r="C55" s="2" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Transaction</v>
-      </c>
-      <c r="D55" s="3" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Loan</v>
-      </c>
-      <c r="F55" s="18">
-        <f t="shared" si="0"/>
+      <c r="C55" s="11" t="str">
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+      </c>
+      <c r="D55" s="11" t="str">
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report BusinessTrip Settlement Summary</v>
+      </c>
+      <c r="F55" s="20">
+        <f t="shared" si="7"/>
         <v>97000000000054</v>
       </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J55" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
+      <c r="H55" s="14"/>
+      <c r="I55" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J55" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>ReportBusinessTripSettlementSummary</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" si="5"/>
         <v>256000000000054</v>
       </c>
-      <c r="O55" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000054, 'Execute', 'Execute', 'Loan?var=1');</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O55" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000054, 'ReportBusinessTripSettlementSummary', 'Execute', 'ReportBusinessTripSettlementSummary');</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B56" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000055</v>
       </c>
-      <c r="C56" s="2" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      <c r="C56" s="3" t="str">
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="D56" s="3" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Loan Summary</v>
-      </c>
-      <c r="F56" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Supplier</v>
+      </c>
+      <c r="F56" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000055</v>
       </c>
-      <c r="H56" s="4" t="str">
-        <f>D56</f>
-        <v>Loan Summary</v>
-      </c>
+      <c r="H56" s="4"/>
       <c r="I56" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Loan Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J56" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>LoanSummary</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>59</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="M56" s="6">
         <f t="shared" si="5"/>
         <v>256000000000055</v>
       </c>
-      <c r="O56" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000055, 'LoanSummary', 'Loan Summary', 'ReportLoanSummary');</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O56" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000055, 'Execute', 'Execute', 'Supplier');</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B57" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000056</v>
       </c>
-      <c r="C57" s="2" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      <c r="C57" s="3" t="str">
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="D57" s="3" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Loan Settlement</v>
-      </c>
-      <c r="F57" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Purchase Requisition</v>
+      </c>
+      <c r="F57" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000056</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J57" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" si="5"/>
         <v>256000000000056</v>
       </c>
-      <c r="O57" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000056, 'Execute', 'Execute', 'LoanSettlement?var=1');</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O57" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000056, 'Execute', 'Execute', 'PurchaseRequisition?var=1');</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B58" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000057</v>
       </c>
-      <c r="C58" s="2" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      <c r="C58" s="3" t="str">
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="D58" s="3" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Loan Settlement Summary</v>
-      </c>
-      <c r="F58" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Purchase Requisition Summary</v>
+      </c>
+      <c r="F58" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000057</v>
       </c>
-      <c r="H58" s="4" t="str">
-        <f>D58</f>
-        <v>Loan Settlement Summary</v>
-      </c>
+      <c r="H58" s="4"/>
       <c r="I58" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Loan Settlement Summary</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J58" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>LoanSettlementSummary</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>61</v>
+        <f t="shared" si="1"/>
+        <v>ReportPurchaseRequisitionSummary</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="5"/>
         <v>256000000000057</v>
       </c>
-      <c r="O58" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000057, 'LoanSettlementSummary', 'Loan Settlement Summary', 'ReportLoanSettlementSummary');</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O58" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000057, 'ReportPurchaseRequisitionSummary', 'Execute', 'ReportPurchaseRequisitionSummary');</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B59" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000058</v>
       </c>
-      <c r="C59" s="2" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      <c r="C59" s="3" t="str">
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="D59" s="3" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Loan to Loan Settlement</v>
-      </c>
-      <c r="F59" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Purchase Requisition To Purchase Order</v>
+      </c>
+      <c r="F59" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000058</v>
       </c>
-      <c r="H59" s="4" t="str">
-        <f>D59</f>
-        <v>Loan to Loan Settlement</v>
-      </c>
+      <c r="H59" s="4"/>
       <c r="I59" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Loan to Loan Settlement</v>
+        <f t="shared" si="3"/>
+        <v>Execute</v>
       </c>
       <c r="J59" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>LoantoLoanSettlement</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>62</v>
+        <f t="shared" si="1"/>
+        <v>ReportPurchaseRequisitionToPurchaseOrder</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" si="5"/>
         <v>256000000000058</v>
       </c>
-      <c r="O59" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000058, 'LoantoLoanSettlement', 'Loan to Loan Settlement', 'ReportLoantoLoanSettlement');</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O59" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000058, 'ReportPurchaseRequisitionToPurchaseOrder', 'Execute', 'ReportPurchaseRequisitionToPurchaseOrder');</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B60" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000059</v>
       </c>
-      <c r="C60" s="2" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
+      <c r="C60" s="3" t="str">
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="D60" s="3" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Cash &amp; Bank</v>
-      </c>
-      <c r="F60" s="18">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Purchase Order</v>
+      </c>
+      <c r="F60" s="17">
+        <f t="shared" si="7"/>
         <v>97000000000059</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
       <c r="J60" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K60" s="19" t="s">
-        <v>63</v>
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="M60" s="6">
         <f t="shared" si="5"/>
         <v>256000000000059</v>
       </c>
-      <c r="O60" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000059, 'Execute', 'Execute', 'Journal?var=1');</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O60" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000059, 'Execute', 'Execute', 'PurchaseOrder?var=1');</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B61" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97000000000060</v>
       </c>
-      <c r="C61" s="2" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+      <c r="C61" s="3" t="str">
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+      </c>
+      <c r="D61" s="3" t="str">
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Report Purchase Order Summary</v>
+      </c>
+      <c r="F61" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000060</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J61" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>ReportPurchaseOrderSummary</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M61" s="6">
+        <f t="shared" si="5"/>
+        <v>256000000000060</v>
+      </c>
+      <c r="O61" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000060, 'ReportPurchaseOrderSummary', 'Execute', 'ReportPurchaseOrderSummary');</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="9">
+        <f t="shared" si="2"/>
+        <v>97000000000061</v>
+      </c>
+      <c r="C62" s="11" t="str">
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="D62" s="11" t="str">
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Purchase Order to Account Payable</v>
+      </c>
+      <c r="F62" s="20">
+        <f t="shared" si="7"/>
+        <v>97000000000061</v>
+      </c>
+      <c r="H62" s="14"/>
+      <c r="I62" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J62" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>PurchaseOrdertoAccountPayable</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M62" s="6">
+        <f t="shared" si="5"/>
+        <v>256000000000061</v>
+      </c>
+      <c r="O62" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000061, 'PurchaseOrdertoAccountPayable', 'Execute', 'ReportPOtoAP');</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="7">
+        <f t="shared" si="2"/>
+        <v>97000000000062</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Bank.Transaction</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Bank</v>
+      </c>
+      <c r="F63" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000062</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J63" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K63" s="18"/>
+      <c r="M63" s="6">
+        <f t="shared" si="5"/>
+        <v>256000000000062</v>
+      </c>
+      <c r="O63" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000062, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="7">
+        <f t="shared" si="2"/>
+        <v>97000000000063</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Bank Account</v>
+      </c>
+      <c r="F64" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000063</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>Execute</v>
+      </c>
+      <c r="J64" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K64" s="18"/>
+      <c r="M64" s="6">
+        <f t="shared" si="5"/>
+        <v>256000000000063</v>
+      </c>
+      <c r="O64" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000063, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="7">
+        <f t="shared" si="2"/>
+        <v>97000000000064</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Currency.Transaction</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Currency</v>
+      </c>
+      <c r="F65" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000064</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="3" t="str">
+        <f t="shared" ref="I65:I98" si="8">IF(EXACT(F65, ""), "", IF(EXACT(H65, ""), "Execute", H65))</f>
+        <v>Execute</v>
+      </c>
+      <c r="J65" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Execute</v>
+      </c>
+      <c r="K65" s="18"/>
+      <c r="M65" s="6">
+        <f t="shared" si="5"/>
+        <v>256000000000064</v>
+      </c>
+      <c r="O65" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000064, 'Execute', 'Execute', null);</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B66" s="7">
+        <f t="shared" si="2"/>
+        <v>97000000000065</v>
+      </c>
+      <c r="C66" s="3" t="str">
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Exchange Rate</v>
+      </c>
+      <c r="F66" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000065</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J66" s="3" t="str">
+        <f t="shared" ref="J66:J90" si="9">IF(EXACT(F66, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C66)), D66, IF(EXACT(H66, ""), "Execute", H66)), " ", ""), "&amp;", "")
+)</f>
+        <v>Execute</v>
+      </c>
+      <c r="K66" s="18"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B67" s="7">
+        <f t="shared" ref="B67:B98" si="10">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
+        <v>97000000000066</v>
+      </c>
+      <c r="C67" s="3" t="str">
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Exchange Rate Summary</v>
+      </c>
+      <c r="F67" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000066</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J67" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ExchangeRateSummary</v>
+      </c>
+      <c r="K67" s="18"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B68" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000067</v>
+      </c>
+      <c r="C68" s="3" t="str">
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+      </c>
+      <c r="D68" s="3" t="str">
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Payment Term</v>
+      </c>
+      <c r="F68" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000067</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J68" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K68" s="18"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B69" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000068</v>
+      </c>
+      <c r="C69" s="3" t="str">
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.General.MasterData.Period.Transaction</v>
+      </c>
+      <c r="D69" s="3" t="str">
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Period</v>
+      </c>
+      <c r="F69" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000068</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J69" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K69" s="18"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B70" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000069</v>
+      </c>
+      <c r="C70" s="3" t="str">
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+      </c>
+      <c r="D70" s="3" t="str">
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Asset Category</v>
+      </c>
+      <c r="F70" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000069</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J70" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K70" s="18"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B71" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000070</v>
+      </c>
+      <c r="C71" s="3" t="str">
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+      </c>
+      <c r="D71" s="3" t="str">
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Chart of Account</v>
+      </c>
+      <c r="F71" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000070</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J71" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K71" s="18"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B72" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000071</v>
+      </c>
+      <c r="C72" s="3" t="str">
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+      </c>
+      <c r="D72" s="3" t="str">
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Depreciation Method</v>
+      </c>
+      <c r="F72" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000071</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J72" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K72" s="18"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B73" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000072</v>
+      </c>
+      <c r="C73" s="3" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+      </c>
+      <c r="D73" s="3" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Depreciation Rate Years</v>
+      </c>
+      <c r="F73" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000072</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J73" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K73" s="18"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B74" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000073</v>
+      </c>
+      <c r="C74" s="3" t="str">
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+      </c>
+      <c r="D74" s="3" t="str">
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Value Added Tax</v>
+      </c>
+      <c r="F74" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000073</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J74" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K74" s="18"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B75" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000074</v>
+      </c>
+      <c r="C75" s="3" t="str">
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+      </c>
+      <c r="D75" s="3" t="str">
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>General Journal</v>
+      </c>
+      <c r="F75" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000074</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J75" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K75" s="18"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B76" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000075</v>
+      </c>
+      <c r="C76" s="3" t="str">
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+      </c>
+      <c r="D76" s="3" t="str">
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>General Journal Summary</v>
+      </c>
+      <c r="F76" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000075</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J76" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>GeneralJournalSummary</v>
+      </c>
+      <c r="K76" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B77" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000076</v>
+      </c>
+      <c r="C77" s="3" t="str">
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="D77" s="3" t="str">
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Reimbursement</v>
+      </c>
+      <c r="F77" s="17">
+        <f t="shared" si="7"/>
+        <v>97000000000076</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J77" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K77" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B78" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000077</v>
+      </c>
+      <c r="C78" s="3" t="str">
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="D78" s="3" t="str">
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="F78" s="17">
+        <f t="shared" ref="F78:F98" si="11">IF(EXACT(B78, ""), F77, B78)</f>
+        <v>97000000000077</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J78" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ReimbursementSummary</v>
+      </c>
+      <c r="K78" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B79" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000078</v>
+      </c>
+      <c r="C79" s="3" t="str">
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="D79" s="3" t="str">
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Reimbursement to Debit Note</v>
+      </c>
+      <c r="F79" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000078</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J79" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>ReimbursementtoDebitNote</v>
+      </c>
+      <c r="K79" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B80" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000079</v>
+      </c>
+      <c r="C80" s="3" t="str">
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
+      </c>
+      <c r="D80" s="3" t="str">
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Debit Note</v>
+      </c>
+      <c r="F80" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000079</v>
+      </c>
+      <c r="H80" s="4"/>
+      <c r="I80" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J80" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B81" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000080</v>
+      </c>
+      <c r="C81" s="3" t="str">
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+      </c>
+      <c r="D81" s="3" t="str">
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Debit Note Summary</v>
+      </c>
+      <c r="F81" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000080</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J81" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>DebitNoteSummary</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B82" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000081</v>
+      </c>
+      <c r="C82" s="3" t="str">
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
+      </c>
+      <c r="D82" s="3" t="str">
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Credit Note</v>
+      </c>
+      <c r="F82" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000081</v>
+      </c>
+      <c r="H82" s="4"/>
+      <c r="I82" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J82" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B83" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000082</v>
+      </c>
+      <c r="C83" s="3" t="str">
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+      </c>
+      <c r="D83" s="3" t="str">
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Credit Note Summary</v>
+      </c>
+      <c r="F83" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000082</v>
+      </c>
+      <c r="H83" s="4"/>
+      <c r="I83" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J83" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>CreditNoteSummary</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B84" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000083</v>
+      </c>
+      <c r="C84" s="3" t="str">
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Transaction</v>
+      </c>
+      <c r="D84" s="3" t="str">
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Loan</v>
+      </c>
+      <c r="F84" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000083</v>
+      </c>
+      <c r="H84" s="4"/>
+      <c r="I84" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J84" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K84" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000084</v>
+      </c>
+      <c r="C85" s="3" t="str">
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      </c>
+      <c r="D85" s="3" t="str">
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Loan Summary</v>
+      </c>
+      <c r="F85" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000084</v>
+      </c>
+      <c r="H85" s="4"/>
+      <c r="I85" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J85" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>LoanSummary</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B86" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000085</v>
+      </c>
+      <c r="C86" s="3" t="str">
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D86" s="3" t="str">
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Loan to Loan Settlement</v>
+      </c>
+      <c r="F86" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000085</v>
+      </c>
+      <c r="H86" s="4"/>
+      <c r="I86" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J86" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>LoantoLoanSettlement</v>
+      </c>
+      <c r="K86" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B87" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000086</v>
+      </c>
+      <c r="C87" s="3" t="str">
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="D87" s="3" t="str">
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="F87" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000086</v>
+      </c>
+      <c r="H87" s="4"/>
+      <c r="I87" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J87" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B88" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000087</v>
+      </c>
+      <c r="C88" s="3" t="str">
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D88" s="3" t="str">
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="F88" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000087</v>
+      </c>
+      <c r="H88" s="4"/>
+      <c r="I88" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J88" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>LoanSettlementSummary</v>
+      </c>
+      <c r="K88" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B89" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000088</v>
+      </c>
+      <c r="C89" s="3" t="str">
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
+      </c>
+      <c r="D89" s="3" t="str">
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Cash &amp; Bank</v>
+      </c>
+      <c r="F89" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000088</v>
+      </c>
+      <c r="H89" s="4"/>
+      <c r="I89" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J89" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>Execute</v>
+      </c>
+      <c r="K89" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B90" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000089</v>
+      </c>
+      <c r="C90" s="3" t="str">
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>Module.Finance.Data.CashBank.Report.DataList</v>
       </c>
-      <c r="D61" s="3" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Cash &amp; Bank Report</v>
-      </c>
-      <c r="F61" s="18">
-        <f t="shared" si="0"/>
-        <v>97000000000060</v>
-      </c>
-      <c r="H61" s="4" t="str">
-        <f>D61</f>
-        <v>Cash &amp; Bank Report</v>
-      </c>
-      <c r="I61" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Cash &amp; Bank Report</v>
-      </c>
-      <c r="J61" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Cash&amp;BankReport</v>
-      </c>
-      <c r="K61" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M61" s="6">
-        <f t="shared" si="5"/>
-        <v>256000000000060</v>
-      </c>
-      <c r="O61" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000060, 'Cash&amp;BankReport', 'Cash &amp; Bank Report', 'ReportPaymentJournal');</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="7">
-        <f t="shared" si="1"/>
-        <v>97000000000061</v>
-      </c>
-      <c r="C62" s="2" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+      <c r="D90" s="3" t="str">
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Cash &amp; Bank Summary</v>
+      </c>
+      <c r="F90" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000089</v>
+      </c>
+      <c r="H90" s="4"/>
+      <c r="I90" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J90" s="3" t="str">
+        <f>IF(EXACT(F90, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C90)), D90, IF(EXACT(H90, ""), "Execute", H90)), " ", ""), "&amp;", "")
+)</f>
+        <v>CashBankSummary</v>
+      </c>
+      <c r="K90" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B91" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000090</v>
+      </c>
+      <c r="C91" s="3" t="str">
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
       </c>
-      <c r="D62" s="3" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
+      <c r="D91" s="3" t="str">
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
         <v>Account Payable</v>
       </c>
-      <c r="F62" s="18">
-        <f t="shared" si="0"/>
-        <v>97000000000061</v>
-      </c>
-      <c r="H62" s="4"/>
-      <c r="I62" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Execute</v>
-      </c>
-      <c r="J62" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>Execute</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M62" s="6">
-        <f t="shared" si="5"/>
-        <v>256000000000061</v>
-      </c>
-      <c r="O62" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000061, 'Execute', 'Execute', 'AccountPayable?var=1');</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="9">
-        <f t="shared" si="1"/>
-        <v>97000000000062</v>
-      </c>
-      <c r="C63" s="10" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
+      <c r="F91" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000090</v>
+      </c>
+      <c r="H91" s="4"/>
+      <c r="I91" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J91" s="3" t="str">
+        <f t="shared" ref="J91:J98" si="12">IF(EXACT(F91, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C91)), D91, IF(EXACT(H91, ""), "Execute", H91)), " ", ""), "&amp;", "")
+)</f>
+        <v>Execute</v>
+      </c>
+      <c r="K91" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B92" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000091</v>
+      </c>
+      <c r="C92" s="3" t="str">
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
         <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
       </c>
-      <c r="D63" s="11" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
+      <c r="D92" s="3" t="str">
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
         <v>Account Payable Summary</v>
       </c>
-      <c r="F63" s="22">
-        <f t="shared" si="0"/>
-        <v>97000000000062</v>
-      </c>
-      <c r="H63" s="15" t="str">
-        <f>D63</f>
-        <v>Account Payable Summary</v>
-      </c>
-      <c r="I63" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>Account Payable Summary</v>
-      </c>
-      <c r="J63" s="11" t="str">
-        <f t="shared" si="3"/>
+      <c r="F92" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000091</v>
+      </c>
+      <c r="H92" s="4"/>
+      <c r="I92" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J92" s="3" t="str">
+        <f t="shared" si="12"/>
         <v>AccountPayableSummary</v>
       </c>
-      <c r="K63" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="M63" s="6">
-        <f t="shared" si="5"/>
-        <v>256000000000062</v>
-      </c>
-      <c r="O63" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000062, 'AccountPayableSummary', 'Account Payable Summary', 'ReportAccountPayableSummary');</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="7">
-        <f t="shared" si="1"/>
-        <v>97000000000063</v>
-      </c>
-      <c r="C64" s="2" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1086, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
-      </c>
-      <c r="D64" s="3" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1086, 3, FALSE)</f>
-        <v>Purchase Order to Account Payable</v>
-      </c>
-      <c r="F64" s="18">
-        <f t="shared" si="0"/>
-        <v>97000000000063</v>
-      </c>
-      <c r="H64" s="4" t="str">
-        <f>D64</f>
-        <v>Purchase Order to Account Payable</v>
-      </c>
-      <c r="I64" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>Purchase Order to Account Payable</v>
-      </c>
-      <c r="J64" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>PurchaseOrdertoAccountPayable</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="M64" s="6">
-        <f t="shared" si="5"/>
-        <v>256000000000063</v>
-      </c>
-      <c r="O64" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000063, 'PurchaseOrdertoAccountPayable', 'Purchase Order to Account Payable', 'ReportPOtoAP');</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="9"/>
+      <c r="K92" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B93" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000092</v>
+      </c>
+      <c r="C93" s="3" t="str">
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+      </c>
+      <c r="D93" s="3" t="str">
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="F93" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000092</v>
+      </c>
+      <c r="H93" s="4"/>
+      <c r="I93" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J93" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>Execute</v>
+      </c>
+      <c r="K93" s="18"/>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B94" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000093</v>
+      </c>
+      <c r="C94" s="3" t="str">
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+      </c>
+      <c r="D94" s="3" t="str">
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="F94" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000093</v>
+      </c>
+      <c r="H94" s="4"/>
+      <c r="I94" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J94" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>SalesInvoiceSummary</v>
+      </c>
+      <c r="K94" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B95" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000094</v>
+      </c>
+      <c r="C95" s="3" t="str">
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+      </c>
+      <c r="D95" s="3" t="str">
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="F95" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000094</v>
+      </c>
+      <c r="H95" s="4"/>
+      <c r="I95" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J95" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>SalesInvoicetoCreditNote</v>
+      </c>
+      <c r="K95" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B96" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000095</v>
+      </c>
+      <c r="C96" s="3" t="str">
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="D96" s="3" t="str">
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="F96" s="17">
+        <f t="shared" si="11"/>
+        <v>97000000000095</v>
+      </c>
+      <c r="H96" s="4"/>
+      <c r="I96" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J96" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>Execute</v>
+      </c>
+      <c r="K96" s="18"/>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B97" s="7">
+        <f t="shared" si="10"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="C97" s="11" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="D97" s="11" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="F97" s="20">
+        <f t="shared" si="11"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="H97" s="14"/>
+      <c r="I97" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J97" s="11" t="str">
+        <f t="shared" si="12"/>
+        <v>TaxReconciliationSummary</v>
+      </c>
+      <c r="K97" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B98" s="9">
+        <f t="shared" si="10"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="C98" s="22" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="D98" s="22" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <v>Customer</v>
+      </c>
+      <c r="F98" s="23">
+        <f t="shared" si="11"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="H98" s="26"/>
+      <c r="I98" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J98" s="22" t="str">
+        <f t="shared" si="12"/>
+        <v>Execute</v>
+      </c>
+      <c r="K98" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
@@ -1802,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:O98"/>
+  <dimension ref="B1:Q98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
@@ -1821,7 +1821,7 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B2" s="7">
         <f>IF(ISNUMBER(B1), B1+1, 97000000000001)</f>
         <v>97000000000001</v>
@@ -1859,7 +1859,7 @@
         <v>Login</v>
       </c>
       <c r="F2" s="17">
-        <f t="shared" ref="F2:F65" si="0">IF(EXACT(B2, ""), F1, B2)</f>
+        <f t="shared" ref="F2:F13" si="0">IF(EXACT(B2, ""), F1, B2)</f>
         <v>97000000000001</v>
       </c>
       <c r="H2" s="4"/>
@@ -1884,8 +1884,27 @@
         <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F2, ""), "null", CONCATENATE($F2)), ", ", IF(EXACT($F2, ""),"null", CONCATENATE("'", $J2, "'")), ", ", IF(EXACT($F2, ""), "null", CONCATENATE("'", $I2, "'")), ", ", IF(EXACT($K2, ""), "null", CONCATENATE("'", $K2, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000001, 'Execute', 'Execute', 'login');</v>
       </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q2" s="1" t="str">
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'menu_RefID', ", IF(EXACT($F2, ""), "null", CONCATENATE("'", SUBSTITUTE($F2, "'", "\'"), "'")), "::varchar,",
+"'key', ", IF(EXACT($J2, ""), "null", CONCATENATE("'", SUBSTITUTE($J2, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($I2, ""), "null", CONCATENATE("'", SUBSTITUTE($I2, "'", "\'"), "'")), "::varchar,",
+"'URLPath', ", IF(EXACT($K2, ""), "null", CONCATENATE("'", SUBSTITUTE($K2, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000001'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'login'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
         <f t="shared" ref="B3:B66" si="2">IF(ISNUMBER(B2), B2+1, 97000000000001)</f>
         <v>97000000000002</v>
@@ -1904,7 +1923,7 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I65" si="3">IF(EXACT(F3, ""), "", IF(EXACT(H3, ""), "Execute", H3))</f>
+        <f t="shared" ref="I3:I64" si="3">IF(EXACT(F3, ""), "", IF(EXACT(H3, ""), "Execute", H3))</f>
         <v>Execute</v>
       </c>
       <c r="J3" s="3" t="str">
@@ -1919,11 +1938,30 @@
         <v>256000000000002</v>
       </c>
       <c r="O3" s="15" t="str">
-        <f t="shared" ref="O3:O65" si="4">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F3, ""), "null", CONCATENATE($F3)), ", ", IF(EXACT($F3, ""),"null", CONCATENATE("'", $J3, "'")), ", ", IF(EXACT($F3, ""), "null", CONCATENATE("'", $I3, "'")), ", ", IF(EXACT($K3, ""), "null", CONCATENATE("'", $K3, "'")), ");")</f>
+        <f t="shared" ref="O3:O66" si="4">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F3, ""), "null", CONCATENATE($F3)), ", ", IF(EXACT($F3, ""),"null", CONCATENATE("'", $J3, "'")), ", ", IF(EXACT($F3, ""), "null", CONCATENATE("'", $I3, "'")), ", ", IF(EXACT($K3, ""), "null", CONCATENATE("'", $K3, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000002, 'Execute', 'Execute', 'logout');</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q3" s="1" t="str">
+        <f t="shared" ref="Q3:Q66" si="5">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'menu_RefID', ", IF(EXACT($F3, ""), "null", CONCATENATE("'", SUBSTITUTE($F3, "'", "\'"), "'")), "::varchar,",
+"'key', ", IF(EXACT($J3, ""), "null", CONCATENATE("'", SUBSTITUTE($J3, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($I3, ""), "null", CONCATENATE("'", SUBSTITUTE($I3, "'", "\'"), "'")), "::varchar,",
+"'URLPath', ", IF(EXACT($K3, ""), "null", CONCATENATE("'", SUBSTITUTE($K3, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000002'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'logout'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B4" s="9">
         <f t="shared" si="2"/>
         <v>97000000000003</v>
@@ -1951,15 +1989,19 @@
       </c>
       <c r="K4" s="19"/>
       <c r="M4" s="6">
-        <f t="shared" ref="M4:M65" si="5">IF(ISNUMBER(M3), M3+1, 256000000000001)</f>
+        <f t="shared" ref="M4:M67" si="6">IF(ISNUMBER(M3), M3+1, 256000000000001)</f>
         <v>256000000000003</v>
       </c>
       <c r="O4" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000003, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q4" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000003'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B5" s="12">
         <f t="shared" si="2"/>
         <v>97000000000004</v>
@@ -1978,7 +2020,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="3" t="str">
-        <f t="shared" ref="I5" si="6">IF(EXACT(F5, ""), "", IF(EXACT(H5, ""), "Execute", H5))</f>
+        <f t="shared" ref="I5" si="7">IF(EXACT(F5, ""), "", IF(EXACT(H5, ""), "Execute", H5))</f>
         <v>Execute</v>
       </c>
       <c r="J5" s="3" t="str">
@@ -1989,15 +2031,19 @@
         <v>47</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000004</v>
       </c>
       <c r="O5" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000004, 'Execute', 'Execute', 'dashboard?var=1');</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q5" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000004'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'dashboard?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <f t="shared" si="2"/>
         <v>97000000000005</v>
@@ -2027,15 +2073,19 @@
         <v>46</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000005</v>
       </c>
       <c r="O6" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000005, 'Execute', 'Execute', 'CheckDocument?var=1');</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q6" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000005'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CheckDocument?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <f t="shared" si="2"/>
         <v>97000000000006</v>
@@ -2065,15 +2115,19 @@
         <v>48</v>
       </c>
       <c r="M7" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000006</v>
       </c>
       <c r="O7" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000006, 'Execute', 'Execute', 'MyDocument?var=1');</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q7" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000006'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MyDocument?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" s="9">
         <f t="shared" si="2"/>
         <v>97000000000007</v>
@@ -2101,15 +2155,19 @@
       </c>
       <c r="K8" s="19"/>
       <c r="M8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000007</v>
       </c>
       <c r="O8" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000007, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q8" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000007'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="12">
         <f t="shared" si="2"/>
         <v>97000000000008</v>
@@ -2138,15 +2196,19 @@
       </c>
       <c r="K9" s="25"/>
       <c r="M9" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000008</v>
       </c>
       <c r="O9" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000008, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q9" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000008'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <f t="shared" si="2"/>
         <v>97000000000009</v>
@@ -2175,15 +2237,19 @@
       </c>
       <c r="K10" s="18"/>
       <c r="M10" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000009</v>
       </c>
       <c r="O10" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000009, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q10" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000009'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <f t="shared" si="2"/>
         <v>97000000000010</v>
@@ -2212,15 +2278,19 @@
       </c>
       <c r="K11" s="18"/>
       <c r="M11" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000010</v>
       </c>
       <c r="O11" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000010, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q11" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000010'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <f t="shared" si="2"/>
         <v>97000000000011</v>
@@ -2248,15 +2318,20 @@
       </c>
       <c r="K12" s="18"/>
       <c r="M12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000011</v>
       </c>
       <c r="O12" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000011, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="13" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000011'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="7">
         <f t="shared" si="2"/>
         <v>97000000000012</v>
@@ -2284,15 +2359,20 @@
       </c>
       <c r="K13" s="18"/>
       <c r="M13" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000012</v>
       </c>
       <c r="O13" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000012, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="14" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000012'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="7">
         <f t="shared" si="2"/>
         <v>97000000000013</v>
@@ -2306,7 +2386,7 @@
         <v>Business Document Type</v>
       </c>
       <c r="F14" s="17">
-        <f t="shared" ref="F14:F77" si="7">IF(EXACT(B14, ""), F13, B14)</f>
+        <f t="shared" ref="F14:F77" si="8">IF(EXACT(B14, ""), F13, B14)</f>
         <v>97000000000013</v>
       </c>
       <c r="H14" s="4"/>
@@ -2320,15 +2400,20 @@
       </c>
       <c r="K14" s="18"/>
       <c r="M14" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000013</v>
       </c>
       <c r="O14" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000013, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="15" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000013'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="7">
         <f t="shared" si="2"/>
         <v>97000000000014</v>
@@ -2342,7 +2427,7 @@
         <v>Business Document</v>
       </c>
       <c r="F15" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000014</v>
       </c>
       <c r="H15" s="4"/>
@@ -2356,15 +2441,20 @@
       </c>
       <c r="K15" s="18"/>
       <c r="M15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000014</v>
       </c>
       <c r="O15" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000014, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="16" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000014'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="7">
         <f t="shared" si="2"/>
         <v>97000000000015</v>
@@ -2378,7 +2468,7 @@
         <v>Business Document Version</v>
       </c>
       <c r="F16" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000015</v>
       </c>
       <c r="H16" s="4"/>
@@ -2392,15 +2482,20 @@
       </c>
       <c r="K16" s="18"/>
       <c r="M16" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000015</v>
       </c>
       <c r="O16" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000015, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="17" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000015'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="7">
         <f t="shared" si="2"/>
         <v>97000000000016</v>
@@ -2414,7 +2509,7 @@
         <v>Menu Management</v>
       </c>
       <c r="F17" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000016</v>
       </c>
       <c r="H17" s="4"/>
@@ -2428,15 +2523,20 @@
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000016</v>
       </c>
       <c r="O17" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000016, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="18" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000016'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7">
         <f t="shared" si="2"/>
         <v>97000000000017</v>
@@ -2450,7 +2550,7 @@
         <v>Privilege Menu</v>
       </c>
       <c r="F18" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000017</v>
       </c>
       <c r="H18" s="4"/>
@@ -2464,15 +2564,20 @@
       </c>
       <c r="K18" s="18"/>
       <c r="M18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000017</v>
       </c>
       <c r="O18" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000017, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="19" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000017'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="9">
         <f t="shared" si="2"/>
         <v>97000000000018</v>
@@ -2486,7 +2591,7 @@
         <v>Workflow</v>
       </c>
       <c r="F19" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000018</v>
       </c>
       <c r="H19" s="14"/>
@@ -2500,15 +2605,20 @@
       </c>
       <c r="K19" s="19"/>
       <c r="M19" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000018</v>
       </c>
       <c r="O19" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000018, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="20" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000018'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7">
         <f t="shared" si="2"/>
         <v>97000000000019</v>
@@ -2522,7 +2632,7 @@
         <v>Budget</v>
       </c>
       <c r="F20" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000019</v>
       </c>
       <c r="H20" s="4"/>
@@ -2536,15 +2646,20 @@
       </c>
       <c r="K20" s="18"/>
       <c r="M20" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000019</v>
       </c>
       <c r="O20" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000019, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="21" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000019'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="7">
         <f t="shared" si="2"/>
         <v>97000000000020</v>
@@ -2558,7 +2673,7 @@
         <v>Sub Budget</v>
       </c>
       <c r="F21" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000020</v>
       </c>
       <c r="H21" s="4"/>
@@ -2572,15 +2687,20 @@
       </c>
       <c r="K21" s="18"/>
       <c r="M21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000020</v>
       </c>
       <c r="O21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000020, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="22" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000020'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="7">
         <f t="shared" si="2"/>
         <v>97000000000021</v>
@@ -2594,7 +2714,7 @@
         <v>Modify Budget</v>
       </c>
       <c r="F22" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000021</v>
       </c>
       <c r="H22" s="4"/>
@@ -2610,15 +2730,20 @@
         <v>49</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000021</v>
       </c>
       <c r="O22" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000021, 'Execute', 'Execute', 'ModifyBudget?var=1');</v>
       </c>
-    </row>
-    <row r="23" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000021'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ModifyBudget?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="7">
         <f t="shared" si="2"/>
         <v>97000000000022</v>
@@ -2632,7 +2757,7 @@
         <v>Report Modify Budget Summary</v>
       </c>
       <c r="F23" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000022</v>
       </c>
       <c r="H23" s="4" t="str">
@@ -2651,15 +2776,20 @@
         <v>9</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000022</v>
       </c>
       <c r="O23" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000022, 'ReportModifyBudgetSummary', 'Report Modify Budget Summary', 'ReportModifyBudgetSummary');</v>
       </c>
-    </row>
-    <row r="24" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000022'::varchar,'key', 'ReportModifyBudgetSummary'::varchar,'caption', 'Report Modify Budget Summary'::varchar,'URLPath', 'ReportModifyBudgetSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="7">
         <f t="shared" si="2"/>
         <v>97000000000023</v>
@@ -2673,7 +2803,7 @@
         <v>Work</v>
       </c>
       <c r="F24" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000023</v>
       </c>
       <c r="H24" s="4"/>
@@ -2687,15 +2817,20 @@
       </c>
       <c r="K24" s="18"/>
       <c r="M24" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000023</v>
       </c>
       <c r="O24" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000023, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="25" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000023'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="9">
         <f t="shared" si="2"/>
         <v>97000000000024</v>
@@ -2709,7 +2844,7 @@
         <v>Report Cost Financial Structure</v>
       </c>
       <c r="F25" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000024</v>
       </c>
       <c r="H25" s="14" t="s">
@@ -2725,15 +2860,20 @@
       </c>
       <c r="K25" s="19"/>
       <c r="M25" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000024</v>
       </c>
       <c r="O25" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000024, 'ReportCostFinancialStructure', 'Report Modify Budget Summary', null);</v>
       </c>
-    </row>
-    <row r="26" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000024'::varchar,'key', 'ReportCostFinancialStructure'::varchar,'caption', 'Report Modify Budget Summary'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="7">
         <f t="shared" si="2"/>
         <v>97000000000025</v>
@@ -2747,7 +2887,7 @@
         <v>Blood Aglutinogen Type</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000025</v>
       </c>
       <c r="H26" s="4"/>
@@ -2761,15 +2901,20 @@
       </c>
       <c r="K26" s="18"/>
       <c r="M26" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000025</v>
       </c>
       <c r="O26" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000025, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000025'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="7">
         <f t="shared" si="2"/>
         <v>97000000000026</v>
@@ -2783,7 +2928,7 @@
         <v>Person</v>
       </c>
       <c r="F27" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000026</v>
       </c>
       <c r="H27" s="4"/>
@@ -2797,15 +2942,20 @@
       </c>
       <c r="K27" s="18"/>
       <c r="M27" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000026</v>
       </c>
       <c r="O27" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000026, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="28" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000026'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="7">
         <f t="shared" si="2"/>
         <v>97000000000027</v>
@@ -2819,7 +2969,7 @@
         <v>Religion</v>
       </c>
       <c r="F28" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000027</v>
       </c>
       <c r="H28" s="4"/>
@@ -2833,15 +2983,20 @@
       </c>
       <c r="K28" s="18"/>
       <c r="M28" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000027</v>
       </c>
       <c r="O28" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000027, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="29" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000027'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="7">
         <f t="shared" si="2"/>
         <v>97000000000028</v>
@@ -2855,7 +3010,7 @@
         <v>Role</v>
       </c>
       <c r="F29" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000028</v>
       </c>
       <c r="H29" s="4"/>
@@ -2869,15 +3024,20 @@
       </c>
       <c r="K29" s="18"/>
       <c r="M29" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000028</v>
       </c>
       <c r="O29" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000028, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="30" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000028'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="7">
         <f t="shared" si="2"/>
         <v>97000000000029</v>
@@ -2891,7 +3051,7 @@
         <v>Department</v>
       </c>
       <c r="F30" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000029</v>
       </c>
       <c r="H30" s="4"/>
@@ -2905,15 +3065,20 @@
       </c>
       <c r="K30" s="18"/>
       <c r="M30" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000029</v>
       </c>
       <c r="O30" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000029, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="31" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000029'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="7">
         <f t="shared" si="2"/>
         <v>97000000000030</v>
@@ -2927,7 +3092,7 @@
         <v>Person Work Time Sheet</v>
       </c>
       <c r="F31" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000030</v>
       </c>
       <c r="H31" s="4"/>
@@ -2941,15 +3106,20 @@
       </c>
       <c r="K31" s="18"/>
       <c r="M31" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000030</v>
       </c>
       <c r="O31" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000030, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="32" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000030'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7">
         <f t="shared" si="2"/>
         <v>97000000000031</v>
@@ -2963,7 +3133,7 @@
         <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000031</v>
       </c>
       <c r="H32" s="4"/>
@@ -2979,15 +3149,20 @@
         <v>54</v>
       </c>
       <c r="M32" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000031</v>
       </c>
       <c r="O32" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000031, 'PersonWorkTimeSheetSummary', 'Execute', 'ReportTimesheetSummary');</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000031'::varchar,'key', 'PersonWorkTimeSheetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTimesheetSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="7">
         <f t="shared" si="2"/>
         <v>97000000000032</v>
@@ -3001,7 +3176,7 @@
         <v>Sallary Allocation</v>
       </c>
       <c r="F33" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000032</v>
       </c>
       <c r="H33" s="4"/>
@@ -3015,15 +3190,20 @@
       </c>
       <c r="K33" s="18"/>
       <c r="M33" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000032</v>
       </c>
       <c r="O33" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000032, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000032'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="9">
         <f t="shared" si="2"/>
         <v>97000000000033</v>
@@ -3037,7 +3217,7 @@
         <v>Sallary Allocation Summary</v>
       </c>
       <c r="F34" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000033</v>
       </c>
       <c r="H34" s="14"/>
@@ -3051,15 +3231,20 @@
       </c>
       <c r="K34" s="19"/>
       <c r="M34" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000033</v>
       </c>
       <c r="O34" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000033, 'SallaryAllocationSummary', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000033'::varchar,'key', 'SallaryAllocationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="7">
         <f t="shared" si="2"/>
         <v>97000000000034</v>
@@ -3073,7 +3258,7 @@
         <v>Warehouse</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000034</v>
       </c>
       <c r="H35" s="4"/>
@@ -3087,15 +3272,20 @@
       </c>
       <c r="K35" s="18"/>
       <c r="M35" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000034</v>
       </c>
       <c r="O35" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000034, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="36" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000034'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="7">
         <f t="shared" si="2"/>
         <v>97000000000035</v>
@@ -3109,7 +3299,7 @@
         <v>Product Type</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000035</v>
       </c>
       <c r="H36" s="4"/>
@@ -3123,15 +3313,20 @@
       </c>
       <c r="K36" s="18"/>
       <c r="M36" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000035</v>
       </c>
       <c r="O36" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000035, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000035'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="7">
         <f t="shared" si="2"/>
         <v>97000000000036</v>
@@ -3145,7 +3340,7 @@
         <v>Product</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000036</v>
       </c>
       <c r="H37" s="4"/>
@@ -3159,15 +3354,20 @@
       </c>
       <c r="K37" s="18"/>
       <c r="M37" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000036</v>
       </c>
       <c r="O37" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000036, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="38" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000036'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="7">
         <f t="shared" si="2"/>
         <v>97000000000037</v>
@@ -3181,7 +3381,7 @@
         <v>Delivery Order</v>
       </c>
       <c r="F38" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000037</v>
       </c>
       <c r="H38" s="4"/>
@@ -3197,15 +3397,20 @@
         <v>11</v>
       </c>
       <c r="M38" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000037</v>
       </c>
       <c r="O38" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000037, 'Execute', 'Execute', 'DeliveryOrder?var=1');</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000037'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'DeliveryOrder?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="7">
         <f t="shared" si="2"/>
         <v>97000000000038</v>
@@ -3219,7 +3424,7 @@
         <v>Report DO Summary</v>
       </c>
       <c r="F39" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000038</v>
       </c>
       <c r="H39" s="4"/>
@@ -3235,15 +3440,20 @@
         <v>10</v>
       </c>
       <c r="M39" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000038</v>
       </c>
       <c r="O39" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000038, 'ReportDOSummary', 'Execute', 'ReportDOSummary');</v>
       </c>
-    </row>
-    <row r="40" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000038'::varchar,'key', 'ReportDOSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDOSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="7">
         <f t="shared" si="2"/>
         <v>97000000000039</v>
@@ -3257,7 +3467,7 @@
         <v>Report DO to Material Receive</v>
       </c>
       <c r="F40" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000039</v>
       </c>
       <c r="H40" s="4"/>
@@ -3273,15 +3483,20 @@
         <v>56</v>
       </c>
       <c r="M40" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000039</v>
       </c>
       <c r="O40" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000039, 'ReportDOtoMaterialReceive', 'Execute', 'ReportDoToMaterialReceive');</v>
       </c>
-    </row>
-    <row r="41" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000039'::varchar,'key', 'ReportDOtoMaterialReceive'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDoToMaterialReceive'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="7">
         <f t="shared" si="2"/>
         <v>97000000000040</v>
@@ -3295,7 +3510,7 @@
         <v>Material Receive</v>
       </c>
       <c r="F41" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000040</v>
       </c>
       <c r="H41" s="4"/>
@@ -3311,15 +3526,20 @@
         <v>12</v>
       </c>
       <c r="M41" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000040</v>
       </c>
       <c r="O41" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000040, 'Execute', 'Execute', 'MaterialReceive?var=1');</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000040'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReceive?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7">
         <f t="shared" si="2"/>
         <v>97000000000041</v>
@@ -3333,7 +3553,7 @@
         <v>Report Material Receive Summary</v>
       </c>
       <c r="F42" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000041</v>
       </c>
       <c r="H42" s="4"/>
@@ -3349,15 +3569,20 @@
         <v>55</v>
       </c>
       <c r="M42" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000041</v>
       </c>
       <c r="O42" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000041, 'ReportMaterialReceiveSummary', 'Execute', 'ReportMaterialReceiveSummary');</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000041'::varchar,'key', 'ReportMaterialReceiveSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMaterialReceiveSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="7">
         <f t="shared" si="2"/>
         <v>97000000000042</v>
@@ -3371,7 +3596,7 @@
         <v>Report Material Receive to Material Return</v>
       </c>
       <c r="F43" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000042</v>
       </c>
       <c r="H43" s="4"/>
@@ -3387,15 +3612,20 @@
         <v>57</v>
       </c>
       <c r="M43" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000042</v>
       </c>
       <c r="O43" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000042, 'ReportMaterialReceivetoMaterialReturn', 'Execute', 'ReportMatReceivetoMatReturn');</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000042'::varchar,'key', 'ReportMaterialReceivetoMaterialReturn'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMatReceivetoMatReturn'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="7">
         <f t="shared" si="2"/>
         <v>97000000000043</v>
@@ -3409,7 +3639,7 @@
         <v>Material Return</v>
       </c>
       <c r="F44" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000043</v>
       </c>
       <c r="H44" s="4"/>
@@ -3425,15 +3655,20 @@
         <v>14</v>
       </c>
       <c r="M44" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000043</v>
       </c>
       <c r="O44" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000043, 'Execute', 'Execute', 'MaterialReturn?var=1');</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000043'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReturn?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9">
         <f t="shared" si="2"/>
         <v>97000000000044</v>
@@ -3447,7 +3682,7 @@
         <v>Report Material Return Summary</v>
       </c>
       <c r="F45" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000044</v>
       </c>
       <c r="H45" s="14"/>
@@ -3463,15 +3698,20 @@
         <v>13</v>
       </c>
       <c r="M45" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000044</v>
       </c>
       <c r="O45" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000044, 'ReportMaterialReturnSummary', 'Execute', 'ReportMatReturnSummary');</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000044'::varchar,'key', 'ReportMaterialReturnSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMatReturnSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="7">
         <f t="shared" si="2"/>
         <v>97000000000045</v>
@@ -3485,7 +3725,7 @@
         <v>Advance Request</v>
       </c>
       <c r="F46" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000045</v>
       </c>
       <c r="H46" s="4"/>
@@ -3501,15 +3741,20 @@
         <v>16</v>
       </c>
       <c r="M46" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000045</v>
       </c>
       <c r="O46" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000045, 'Execute', 'Execute', 'AdvanceRequest?var=1');</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000045'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceRequest?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="7">
         <f t="shared" si="2"/>
         <v>97000000000046</v>
@@ -3523,7 +3768,7 @@
         <v>Report Advance Summary</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000046</v>
       </c>
       <c r="H47" s="4"/>
@@ -3539,15 +3784,20 @@
         <v>15</v>
       </c>
       <c r="M47" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000046</v>
       </c>
       <c r="O47" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000046, 'ReportAdvanceSummary', 'Execute', 'ReportAdvanceSummary');</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000046'::varchar,'key', 'ReportAdvanceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="7">
         <f t="shared" si="2"/>
         <v>97000000000047</v>
@@ -3561,7 +3811,7 @@
         <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="F48" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000047</v>
       </c>
       <c r="H48" s="4"/>
@@ -3577,15 +3827,20 @@
         <v>58</v>
       </c>
       <c r="M48" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000047</v>
       </c>
       <c r="O48" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000047, 'ReportAdvancetoAdvanceSettlement', 'Execute', 'ReportAdvanceToASF');</v>
       </c>
-    </row>
-    <row r="49" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000047'::varchar,'key', 'ReportAdvancetoAdvanceSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceToASF'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="7">
         <f t="shared" si="2"/>
         <v>97000000000048</v>
@@ -3599,7 +3854,7 @@
         <v>AdvanceSettlement</v>
       </c>
       <c r="F49" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000048</v>
       </c>
       <c r="H49" s="4"/>
@@ -3615,15 +3870,20 @@
         <v>18</v>
       </c>
       <c r="M49" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000048</v>
       </c>
       <c r="O49" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000048, 'Execute', 'Execute', 'AdvanceSettlement?var=1');</v>
       </c>
-    </row>
-    <row r="50" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000048'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceSettlement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="7">
         <f t="shared" si="2"/>
         <v>97000000000049</v>
@@ -3637,7 +3897,7 @@
         <v>Report Advance Settlement Summary</v>
       </c>
       <c r="F50" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000049</v>
       </c>
       <c r="H50" s="4"/>
@@ -3653,15 +3913,20 @@
         <v>17</v>
       </c>
       <c r="M50" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000049</v>
       </c>
       <c r="O50" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000049, 'ReportAdvanceSettlementSummary', 'Execute', 'ReportAdvanceSettlementSummary');</v>
       </c>
-    </row>
-    <row r="51" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000049'::varchar,'key', 'ReportAdvanceSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSettlementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="7">
         <f t="shared" si="2"/>
         <v>97000000000050</v>
@@ -3675,7 +3940,7 @@
         <v>BusinessTrip Request</v>
       </c>
       <c r="F51" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000050</v>
       </c>
       <c r="H51" s="4"/>
@@ -3691,15 +3956,20 @@
         <v>22</v>
       </c>
       <c r="M51" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000050</v>
       </c>
       <c r="O51" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000050, 'Execute', 'Execute', 'BusinessTripRequest?var=1');</v>
       </c>
-    </row>
-    <row r="52" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000050'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripRequest?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="7">
         <f t="shared" si="2"/>
         <v>97000000000051</v>
@@ -3713,7 +3983,7 @@
         <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="F52" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000051</v>
       </c>
       <c r="H52" s="4"/>
@@ -3729,15 +3999,20 @@
         <v>21</v>
       </c>
       <c r="M52" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000051</v>
       </c>
       <c r="O52" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000051, 'ReportBusinessTripRequestSummary', 'Execute', 'ReportBusinessTripRequestSummary');</v>
       </c>
-    </row>
-    <row r="53" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000051'::varchar,'key', 'ReportBusinessTripRequestSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripRequestSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="7">
         <f t="shared" si="2"/>
         <v>97000000000052</v>
@@ -3751,7 +4026,7 @@
         <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="F53" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000052</v>
       </c>
       <c r="H53" s="4"/>
@@ -3767,15 +4042,20 @@
         <v>59</v>
       </c>
       <c r="M53" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000052</v>
       </c>
       <c r="O53" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000052, 'ReportBusinessTriptoBusinessTripSettlement', 'Execute', 'ReportBusinessTripToBSF');</v>
       </c>
-    </row>
-    <row r="54" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000052'::varchar,'key', 'ReportBusinessTriptoBusinessTripSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripToBSF'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="7">
         <f t="shared" si="2"/>
         <v>97000000000053</v>
@@ -3789,7 +4069,7 @@
         <v>BusinessTrip Settlement</v>
       </c>
       <c r="F54" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000053</v>
       </c>
       <c r="H54" s="4"/>
@@ -3805,15 +4085,20 @@
         <v>20</v>
       </c>
       <c r="M54" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000053</v>
       </c>
       <c r="O54" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000053, 'Execute', 'Execute', 'BusinessTripSettlement?var=1');</v>
       </c>
-    </row>
-    <row r="55" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000053'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripSettlement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="9">
         <f t="shared" si="2"/>
         <v>97000000000054</v>
@@ -3827,7 +4112,7 @@
         <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="F55" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000054</v>
       </c>
       <c r="H55" s="14"/>
@@ -3843,15 +4128,20 @@
         <v>19</v>
       </c>
       <c r="M55" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000054</v>
       </c>
       <c r="O55" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000054, 'ReportBusinessTripSettlementSummary', 'Execute', 'ReportBusinessTripSettlementSummary');</v>
       </c>
-    </row>
-    <row r="56" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000054'::varchar,'key', 'ReportBusinessTripSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripSettlementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B56" s="7">
         <f t="shared" si="2"/>
         <v>97000000000055</v>
@@ -3865,7 +4155,7 @@
         <v>Supplier</v>
       </c>
       <c r="F56" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000055</v>
       </c>
       <c r="H56" s="4"/>
@@ -3881,15 +4171,20 @@
         <v>23</v>
       </c>
       <c r="M56" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000055</v>
       </c>
       <c r="O56" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000055, 'Execute', 'Execute', 'Supplier');</v>
       </c>
-    </row>
-    <row r="57" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000055'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Supplier'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B57" s="7">
         <f t="shared" si="2"/>
         <v>97000000000056</v>
@@ -3903,7 +4198,7 @@
         <v>Purchase Requisition</v>
       </c>
       <c r="F57" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000056</v>
       </c>
       <c r="H57" s="4"/>
@@ -3919,15 +4214,20 @@
         <v>26</v>
       </c>
       <c r="M57" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000056</v>
       </c>
       <c r="O57" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000056, 'Execute', 'Execute', 'PurchaseRequisition?var=1');</v>
       </c>
-    </row>
-    <row r="58" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000056'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseRequisition?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B58" s="7">
         <f t="shared" si="2"/>
         <v>97000000000057</v>
@@ -3941,7 +4241,7 @@
         <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="F58" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000057</v>
       </c>
       <c r="H58" s="4"/>
@@ -3957,15 +4257,20 @@
         <v>24</v>
       </c>
       <c r="M58" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000057</v>
       </c>
       <c r="O58" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000057, 'ReportPurchaseRequisitionSummary', 'Execute', 'ReportPurchaseRequisitionSummary');</v>
       </c>
-    </row>
-    <row r="59" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000057'::varchar,'key', 'ReportPurchaseRequisitionSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B59" s="7">
         <f t="shared" si="2"/>
         <v>97000000000058</v>
@@ -3979,7 +4284,7 @@
         <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="F59" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000058</v>
       </c>
       <c r="H59" s="4"/>
@@ -3995,15 +4300,20 @@
         <v>25</v>
       </c>
       <c r="M59" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000058</v>
       </c>
       <c r="O59" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000058, 'ReportPurchaseRequisitionToPurchaseOrder', 'Execute', 'ReportPurchaseRequisitionToPurchaseOrder');</v>
       </c>
-    </row>
-    <row r="60" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000058'::varchar,'key', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B60" s="7">
         <f t="shared" si="2"/>
         <v>97000000000059</v>
@@ -4017,7 +4327,7 @@
         <v>Purchase Order</v>
       </c>
       <c r="F60" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000059</v>
       </c>
       <c r="H60" s="4"/>
@@ -4033,15 +4343,20 @@
         <v>28</v>
       </c>
       <c r="M60" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000059</v>
       </c>
       <c r="O60" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000059, 'Execute', 'Execute', 'PurchaseOrder?var=1');</v>
       </c>
-    </row>
-    <row r="61" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000059'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseOrder?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B61" s="7">
         <f t="shared" si="2"/>
         <v>97000000000060</v>
@@ -4055,7 +4370,7 @@
         <v>Report Purchase Order Summary</v>
       </c>
       <c r="F61" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000060</v>
       </c>
       <c r="H61" s="4"/>
@@ -4071,15 +4386,20 @@
         <v>27</v>
       </c>
       <c r="M61" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000060</v>
       </c>
       <c r="O61" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000060, 'ReportPurchaseOrderSummary', 'Execute', 'ReportPurchaseOrderSummary');</v>
       </c>
-    </row>
-    <row r="62" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000060'::varchar,'key', 'ReportPurchaseOrderSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseOrderSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B62" s="9">
         <f t="shared" si="2"/>
         <v>97000000000061</v>
@@ -4093,7 +4413,7 @@
         <v>Purchase Order to Account Payable</v>
       </c>
       <c r="F62" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000061</v>
       </c>
       <c r="H62" s="14"/>
@@ -4109,15 +4429,20 @@
         <v>45</v>
       </c>
       <c r="M62" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000061</v>
       </c>
       <c r="O62" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000061, 'PurchaseOrdertoAccountPayable', 'Execute', 'ReportPOtoAP');</v>
       </c>
-    </row>
-    <row r="63" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000061'::varchar,'key', 'PurchaseOrdertoAccountPayable'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPOtoAP'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B63" s="7">
         <f t="shared" si="2"/>
         <v>97000000000062</v>
@@ -4131,7 +4456,7 @@
         <v>Bank</v>
       </c>
       <c r="F63" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000062</v>
       </c>
       <c r="H63" s="4"/>
@@ -4145,15 +4470,20 @@
       </c>
       <c r="K63" s="18"/>
       <c r="M63" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000062</v>
       </c>
       <c r="O63" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000062, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="64" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000062'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B64" s="7">
         <f t="shared" si="2"/>
         <v>97000000000063</v>
@@ -4167,7 +4497,7 @@
         <v>Bank Account</v>
       </c>
       <c r="F64" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000063</v>
       </c>
       <c r="H64" s="4"/>
@@ -4181,15 +4511,20 @@
       </c>
       <c r="K64" s="18"/>
       <c r="M64" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000063</v>
       </c>
       <c r="O64" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000063, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000063'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B65" s="7">
         <f t="shared" si="2"/>
         <v>97000000000064</v>
@@ -4203,12 +4538,12 @@
         <v>Currency</v>
       </c>
       <c r="F65" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000064</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="3" t="str">
-        <f t="shared" ref="I65:I98" si="8">IF(EXACT(F65, ""), "", IF(EXACT(H65, ""), "Execute", H65))</f>
+        <f t="shared" ref="I65:I98" si="9">IF(EXACT(F65, ""), "", IF(EXACT(H65, ""), "Execute", H65))</f>
         <v>Execute</v>
       </c>
       <c r="J65" s="3" t="str">
@@ -4217,15 +4552,20 @@
       </c>
       <c r="K65" s="18"/>
       <c r="M65" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>256000000000064</v>
       </c>
       <c r="O65" s="15" t="str">
         <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000064, 'Execute', 'Execute', null);</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000064'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B66" s="7">
         <f t="shared" si="2"/>
         <v>97000000000065</v>
@@ -4239,25 +4579,37 @@
         <v>Exchange Rate</v>
       </c>
       <c r="F66" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000065</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J66" s="3" t="str">
-        <f t="shared" ref="J66:J90" si="9">IF(EXACT(F66, ""), "",
+        <f t="shared" ref="J66:J89" si="10">IF(EXACT(F66, ""), "",
 SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C66)), D66, IF(EXACT(H66, ""), "Execute", H66)), " ", ""), "&amp;", "")
 )</f>
         <v>Execute</v>
       </c>
       <c r="K66" s="18"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M66" s="6">
+        <f t="shared" si="6"/>
+        <v>256000000000065</v>
+      </c>
+      <c r="O66" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000065, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q66" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000065'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B67" s="7">
-        <f t="shared" ref="B67:B98" si="10">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
+        <f t="shared" ref="B67:B98" si="11">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
         <v>97000000000066</v>
       </c>
       <c r="C67" s="3" t="str">
@@ -4269,23 +4621,50 @@
         <v>Exchange Rate Summary</v>
       </c>
       <c r="F67" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000066</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J67" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>ExchangeRateSummary</v>
       </c>
       <c r="K67" s="18"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M67" s="6">
+        <f t="shared" si="6"/>
+        <v>256000000000066</v>
+      </c>
+      <c r="O67" s="15" t="str">
+        <f t="shared" ref="O67:O98" si="12">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F67, ""), "null", CONCATENATE($F67)), ", ", IF(EXACT($F67, ""),"null", CONCATENATE("'", $J67, "'")), ", ", IF(EXACT($F67, ""), "null", CONCATENATE("'", $I67, "'")), ", ", IF(EXACT($K67, ""), "null", CONCATENATE("'", $K67, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000066, 'ExchangeRateSummary', 'Execute', null);</v>
+      </c>
+      <c r="Q67" s="1" t="str">
+        <f t="shared" ref="Q67:Q98" si="13">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'menu_RefID', ", IF(EXACT($F67, ""), "null", CONCATENATE("'", SUBSTITUTE($F67, "'", "\'"), "'")), "::varchar,",
+"'key', ", IF(EXACT($J67, ""), "null", CONCATENATE("'", SUBSTITUTE($J67, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($I67, ""), "null", CONCATENATE("'", SUBSTITUTE($I67, "'", "\'"), "'")), "::varchar,",
+"'URLPath', ", IF(EXACT($K67, ""), "null", CONCATENATE("'", SUBSTITUTE($K67, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000066'::varchar,'key', 'ExchangeRateSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B68" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000067</v>
       </c>
       <c r="C68" s="3" t="str">
@@ -4297,23 +4676,35 @@
         <v>Payment Term</v>
       </c>
       <c r="F68" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000067</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J68" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K68" s="18"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M68" s="6">
+        <f t="shared" ref="M68:M98" si="14">IF(ISNUMBER(M67), M67+1, 256000000000001)</f>
+        <v>256000000000067</v>
+      </c>
+      <c r="O68" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000067, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q68" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000067'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B69" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000068</v>
       </c>
       <c r="C69" s="3" t="str">
@@ -4325,23 +4716,35 @@
         <v>Period</v>
       </c>
       <c r="F69" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000068</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J69" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K69" s="18"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M69" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000068</v>
+      </c>
+      <c r="O69" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000068, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q69" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000068'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B70" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000069</v>
       </c>
       <c r="C70" s="3" t="str">
@@ -4353,23 +4756,35 @@
         <v>Asset Category</v>
       </c>
       <c r="F70" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000069</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J70" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K70" s="18"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M70" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000069</v>
+      </c>
+      <c r="O70" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000069, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q70" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000069'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B71" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000070</v>
       </c>
       <c r="C71" s="3" t="str">
@@ -4381,23 +4796,35 @@
         <v>Chart of Account</v>
       </c>
       <c r="F71" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000070</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J71" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K71" s="18"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M71" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000070</v>
+      </c>
+      <c r="O71" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000070, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q71" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000070'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B72" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000071</v>
       </c>
       <c r="C72" s="3" t="str">
@@ -4409,23 +4836,35 @@
         <v>Depreciation Method</v>
       </c>
       <c r="F72" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000071</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J72" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K72" s="18"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M72" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000071</v>
+      </c>
+      <c r="O72" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000071, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q72" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000071'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B73" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000072</v>
       </c>
       <c r="C73" s="3" t="str">
@@ -4437,23 +4876,35 @@
         <v>Depreciation Rate Years</v>
       </c>
       <c r="F73" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000072</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J73" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K73" s="18"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M73" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000072</v>
+      </c>
+      <c r="O73" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000072, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q73" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000072'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B74" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000073</v>
       </c>
       <c r="C74" s="3" t="str">
@@ -4465,23 +4916,35 @@
         <v>Value Added Tax</v>
       </c>
       <c r="F74" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000073</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J74" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K74" s="18"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M74" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000073</v>
+      </c>
+      <c r="O74" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000073, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q74" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000073'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B75" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000074</v>
       </c>
       <c r="C75" s="3" t="str">
@@ -4493,23 +4956,35 @@
         <v>General Journal</v>
       </c>
       <c r="F75" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000074</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J75" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K75" s="18"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M75" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000074</v>
+      </c>
+      <c r="O75" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000074, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q75" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000074'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B76" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000075</v>
       </c>
       <c r="C76" s="3" t="str">
@@ -4521,25 +4996,37 @@
         <v>General Journal Summary</v>
       </c>
       <c r="F76" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000075</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J76" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>GeneralJournalSummary</v>
       </c>
       <c r="K76" s="18" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M76" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000075</v>
+      </c>
+      <c r="O76" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000075, 'GeneralJournalSummary', 'Execute', 'ReportGeneralJournalSummary');</v>
+      </c>
+      <c r="Q76" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000075'::varchar,'key', 'GeneralJournalSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportGeneralJournalSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B77" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000076</v>
       </c>
       <c r="C77" s="3" t="str">
@@ -4551,25 +5038,37 @@
         <v>Reimbursement</v>
       </c>
       <c r="F77" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97000000000076</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J77" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K77" s="18" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M77" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000076</v>
+      </c>
+      <c r="O77" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000076, 'Execute', 'Execute', 'Reimbursement?var=1');</v>
+      </c>
+      <c r="Q77" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000076'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Reimbursement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B78" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000077</v>
       </c>
       <c r="C78" s="3" t="str">
@@ -4581,25 +5080,37 @@
         <v>Reimbursement Summary</v>
       </c>
       <c r="F78" s="17">
-        <f t="shared" ref="F78:F98" si="11">IF(EXACT(B78, ""), F77, B78)</f>
+        <f t="shared" ref="F78:F98" si="15">IF(EXACT(B78, ""), F77, B78)</f>
         <v>97000000000077</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J78" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>ReimbursementSummary</v>
       </c>
       <c r="K78" s="18" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M78" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000077</v>
+      </c>
+      <c r="O78" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000077, 'ReimbursementSummary', 'Execute', 'ReportReimbursementSummary');</v>
+      </c>
+      <c r="Q78" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000077'::varchar,'key', 'ReimbursementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportReimbursementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000078</v>
       </c>
       <c r="C79" s="3" t="str">
@@ -4611,25 +5122,37 @@
         <v>Reimbursement to Debit Note</v>
       </c>
       <c r="F79" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000078</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J79" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>ReimbursementtoDebitNote</v>
       </c>
       <c r="K79" s="18" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M79" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000078</v>
+      </c>
+      <c r="O79" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000078, 'ReimbursementtoDebitNote', 'Execute', 'ReportRemToDN');</v>
+      </c>
+      <c r="Q79" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000078'::varchar,'key', 'ReimbursementtoDebitNote'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportRemToDN'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B80" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000079</v>
       </c>
       <c r="C80" s="3" t="str">
@@ -4641,25 +5164,37 @@
         <v>Debit Note</v>
       </c>
       <c r="F80" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000079</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J80" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K80" s="18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M80" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000079</v>
+      </c>
+      <c r="O80" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000079, 'Execute', 'Execute', 'DebitNote?var=1');</v>
+      </c>
+      <c r="Q80" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000079'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'DebitNote?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B81" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000080</v>
       </c>
       <c r="C81" s="3" t="str">
@@ -4671,25 +5206,37 @@
         <v>Debit Note Summary</v>
       </c>
       <c r="F81" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000080</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J81" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>DebitNoteSummary</v>
       </c>
       <c r="K81" s="18" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M81" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000080</v>
+      </c>
+      <c r="O81" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000080, 'DebitNoteSummary', 'Execute', 'ReportDebitNoteSummary');</v>
+      </c>
+      <c r="Q81" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000080'::varchar,'key', 'DebitNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDebitNoteSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B82" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000081</v>
       </c>
       <c r="C82" s="3" t="str">
@@ -4701,25 +5248,37 @@
         <v>Credit Note</v>
       </c>
       <c r="F82" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000081</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J82" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K82" s="18" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M82" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000081</v>
+      </c>
+      <c r="O82" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000081, 'Execute', 'Execute', 'CreditNote?var=1');</v>
+      </c>
+      <c r="Q82" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000081'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CreditNote?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B83" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000082</v>
       </c>
       <c r="C83" s="3" t="str">
@@ -4731,25 +5290,37 @@
         <v>Credit Note Summary</v>
       </c>
       <c r="F83" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000082</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J83" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>CreditNoteSummary</v>
       </c>
       <c r="K83" s="18" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M83" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000082</v>
+      </c>
+      <c r="O83" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000082, 'CreditNoteSummary', 'Execute', 'ReportCreditNoteSummary');</v>
+      </c>
+      <c r="Q83" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000082'::varchar,'key', 'CreditNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportCreditNoteSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B84" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000083</v>
       </c>
       <c r="C84" s="3" t="str">
@@ -4761,25 +5332,37 @@
         <v>Loan</v>
       </c>
       <c r="F84" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000083</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J84" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K84" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M84" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000083</v>
+      </c>
+      <c r="O84" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000083, 'Execute', 'Execute', 'Loan?var=1');</v>
+      </c>
+      <c r="Q84" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000083'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Loan?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B85" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000084</v>
       </c>
       <c r="C85" s="3" t="str">
@@ -4791,25 +5374,37 @@
         <v>Loan Summary</v>
       </c>
       <c r="F85" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000084</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J85" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>LoanSummary</v>
       </c>
       <c r="K85" s="18" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M85" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000084</v>
+      </c>
+      <c r="O85" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000084, 'LoanSummary', 'Execute', 'ReportLoanSummary');</v>
+      </c>
+      <c r="Q85" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000084'::varchar,'key', 'LoanSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B86" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000085</v>
       </c>
       <c r="C86" s="3" t="str">
@@ -4821,25 +5416,37 @@
         <v>Loan to Loan Settlement</v>
       </c>
       <c r="F86" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000085</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J86" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>LoantoLoanSettlement</v>
       </c>
       <c r="K86" s="18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M86" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000085</v>
+      </c>
+      <c r="O86" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000085, 'LoantoLoanSettlement', 'Execute', 'ReportLoantoLoanSettlement');</v>
+      </c>
+      <c r="Q86" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000085'::varchar,'key', 'LoantoLoanSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoantoLoanSettlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B87" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000086</v>
       </c>
       <c r="C87" s="3" t="str">
@@ -4851,25 +5458,37 @@
         <v>Loan Settlement</v>
       </c>
       <c r="F87" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000086</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J87" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K87" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M87" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000086</v>
+      </c>
+      <c r="O87" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000086, 'Execute', 'Execute', 'LoanSettlement?var=1');</v>
+      </c>
+      <c r="Q87" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000086'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'LoanSettlement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B88" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000087</v>
       </c>
       <c r="C88" s="3" t="str">
@@ -4881,25 +5500,37 @@
         <v>Loan Settlement Summary</v>
       </c>
       <c r="F88" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000087</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J88" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>LoanSettlementSummary</v>
       </c>
       <c r="K88" s="18" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M88" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000087</v>
+      </c>
+      <c r="O88" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000087, 'LoanSettlementSummary', 'Execute', 'ReportLoanSettlementSummary');</v>
+      </c>
+      <c r="Q88" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000087'::varchar,'key', 'LoanSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSettlementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B89" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000088</v>
       </c>
       <c r="C89" s="3" t="str">
@@ -4911,25 +5542,37 @@
         <v>Cash &amp; Bank</v>
       </c>
       <c r="F89" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000088</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J89" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
       <c r="K89" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M89" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000088</v>
+      </c>
+      <c r="O89" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000088, 'Execute', 'Execute', 'Journal?var=1');</v>
+      </c>
+      <c r="Q89" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000088'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Journal?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B90" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000089</v>
       </c>
       <c r="C90" s="3" t="str">
@@ -4941,12 +5584,12 @@
         <v>Cash &amp; Bank Summary</v>
       </c>
       <c r="F90" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000089</v>
       </c>
       <c r="H90" s="4"/>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J90" s="3" t="str">
@@ -4958,10 +5601,22 @@
       <c r="K90" s="18" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M90" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000089</v>
+      </c>
+      <c r="O90" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000089, 'CashBankSummary', 'Execute', 'ReportPaymentJournal');</v>
+      </c>
+      <c r="Q90" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000089'::varchar,'key', 'CashBankSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPaymentJournal'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B91" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000090</v>
       </c>
       <c r="C91" s="3" t="str">
@@ -4973,16 +5628,16 @@
         <v>Account Payable</v>
       </c>
       <c r="F91" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000090</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J91" s="3" t="str">
-        <f t="shared" ref="J91:J98" si="12">IF(EXACT(F91, ""), "",
+        <f t="shared" ref="J91:J98" si="16">IF(EXACT(F91, ""), "",
 SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C91)), D91, IF(EXACT(H91, ""), "Execute", H91)), " ", ""), "&amp;", "")
 )</f>
         <v>Execute</v>
@@ -4990,10 +5645,22 @@
       <c r="K91" s="18" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M91" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000090</v>
+      </c>
+      <c r="O91" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000090, 'Execute', 'Execute', 'AccountPayable?var=1');</v>
+      </c>
+      <c r="Q91" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000090'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AccountPayable?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B92" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000091</v>
       </c>
       <c r="C92" s="3" t="str">
@@ -5005,25 +5672,37 @@
         <v>Account Payable Summary</v>
       </c>
       <c r="F92" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000091</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J92" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>AccountPayableSummary</v>
       </c>
       <c r="K92" s="18" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M92" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000091</v>
+      </c>
+      <c r="O92" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000091, 'AccountPayableSummary', 'Execute', 'ReportAccountPayableSummary');</v>
+      </c>
+      <c r="Q92" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000091'::varchar,'key', 'AccountPayableSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAccountPayableSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B93" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000092</v>
       </c>
       <c r="C93" s="3" t="str">
@@ -5035,23 +5714,35 @@
         <v>Sales Invoice</v>
       </c>
       <c r="F93" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000092</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J93" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Execute</v>
+      </c>
+      <c r="K93" s="18"/>
+      <c r="M93" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000092</v>
+      </c>
+      <c r="O93" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>Execute</v>
-      </c>
-      <c r="K93" s="18"/>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000092, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q93" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000092'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B94" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000093</v>
       </c>
       <c r="C94" s="3" t="str">
@@ -5063,25 +5754,37 @@
         <v>Sales Invoice Summary</v>
       </c>
       <c r="F94" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000093</v>
       </c>
       <c r="H94" s="4"/>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J94" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>SalesInvoiceSummary</v>
       </c>
       <c r="K94" s="18" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M94" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000093</v>
+      </c>
+      <c r="O94" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000093, 'SalesInvoiceSummary', 'Execute', 'ReportInvoiceSummary');</v>
+      </c>
+      <c r="Q94" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000093'::varchar,'key', 'SalesInvoiceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportInvoiceSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B95" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000094</v>
       </c>
       <c r="C95" s="3" t="str">
@@ -5093,25 +5796,37 @@
         <v>Sales Invoice to Credit Note</v>
       </c>
       <c r="F95" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000094</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J95" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>SalesInvoicetoCreditNote</v>
       </c>
       <c r="K95" s="18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M95" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000094</v>
+      </c>
+      <c r="O95" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000094, 'SalesInvoicetoCreditNote', 'Execute', 'ReportInvoiceToCN');</v>
+      </c>
+      <c r="Q95" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000094'::varchar,'key', 'SalesInvoicetoCreditNote'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportInvoiceToCN'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B96" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000095</v>
       </c>
       <c r="C96" s="3" t="str">
@@ -5123,23 +5838,35 @@
         <v>Tax Reconciliation</v>
       </c>
       <c r="F96" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000095</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J96" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Execute</v>
+      </c>
+      <c r="K96" s="18"/>
+      <c r="M96" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000095</v>
+      </c>
+      <c r="O96" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>Execute</v>
-      </c>
-      <c r="K96" s="18"/>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000095, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q96" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000095'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B97" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000096</v>
       </c>
       <c r="C97" s="11" t="str">
@@ -5151,25 +5878,37 @@
         <v>Tax Reconciliation Summary</v>
       </c>
       <c r="F97" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000096</v>
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J97" s="11" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>TaxReconciliationSummary</v>
       </c>
       <c r="K97" s="19" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M97" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000096</v>
+      </c>
+      <c r="O97" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000096, 'TaxReconciliationSummary', 'Execute', 'ReportTaxReconSummary');</v>
+      </c>
+      <c r="Q97" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000096'::varchar,'key', 'TaxReconciliationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTaxReconSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B98" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>97000000000097</v>
       </c>
       <c r="C98" s="22" t="str">
@@ -5181,19 +5920,31 @@
         <v>Customer</v>
       </c>
       <c r="F98" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>97000000000097</v>
       </c>
       <c r="H98" s="26"/>
       <c r="I98" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Execute</v>
       </c>
       <c r="J98" s="22" t="str">
+        <f t="shared" si="16"/>
+        <v>Execute</v>
+      </c>
+      <c r="K98" s="27"/>
+      <c r="M98" s="6">
+        <f t="shared" si="14"/>
+        <v>256000000000097</v>
+      </c>
+      <c r="O98" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>Execute</v>
-      </c>
-      <c r="K98" s="27"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000097, 'Execute', 'Execute', null);</v>
+      </c>
+      <c r="Q98" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000097'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Action</t>
   </si>
@@ -49,18 +49,12 @@
     <t>ReportModifyBudgetSummary</t>
   </si>
   <si>
-    <t>ReportDOSummary</t>
-  </si>
-  <si>
     <t>DeliveryOrder?var=1</t>
   </si>
   <si>
     <t>MaterialReceive?var=1</t>
   </si>
   <si>
-    <t>ReportMatReturnSummary</t>
-  </si>
-  <si>
     <t>MaterialReturn?var=1</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>BusinessTripRequest?var=1</t>
   </si>
   <si>
-    <t>Supplier</t>
-  </si>
-  <si>
     <t>ReportPurchaseRequisitionSummary</t>
   </si>
   <si>
@@ -112,9 +103,6 @@
     <t>ReportReimbursementSummary</t>
   </si>
   <si>
-    <t>DebitNote?var=1</t>
-  </si>
-  <si>
     <t>ReportDebitNoteSummary</t>
   </si>
   <si>
@@ -160,9 +148,6 @@
     <t>CheckDocument?var=1</t>
   </si>
   <si>
-    <t>dashboard?var=1</t>
-  </si>
-  <si>
     <t>MyDocument?var=1</t>
   </si>
   <si>
@@ -175,9 +160,6 @@
     <t>ReportInvoiceSummary</t>
   </si>
   <si>
-    <t>ReportInvoiceToCN</t>
-  </si>
-  <si>
     <t>ReportTaxReconSummary</t>
   </si>
   <si>
@@ -187,9 +169,6 @@
     <t>ReportMaterialReceiveSummary</t>
   </si>
   <si>
-    <t>ReportDoToMaterialReceive</t>
-  </si>
-  <si>
     <t>ReportMatReceivetoMatReturn</t>
   </si>
   <si>
@@ -199,7 +178,67 @@
     <t>ReportBusinessTripToBSF</t>
   </si>
   <si>
-    <t>Report Modify Budget Summary</t>
+    <t>Dashboard?var=1</t>
+  </si>
+  <si>
+    <t>MenuManagement?var=1</t>
+  </si>
+  <si>
+    <t>Budget?var=1</t>
+  </si>
+  <si>
+    <t>BudgetProgress?var=1</t>
+  </si>
+  <si>
+    <t>GeneralJournal?var=1</t>
+  </si>
+  <si>
+    <t>Invoice?var=1</t>
+  </si>
+  <si>
+    <t>TaxRecon?var=1</t>
+  </si>
+  <si>
+    <t>ReportGeneralLedger</t>
+  </si>
+  <si>
+    <t>PrivilegeMenu?var=1</t>
+  </si>
+  <si>
+    <t>Workflow?var=1</t>
+  </si>
+  <si>
+    <t>Timesheet?var=1</t>
+  </si>
+  <si>
+    <t>Product?var=1</t>
+  </si>
+  <si>
+    <t>StockOpname?var=1</t>
+  </si>
+  <si>
+    <t>ReportDeliveryOrderSummary</t>
+  </si>
+  <si>
+    <t>ReportMaterialReturnSummary</t>
+  </si>
+  <si>
+    <t>ReportDOToMaterialReceive</t>
+  </si>
+  <si>
+    <t>Supplier?var=1</t>
+  </si>
+  <si>
+    <t>CategorySupplier?var=1</t>
+  </si>
+  <si>
+    <t>SpecializationSupplier?var=1</t>
+  </si>
+  <si>
+    <t>CustomerOrder?var=1</t>
+  </si>
+  <si>
+    <t>ReportCustomerOrderSummary</t>
   </si>
 </sst>
 </file>
@@ -298,7 +337,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -363,27 +402,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -408,12 +432,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -438,6 +456,7 @@
     <sheetNames>
       <sheetName val="MainOLD"/>
       <sheetName val="Main"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -623,10 +642,10 @@
             <v>97000000000017</v>
           </cell>
           <cell r="F18" t="str">
-            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
+            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
           </cell>
           <cell r="G18" t="str">
-            <v>Privilege Menu</v>
+            <v>Budget</v>
           </cell>
         </row>
         <row r="19">
@@ -634,10 +653,10 @@
             <v>97000000000018</v>
           </cell>
           <cell r="F19" t="str">
-            <v>Module.General.MasterData.Workflow.Transaction</v>
+            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
           </cell>
           <cell r="G19" t="str">
-            <v>Workflow</v>
+            <v>Sub Budget</v>
           </cell>
         </row>
         <row r="20">
@@ -645,7 +664,7 @@
             <v>97000000000019</v>
           </cell>
           <cell r="F20" t="str">
-            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+            <v>Module.Budgeting.Data.Budget.Report.Transaction</v>
           </cell>
           <cell r="G20" t="str">
             <v>Budget</v>
@@ -656,10 +675,10 @@
             <v>97000000000020</v>
           </cell>
           <cell r="F21" t="str">
-            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+            <v>Module.Budgeting.Data.Budget.Report.Resume</v>
           </cell>
           <cell r="G21" t="str">
-            <v>Sub Budget</v>
+            <v>Report Budget Summary</v>
           </cell>
         </row>
         <row r="22">
@@ -689,10 +708,10 @@
             <v>97000000000023</v>
           </cell>
           <cell r="F24" t="str">
-            <v>Module.Budgeting.Data.Work.Transaction</v>
+            <v>Module.Budgeting.Data.ProgressBudget.Transaction</v>
           </cell>
           <cell r="G24" t="str">
-            <v>Work</v>
+            <v>Progress Budget</v>
           </cell>
         </row>
         <row r="25">
@@ -700,10 +719,10 @@
             <v>97000000000024</v>
           </cell>
           <cell r="F25" t="str">
-            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+            <v>Module.Budgeting.Data.ProgressBudget.Report.Resume</v>
           </cell>
           <cell r="G25" t="str">
-            <v>Report Cost Financial Structure</v>
+            <v>Report Progress Budget Summary</v>
           </cell>
         </row>
         <row r="26">
@@ -711,10 +730,10 @@
             <v>97000000000025</v>
           </cell>
           <cell r="F26" t="str">
-            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+            <v>Module.Budgeting.Data.SCurve.Report.Resume</v>
           </cell>
           <cell r="G26" t="str">
-            <v>Blood Aglutinogen Type</v>
+            <v>S-Curve Summary</v>
           </cell>
         </row>
         <row r="27">
@@ -722,10 +741,10 @@
             <v>97000000000026</v>
           </cell>
           <cell r="F27" t="str">
-            <v>Module.General.MasterData.Person.Transaction</v>
+            <v>Module.Budgeting.Data.Work.Transaction</v>
           </cell>
           <cell r="G27" t="str">
-            <v>Person</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="28">
@@ -733,10 +752,10 @@
             <v>97000000000027</v>
           </cell>
           <cell r="F28" t="str">
-            <v>Module.General.MasterData.Religion.Transaction</v>
+            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
           </cell>
           <cell r="G28" t="str">
-            <v>Religion</v>
+            <v>Report Cost Financial Structure</v>
           </cell>
         </row>
         <row r="29">
@@ -744,10 +763,10 @@
             <v>97000000000028</v>
           </cell>
           <cell r="F29" t="str">
-            <v>Module.General.MasterData.UserRole.Transaction</v>
+            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
           </cell>
           <cell r="G29" t="str">
-            <v>Role</v>
+            <v>Blood Aglutinogen Type</v>
           </cell>
         </row>
         <row r="30">
@@ -755,10 +774,10 @@
             <v>97000000000029</v>
           </cell>
           <cell r="F30" t="str">
-            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
+            <v>Module.General.MasterData.Person.Transaction</v>
           </cell>
           <cell r="G30" t="str">
-            <v>Department</v>
+            <v>Person</v>
           </cell>
         </row>
         <row r="31">
@@ -766,10 +785,10 @@
             <v>97000000000030</v>
           </cell>
           <cell r="F31" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
           </cell>
           <cell r="G31" t="str">
-            <v>Person Work Time Sheet</v>
+            <v>Privilege Menu</v>
           </cell>
         </row>
         <row r="32">
@@ -777,10 +796,10 @@
             <v>97000000000031</v>
           </cell>
           <cell r="F32" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
+            <v>Module.General.MasterData.Religion.Transaction</v>
           </cell>
           <cell r="G32" t="str">
-            <v>Person Work Time Sheet Summary</v>
+            <v>Religion</v>
           </cell>
         </row>
         <row r="33">
@@ -788,10 +807,10 @@
             <v>97000000000032</v>
           </cell>
           <cell r="F33" t="str">
-            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
+            <v>Module.General.MasterData.User.Transaction</v>
           </cell>
           <cell r="G33" t="str">
-            <v>Sallary Allocation</v>
+            <v>User</v>
           </cell>
         </row>
         <row r="34">
@@ -799,10 +818,10 @@
             <v>97000000000033</v>
           </cell>
           <cell r="F34" t="str">
-            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+            <v>Module.General.MasterData.UserRole.Transaction</v>
           </cell>
           <cell r="G34" t="str">
-            <v>Sallary Allocation Summary</v>
+            <v>Role</v>
           </cell>
         </row>
         <row r="35">
@@ -810,10 +829,10 @@
             <v>97000000000034</v>
           </cell>
           <cell r="F35" t="str">
-            <v>Module.General.MasterData.Warehouse.Transaction</v>
+            <v>Module.General.MasterData.Workflow.Transaction</v>
           </cell>
           <cell r="G35" t="str">
-            <v>Warehouse</v>
+            <v>Workflow</v>
           </cell>
         </row>
         <row r="36">
@@ -821,10 +840,10 @@
             <v>97000000000035</v>
           </cell>
           <cell r="F36" t="str">
-            <v>Module.General.MasterData.ProductType.Transaction</v>
+            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
           </cell>
           <cell r="G36" t="str">
-            <v>Product Type</v>
+            <v>Department</v>
           </cell>
         </row>
         <row r="37">
@@ -832,10 +851,10 @@
             <v>97000000000036</v>
           </cell>
           <cell r="F37" t="str">
-            <v>Module.General.MasterData.Product.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
           </cell>
           <cell r="G37" t="str">
-            <v>Product</v>
+            <v>Person Work Time Sheet</v>
           </cell>
         </row>
         <row r="38">
@@ -843,10 +862,10 @@
             <v>97000000000037</v>
           </cell>
           <cell r="F38" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
           </cell>
           <cell r="G38" t="str">
-            <v>Delivery Order</v>
+            <v>Person Work Time Sheet Summary</v>
           </cell>
         </row>
         <row r="39">
@@ -854,10 +873,10 @@
             <v>97000000000038</v>
           </cell>
           <cell r="F39" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
           </cell>
           <cell r="G39" t="str">
-            <v>Report DO Summary</v>
+            <v>Sallary Allocation</v>
           </cell>
         </row>
         <row r="40">
@@ -865,10 +884,10 @@
             <v>97000000000039</v>
           </cell>
           <cell r="F40" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
           </cell>
           <cell r="G40" t="str">
-            <v>Report DO to Material Receive</v>
+            <v>Sallary Allocation Summary</v>
           </cell>
         </row>
         <row r="41">
@@ -876,10 +895,10 @@
             <v>97000000000040</v>
           </cell>
           <cell r="F41" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+            <v>Module.General.MasterData.Product.Transaction</v>
           </cell>
           <cell r="G41" t="str">
-            <v>Material Receive</v>
+            <v>Product</v>
           </cell>
         </row>
         <row r="42">
@@ -887,10 +906,10 @@
             <v>97000000000041</v>
           </cell>
           <cell r="F42" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
+            <v>Module.General.MasterData.ProductType.Transaction</v>
           </cell>
           <cell r="G42" t="str">
-            <v>Report Material Receive Summary</v>
+            <v>Product Type</v>
           </cell>
         </row>
         <row r="43">
@@ -898,10 +917,10 @@
             <v>97000000000042</v>
           </cell>
           <cell r="F43" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
+            <v>Module.General.MasterData.Warehouse.Transaction</v>
           </cell>
           <cell r="G43" t="str">
-            <v>Report Material Receive to Material Return</v>
+            <v>Warehouse</v>
           </cell>
         </row>
         <row r="44">
@@ -909,10 +928,10 @@
             <v>97000000000043</v>
           </cell>
           <cell r="F44" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+            <v>Module.General.MasterData.Work.Transaction</v>
           </cell>
           <cell r="G44" t="str">
-            <v>Material Return</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="45">
@@ -920,10 +939,10 @@
             <v>97000000000044</v>
           </cell>
           <cell r="F45" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
           </cell>
           <cell r="G45" t="str">
-            <v>Report Material Return Summary</v>
+            <v>Delivery Order</v>
           </cell>
         </row>
         <row r="46">
@@ -931,10 +950,10 @@
             <v>97000000000045</v>
           </cell>
           <cell r="F46" t="str">
-            <v>Module.Finance.Data.Advance.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
           </cell>
           <cell r="G46" t="str">
-            <v>Advance Request</v>
+            <v>Report DO Summary</v>
           </cell>
         </row>
         <row r="47">
@@ -942,10 +961,10 @@
             <v>97000000000046</v>
           </cell>
           <cell r="F47" t="str">
-            <v>Module.Finance.Data.Advance.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G47" t="str">
-            <v>Report Advance Summary</v>
+            <v>Report DO to Material Receive</v>
           </cell>
         </row>
         <row r="48">
@@ -953,10 +972,10 @@
             <v>97000000000047</v>
           </cell>
           <cell r="F48" t="str">
-            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
           </cell>
           <cell r="G48" t="str">
-            <v>Report Advance to Advance Settlement</v>
+            <v>Material Receive</v>
           </cell>
         </row>
         <row r="49">
@@ -964,10 +983,10 @@
             <v>97000000000048</v>
           </cell>
           <cell r="F49" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G49" t="str">
-            <v>AdvanceSettlement</v>
+            <v>Report Material Receive Summary</v>
           </cell>
         </row>
         <row r="50">
@@ -975,10 +994,10 @@
             <v>97000000000049</v>
           </cell>
           <cell r="F50" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G50" t="str">
-            <v>Report Advance Settlement Summary</v>
+            <v>Report Material Receive to Material Return</v>
           </cell>
         </row>
         <row r="51">
@@ -986,10 +1005,10 @@
             <v>97000000000050</v>
           </cell>
           <cell r="F51" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
           </cell>
           <cell r="G51" t="str">
-            <v>BusinessTrip Request</v>
+            <v>Material Return</v>
           </cell>
         </row>
         <row r="52">
@@ -997,10 +1016,10 @@
             <v>97000000000051</v>
           </cell>
           <cell r="F52" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G52" t="str">
-            <v>Report BusinessTrip Request Summary</v>
+            <v>Report Material Return Summary</v>
           </cell>
         </row>
         <row r="53">
@@ -1008,10 +1027,10 @@
             <v>97000000000052</v>
           </cell>
           <cell r="F53" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</v>
           </cell>
           <cell r="G53" t="str">
-            <v>Report BusinessTrip to BusinessTrip Settlement</v>
+            <v>Stock Opname</v>
           </cell>
         </row>
         <row r="54">
@@ -1019,10 +1038,10 @@
             <v>97000000000053</v>
           </cell>
           <cell r="F54" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</v>
           </cell>
           <cell r="G54" t="str">
-            <v>BusinessTrip Settlement</v>
+            <v>Report Stock Opname Summary</v>
           </cell>
         </row>
         <row r="55">
@@ -1030,10 +1049,10 @@
             <v>97000000000054</v>
           </cell>
           <cell r="F55" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.Finance.Data.Advance.Transaction</v>
           </cell>
           <cell r="G55" t="str">
-            <v>Report BusinessTrip Settlement Summary</v>
+            <v>Advance Request</v>
           </cell>
         </row>
         <row r="56">
@@ -1041,10 +1060,10 @@
             <v>97000000000055</v>
           </cell>
           <cell r="F56" t="str">
-            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+            <v>Module.Finance.Data.Advance.Report.DataList</v>
           </cell>
           <cell r="G56" t="str">
-            <v>Supplier</v>
+            <v>Report Advance Summary</v>
           </cell>
         </row>
         <row r="57">
@@ -1052,10 +1071,10 @@
             <v>97000000000056</v>
           </cell>
           <cell r="F57" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G57" t="str">
-            <v>Purchase Requisition</v>
+            <v>Report Advance to Advance Settlement</v>
           </cell>
         </row>
         <row r="58">
@@ -1063,10 +1082,10 @@
             <v>97000000000057</v>
           </cell>
           <cell r="F58" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
           </cell>
           <cell r="G58" t="str">
-            <v>Report Purchase Requisition Summary</v>
+            <v>AdvanceSettlement</v>
           </cell>
         </row>
         <row r="59">
@@ -1074,10 +1093,10 @@
             <v>97000000000058</v>
           </cell>
           <cell r="F59" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G59" t="str">
-            <v>Report Purchase Requisition To Purchase Order</v>
+            <v>Report Advance Settlement Summary</v>
           </cell>
         </row>
         <row r="60">
@@ -1085,10 +1104,10 @@
             <v>97000000000059</v>
           </cell>
           <cell r="F60" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
           </cell>
           <cell r="G60" t="str">
-            <v>Purchase Order</v>
+            <v>BusinessTrip Request</v>
           </cell>
         </row>
         <row r="61">
@@ -1096,10 +1115,10 @@
             <v>97000000000060</v>
           </cell>
           <cell r="F61" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
           </cell>
           <cell r="G61" t="str">
-            <v>Report Purchase Order Summary</v>
+            <v>Report BusinessTrip Request Summary</v>
           </cell>
         </row>
         <row r="62">
@@ -1107,10 +1126,10 @@
             <v>97000000000061</v>
           </cell>
           <cell r="F62" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G62" t="str">
-            <v>Purchase Order to Account Payable</v>
+            <v>Report BusinessTrip to BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="63">
@@ -1118,10 +1137,10 @@
             <v>97000000000062</v>
           </cell>
           <cell r="F63" t="str">
-            <v>Module.General.MasterData.Bank.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
           </cell>
           <cell r="G63" t="str">
-            <v>Bank</v>
+            <v>BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="64">
@@ -1129,10 +1148,10 @@
             <v>97000000000063</v>
           </cell>
           <cell r="F64" t="str">
-            <v>Module.General.MasterData.BankAccount.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G64" t="str">
-            <v>Bank Account</v>
+            <v>Report BusinessTrip Settlement Summary</v>
           </cell>
         </row>
         <row r="65">
@@ -1140,10 +1159,10 @@
             <v>97000000000064</v>
           </cell>
           <cell r="F65" t="str">
-            <v>Module.General.MasterData.Currency.Transaction</v>
+            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
           </cell>
           <cell r="G65" t="str">
-            <v>Currency</v>
+            <v>Supplier</v>
           </cell>
         </row>
         <row r="66">
@@ -1151,10 +1170,10 @@
             <v>97000000000065</v>
           </cell>
           <cell r="F66" t="str">
-            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+            <v>Module.SupplyChain.MasterData.SupplierCategory.Transaction</v>
           </cell>
           <cell r="G66" t="str">
-            <v>Exchange Rate</v>
+            <v>Supplier Category</v>
           </cell>
         </row>
         <row r="67">
@@ -1162,10 +1181,10 @@
             <v>97000000000066</v>
           </cell>
           <cell r="F67" t="str">
-            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+            <v>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</v>
           </cell>
           <cell r="G67" t="str">
-            <v>Exchange Rate Summary</v>
+            <v>Supplier Sub Category</v>
           </cell>
         </row>
         <row r="68">
@@ -1173,10 +1192,10 @@
             <v>97000000000067</v>
           </cell>
           <cell r="F68" t="str">
-            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
           </cell>
           <cell r="G68" t="str">
-            <v>Payment Term</v>
+            <v>Purchase Requisition</v>
           </cell>
         </row>
         <row r="69">
@@ -1184,10 +1203,10 @@
             <v>97000000000068</v>
           </cell>
           <cell r="F69" t="str">
-            <v>Module.General.MasterData.Period.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
           </cell>
           <cell r="G69" t="str">
-            <v>Period</v>
+            <v>Report Purchase Requisition Summary</v>
           </cell>
         </row>
         <row r="70">
@@ -1195,10 +1214,10 @@
             <v>97000000000069</v>
           </cell>
           <cell r="F70" t="str">
-            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G70" t="str">
-            <v>Asset Category</v>
+            <v>Report Purchase Requisition To Purchase Order</v>
           </cell>
         </row>
         <row r="71">
@@ -1206,10 +1225,10 @@
             <v>97000000000070</v>
           </cell>
           <cell r="F71" t="str">
-            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
           </cell>
           <cell r="G71" t="str">
-            <v>Chart of Account</v>
+            <v>Purchase Order</v>
           </cell>
         </row>
         <row r="72">
@@ -1217,10 +1236,10 @@
             <v>97000000000071</v>
           </cell>
           <cell r="F72" t="str">
-            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G72" t="str">
-            <v>Depreciation Method</v>
+            <v>Report Purchase Order Summary</v>
           </cell>
         </row>
         <row r="73">
@@ -1228,10 +1247,10 @@
             <v>97000000000072</v>
           </cell>
           <cell r="F73" t="str">
-            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
           </cell>
           <cell r="G73" t="str">
-            <v>Depreciation Rate Years</v>
+            <v>Report Purchase Order to Account Payable Summary</v>
           </cell>
         </row>
         <row r="74">
@@ -1239,10 +1258,10 @@
             <v>97000000000073</v>
           </cell>
           <cell r="F74" t="str">
-            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+            <v>Module.General.MasterData.Bank.Transaction</v>
           </cell>
           <cell r="G74" t="str">
-            <v>Value Added Tax</v>
+            <v>Bank</v>
           </cell>
         </row>
         <row r="75">
@@ -1250,10 +1269,10 @@
             <v>97000000000074</v>
           </cell>
           <cell r="F75" t="str">
-            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+            <v>Module.General.MasterData.BankAccount.Transaction</v>
           </cell>
           <cell r="G75" t="str">
-            <v>General Journal</v>
+            <v>Bank Account</v>
           </cell>
         </row>
         <row r="76">
@@ -1261,10 +1280,10 @@
             <v>97000000000075</v>
           </cell>
           <cell r="F76" t="str">
-            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+            <v>Module.General.MasterData.Currency.Transaction</v>
           </cell>
           <cell r="G76" t="str">
-            <v>General Journal Summary</v>
+            <v>Currency</v>
           </cell>
         </row>
         <row r="77">
@@ -1272,10 +1291,10 @@
             <v>97000000000076</v>
           </cell>
           <cell r="F77" t="str">
-            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
           </cell>
           <cell r="G77" t="str">
-            <v>Reimbursement</v>
+            <v>Exchange Rate</v>
           </cell>
         </row>
         <row r="78">
@@ -1283,10 +1302,10 @@
             <v>97000000000077</v>
           </cell>
           <cell r="F78" t="str">
-            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
           </cell>
           <cell r="G78" t="str">
-            <v>Reimbursement Summary</v>
+            <v>Exchange Rate Summary</v>
           </cell>
         </row>
         <row r="79">
@@ -1294,10 +1313,10 @@
             <v>97000000000078</v>
           </cell>
           <cell r="F79" t="str">
-            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
           </cell>
           <cell r="G79" t="str">
-            <v>Reimbursement to Debit Note</v>
+            <v>Payment Term</v>
           </cell>
         </row>
         <row r="80">
@@ -1305,10 +1324,10 @@
             <v>97000000000079</v>
           </cell>
           <cell r="F80" t="str">
-            <v>Module.Finance.Data.DebitNote.Transaction</v>
+            <v>Module.General.MasterData.Period.Transaction</v>
           </cell>
           <cell r="G80" t="str">
-            <v>Debit Note</v>
+            <v>Period</v>
           </cell>
         </row>
         <row r="81">
@@ -1316,10 +1335,10 @@
             <v>97000000000080</v>
           </cell>
           <cell r="F81" t="str">
-            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
           </cell>
           <cell r="G81" t="str">
-            <v>Debit Note Summary</v>
+            <v>Asset Category</v>
           </cell>
         </row>
         <row r="82">
@@ -1327,10 +1346,10 @@
             <v>97000000000081</v>
           </cell>
           <cell r="F82" t="str">
-            <v>Module.Finance.Data.CreditNote.Transaction</v>
+            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
           </cell>
           <cell r="G82" t="str">
-            <v>Credit Note</v>
+            <v>Chart of Account</v>
           </cell>
         </row>
         <row r="83">
@@ -1338,10 +1357,10 @@
             <v>97000000000082</v>
           </cell>
           <cell r="F83" t="str">
-            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
           </cell>
           <cell r="G83" t="str">
-            <v>Credit Note Summary</v>
+            <v>Depreciation Method</v>
           </cell>
         </row>
         <row r="84">
@@ -1349,10 +1368,10 @@
             <v>97000000000083</v>
           </cell>
           <cell r="F84" t="str">
-            <v>Module.Finance.Data.Loan.Transaction</v>
+            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
           </cell>
           <cell r="G84" t="str">
-            <v>Loan</v>
+            <v>Depreciation Rate Years</v>
           </cell>
         </row>
         <row r="85">
@@ -1360,10 +1379,10 @@
             <v>97000000000084</v>
           </cell>
           <cell r="F85" t="str">
-            <v>Module.Finance.Data.Loan.Report.DataList</v>
+            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
           </cell>
           <cell r="G85" t="str">
-            <v>Loan Summary</v>
+            <v>Value Added Tax</v>
           </cell>
         </row>
         <row r="86">
@@ -1371,10 +1390,10 @@
             <v>97000000000085</v>
           </cell>
           <cell r="F86" t="str">
-            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+            <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
           </cell>
           <cell r="G86" t="str">
-            <v>Loan to Loan Settlement</v>
+            <v>Balance Sheet</v>
           </cell>
         </row>
         <row r="87">
@@ -1382,10 +1401,10 @@
             <v>97000000000086</v>
           </cell>
           <cell r="F87" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
           </cell>
           <cell r="G87" t="str">
-            <v>Loan Settlement</v>
+            <v>General Journal</v>
           </cell>
         </row>
         <row r="88">
@@ -1393,10 +1412,10 @@
             <v>97000000000087</v>
           </cell>
           <cell r="F88" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
           </cell>
           <cell r="G88" t="str">
-            <v>Loan Settlement Summary</v>
+            <v>General Journal Summary</v>
           </cell>
         </row>
         <row r="89">
@@ -1404,10 +1423,10 @@
             <v>97000000000088</v>
           </cell>
           <cell r="F89" t="str">
-            <v>Module.Finance.Data.CashBank.Transaction</v>
+            <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
           </cell>
           <cell r="G89" t="str">
-            <v>Cash &amp; Bank</v>
+            <v>General Ledger Summary</v>
           </cell>
         </row>
         <row r="90">
@@ -1415,10 +1434,10 @@
             <v>97000000000089</v>
           </cell>
           <cell r="F90" t="str">
-            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+            <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
           </cell>
           <cell r="G90" t="str">
-            <v>Cash &amp; Bank Summary</v>
+            <v>Profit Loss Summary</v>
           </cell>
         </row>
         <row r="91">
@@ -1426,10 +1445,10 @@
             <v>97000000000090</v>
           </cell>
           <cell r="F91" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+            <v>Module.Finance.Data.CashBank.Transaction</v>
           </cell>
           <cell r="G91" t="str">
-            <v>Account Payable</v>
+            <v>Cash &amp; Bank</v>
           </cell>
         </row>
         <row r="92">
@@ -1437,10 +1456,10 @@
             <v>97000000000091</v>
           </cell>
           <cell r="F92" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+            <v>Module.Finance.Data.CashBank.Report.DataList</v>
           </cell>
           <cell r="G92" t="str">
-            <v>Account Payable Summary</v>
+            <v>Cash &amp; Bank Summary</v>
           </cell>
         </row>
         <row r="93">
@@ -1448,10 +1467,10 @@
             <v>97000000000092</v>
           </cell>
           <cell r="F93" t="str">
-            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+            <v>Module.Finance.Data.CreditNote.Transaction</v>
           </cell>
           <cell r="G93" t="str">
-            <v>Sales Invoice</v>
+            <v>Credit Note</v>
           </cell>
         </row>
         <row r="94">
@@ -1459,10 +1478,10 @@
             <v>97000000000093</v>
           </cell>
           <cell r="F94" t="str">
-            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
           </cell>
           <cell r="G94" t="str">
-            <v>Sales Invoice Summary</v>
+            <v>Credit Note Summary</v>
           </cell>
         </row>
         <row r="95">
@@ -1470,10 +1489,10 @@
             <v>97000000000094</v>
           </cell>
           <cell r="F95" t="str">
-            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+            <v>Module.Finance.Data.DebitNote.Transaction</v>
           </cell>
           <cell r="G95" t="str">
-            <v>Sales Invoice to Credit Note</v>
+            <v>Debit Note</v>
           </cell>
         </row>
         <row r="96">
@@ -1481,10 +1500,10 @@
             <v>97000000000095</v>
           </cell>
           <cell r="F96" t="str">
-            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
           </cell>
           <cell r="G96" t="str">
-            <v>Tax Reconciliation</v>
+            <v>Debit Note Summary</v>
           </cell>
         </row>
         <row r="97">
@@ -1492,10 +1511,10 @@
             <v>97000000000096</v>
           </cell>
           <cell r="F97" t="str">
-            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+            <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
           </cell>
           <cell r="G97" t="str">
-            <v>Tax Reconciliation Summary</v>
+            <v>Fixed Asset</v>
           </cell>
         </row>
         <row r="98">
@@ -1503,13 +1522,212 @@
             <v>97000000000097</v>
           </cell>
           <cell r="F98" t="str">
+            <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Fixed Asset Summary</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="E99">
+            <v>97000000000098</v>
+          </cell>
+          <cell r="F99" t="str">
+            <v>Module.Finance.Data.Loan.Transaction</v>
+          </cell>
+          <cell r="G99" t="str">
+            <v>Loan</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="E100">
+            <v>97000000000099</v>
+          </cell>
+          <cell r="F100" t="str">
+            <v>Module.Finance.Data.Loan.Report.DataList</v>
+          </cell>
+          <cell r="G100" t="str">
+            <v>Loan Summary</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="E101">
+            <v>97000000000100</v>
+          </cell>
+          <cell r="F101" t="str">
+            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G101" t="str">
+            <v>Loan to Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="E102">
+            <v>97000000000101</v>
+          </cell>
+          <cell r="F102" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+          </cell>
+          <cell r="G102" t="str">
+            <v>Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="E103">
+            <v>97000000000102</v>
+          </cell>
+          <cell r="F103" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G103" t="str">
+            <v>Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="E104">
+            <v>97000000000103</v>
+          </cell>
+          <cell r="F104" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+          </cell>
+          <cell r="G104" t="str">
+            <v>Account Payable</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="E105">
+            <v>97000000000104</v>
+          </cell>
+          <cell r="F105" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+          </cell>
+          <cell r="G105" t="str">
+            <v>Account Payable Summary</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="E106">
+            <v>97000000000105</v>
+          </cell>
+          <cell r="F106" t="str">
+            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+          </cell>
+          <cell r="G106" t="str">
+            <v>Reimbursement</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="E107">
+            <v>97000000000106</v>
+          </cell>
+          <cell r="F107" t="str">
+            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+          </cell>
+          <cell r="G107" t="str">
+            <v>Reimbursement Summary</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="E108">
+            <v>97000000000107</v>
+          </cell>
+          <cell r="F108" t="str">
+            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G108" t="str">
+            <v>Reimbursement to Debit Note Summary</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="E109">
+            <v>97000000000108</v>
+          </cell>
+          <cell r="F109" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+          </cell>
+          <cell r="G109" t="str">
+            <v>Sales Invoice</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="E110">
+            <v>97000000000109</v>
+          </cell>
+          <cell r="F110" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+          </cell>
+          <cell r="G110" t="str">
+            <v>Sales Invoice Summary</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="E111">
+            <v>97000000000110</v>
+          </cell>
+          <cell r="F111" t="str">
+            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G111" t="str">
+            <v>Sales Invoice to Credit Note</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="E112">
+            <v>97000000000111</v>
+          </cell>
+          <cell r="F112" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+          </cell>
+          <cell r="G112" t="str">
+            <v>Tax Reconciliation</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="E113">
+            <v>97000000000112</v>
+          </cell>
+          <cell r="F113" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+          </cell>
+          <cell r="G113" t="str">
+            <v>Tax Reconciliation Summary</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="E114">
+            <v>97000000000113</v>
+          </cell>
+          <cell r="F114" t="str">
             <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
           </cell>
-          <cell r="G98" t="str">
+          <cell r="G114" t="str">
             <v>Customer</v>
           </cell>
         </row>
+        <row r="115">
+          <cell r="E115">
+            <v>97000000000114</v>
+          </cell>
+          <cell r="F115" t="str">
+            <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+          </cell>
+          <cell r="G115" t="str">
+            <v>Customer Order</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="E116">
+            <v>97000000000115</v>
+          </cell>
+          <cell r="F116" t="str">
+            <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+          </cell>
+          <cell r="G116" t="str">
+            <v>Customer Order Summary</v>
+          </cell>
+        </row>
       </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1802,19 +2020,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:Q98"/>
+  <dimension ref="B1:Q116"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2.140625" style="16" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="32.28515625" style="1" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="40.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -1851,15 +2069,15 @@
         <v>97000000000001</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>System.Login</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Login</v>
       </c>
       <c r="F2" s="17">
-        <f t="shared" ref="F2:F13" si="0">IF(EXACT(B2, ""), F1, B2)</f>
+        <f t="shared" ref="F2:F65" si="0">IF(EXACT(B2, ""), F1, B2)</f>
         <v>97000000000001</v>
       </c>
       <c r="H2" s="4"/>
@@ -1910,11 +2128,11 @@
         <v>97000000000002</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>System.Logout</v>
       </c>
       <c r="D3" s="3" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Logout</v>
       </c>
       <c r="F3" s="17">
@@ -1967,11 +2185,11 @@
         <v>97000000000003</v>
       </c>
       <c r="C4" s="10" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>System.Lock</v>
       </c>
       <c r="D4" s="11" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Lock</v>
       </c>
       <c r="F4" s="20">
@@ -1987,18 +2205,20 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K4" s="19"/>
+      <c r="K4" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="M4" s="6">
         <f t="shared" ref="M4:M67" si="6">IF(ISNUMBER(M3), M3+1, 256000000000001)</f>
         <v>256000000000003</v>
       </c>
       <c r="O4" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000003, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000003, 'Execute', 'Execute', 'Dashboard?var=1');</v>
       </c>
       <c r="Q4" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000003'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000003'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Dashboard?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
@@ -2007,11 +2227,11 @@
         <v>97000000000004</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Dashboard.Home</v>
       </c>
       <c r="D5" s="3" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Dashboard</v>
       </c>
       <c r="F5" s="17">
@@ -2027,20 +2247,18 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>47</v>
-      </c>
+      <c r="K5" s="18"/>
       <c r="M5" s="6">
         <f t="shared" si="6"/>
         <v>256000000000004</v>
       </c>
       <c r="O5" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000004, 'Execute', 'Execute', 'dashboard?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000004, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q5" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000004'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'dashboard?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000004'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.2">
@@ -2049,11 +2267,11 @@
         <v>97000000000005</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="D6" s="3" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Document Tracking</v>
       </c>
       <c r="F6" s="17">
@@ -2070,7 +2288,7 @@
         <v>Execute</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="6"/>
@@ -2091,11 +2309,11 @@
         <v>97000000000006</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Dashboard.MyDocumentTracking</v>
       </c>
       <c r="D7" s="3" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>My Document Tracking</v>
       </c>
       <c r="F7" s="17">
@@ -2112,7 +2330,7 @@
         <v>Execute</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M7" s="6">
         <f t="shared" si="6"/>
@@ -2133,11 +2351,11 @@
         <v>97000000000007</v>
       </c>
       <c r="C8" s="10" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Dashboard.MyDocumentDisposition</v>
       </c>
       <c r="D8" s="11" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>My Document Disposition</v>
       </c>
       <c r="F8" s="20">
@@ -2145,15 +2363,15 @@
         <v>97000000000007</v>
       </c>
       <c r="H8" s="14"/>
-      <c r="I8" s="11" t="str">
+      <c r="I8" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J8" s="11" t="str">
+      <c r="J8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K8" s="19"/>
+      <c r="K8" s="18"/>
       <c r="M8" s="6">
         <f t="shared" si="6"/>
         <v>256000000000007</v>
@@ -2173,11 +2391,11 @@
         <v>97000000000008</v>
       </c>
       <c r="C9" s="13" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.Country.Transaction</v>
       </c>
       <c r="D9" s="13" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Country</v>
       </c>
       <c r="F9" s="17">
@@ -2185,16 +2403,16 @@
         <v>97000000000008</v>
       </c>
       <c r="G9" s="16"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="13" t="str">
+      <c r="H9" s="4"/>
+      <c r="I9" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J9" s="13" t="str">
+      <c r="J9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="18"/>
       <c r="M9" s="6">
         <f t="shared" si="6"/>
         <v>256000000000008</v>
@@ -2214,11 +2432,11 @@
         <v>97000000000009</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="D10" s="3" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Province / State</v>
       </c>
       <c r="F10" s="17">
@@ -2255,11 +2473,11 @@
         <v>97000000000010</v>
       </c>
       <c r="C11" s="3" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
       </c>
       <c r="D11" s="3" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Municipality / Regency</v>
       </c>
       <c r="F11" s="17">
@@ -2296,11 +2514,11 @@
         <v>97000000000011</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
       </c>
       <c r="D12" s="3" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>District</v>
       </c>
       <c r="F12" s="17">
@@ -2337,11 +2555,11 @@
         <v>97000000000012</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
       </c>
       <c r="D13" s="3" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Urban Village / Village</v>
       </c>
       <c r="F13" s="17">
@@ -2378,15 +2596,15 @@
         <v>97000000000013</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="D14" s="3" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Business Document Type</v>
       </c>
       <c r="F14" s="17">
-        <f t="shared" ref="F14:F77" si="8">IF(EXACT(B14, ""), F13, B14)</f>
+        <f t="shared" si="0"/>
         <v>97000000000013</v>
       </c>
       <c r="H14" s="4"/>
@@ -2419,15 +2637,15 @@
         <v>97000000000014</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="D15" s="3" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Business Document</v>
       </c>
       <c r="F15" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000014</v>
       </c>
       <c r="H15" s="4"/>
@@ -2460,15 +2678,15 @@
         <v>97000000000015</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="D16" s="3" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Business Document Version</v>
       </c>
       <c r="F16" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000015</v>
       </c>
       <c r="H16" s="4"/>
@@ -2496,20 +2714,20 @@
       </c>
     </row>
     <row r="17" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <f t="shared" si="2"/>
         <v>97000000000016</v>
       </c>
-      <c r="C17" s="3" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+      <c r="C17" s="11" t="str">
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.General.MasterData.MenuManagement.Transaction</v>
       </c>
-      <c r="D17" s="3" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+      <c r="D17" s="11" t="str">
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Menu Management</v>
       </c>
-      <c r="F17" s="17">
-        <f t="shared" si="8"/>
+      <c r="F17" s="20">
+        <f t="shared" si="0"/>
         <v>97000000000016</v>
       </c>
       <c r="H17" s="4"/>
@@ -2521,19 +2739,21 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K17" s="18"/>
+      <c r="K17" s="19" t="s">
+        <v>54</v>
+      </c>
       <c r="M17" s="6">
         <f t="shared" si="6"/>
         <v>256000000000016</v>
       </c>
       <c r="O17" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000016, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000016, 'Execute', 'Execute', 'MenuManagement?var=1');</v>
       </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000016'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000016'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MenuManagement?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="18" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2542,15 +2762,15 @@
         <v>97000000000017</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="D18" s="3" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Privilege Menu</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Budget</v>
       </c>
       <c r="F18" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000017</v>
       </c>
       <c r="H18" s="4"/>
@@ -2578,32 +2798,32 @@
       </c>
     </row>
     <row r="19" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <f t="shared" si="2"/>
         <v>97000000000018</v>
       </c>
-      <c r="C19" s="11" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Workflow.Transaction</v>
-      </c>
-      <c r="D19" s="11" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Workflow</v>
-      </c>
-      <c r="F19" s="20">
-        <f t="shared" si="8"/>
+      <c r="C19" s="3" t="str">
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sub Budget</v>
+      </c>
+      <c r="F19" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000018</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="11" t="str">
+      <c r="H19" s="4"/>
+      <c r="I19" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J19" s="11" t="str">
+      <c r="J19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K19" s="19"/>
+      <c r="K19" s="18"/>
       <c r="M19" s="6">
         <f t="shared" si="6"/>
         <v>256000000000018</v>
@@ -2624,15 +2844,15 @@
         <v>97000000000019</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Budget.Report.Transaction</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Budget</v>
       </c>
       <c r="F20" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000019</v>
       </c>
       <c r="H20" s="4"/>
@@ -2642,21 +2862,23 @@
       </c>
       <c r="J20" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
-      </c>
-      <c r="K20" s="18"/>
+        <v>Budget</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="M20" s="6">
         <f t="shared" si="6"/>
         <v>256000000000019</v>
       </c>
       <c r="O20" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000019, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000019, 'Budget', 'Execute', 'Budget?var=1');</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000019'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000019'::varchar,'key', 'Budget'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Budget?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="21" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2665,15 +2887,15 @@
         <v>97000000000020</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Budget.Report.Resume</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sub Budget</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Budget Summary</v>
       </c>
       <c r="F21" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000020</v>
       </c>
       <c r="H21" s="4"/>
@@ -2683,7 +2905,7 @@
       </c>
       <c r="J21" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>ReportBudgetSummary</v>
       </c>
       <c r="K21" s="18"/>
       <c r="M21" s="6">
@@ -2692,12 +2914,12 @@
       </c>
       <c r="O21" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000020, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000020, 'ReportBudgetSummary', 'Execute', null);</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000020'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000020'::varchar,'key', 'ReportBudgetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="22" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2706,15 +2928,15 @@
         <v>97000000000021</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Modify Budget</v>
       </c>
       <c r="F22" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000021</v>
       </c>
       <c r="H22" s="4"/>
@@ -2727,7 +2949,7 @@
         <v>Execute</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" si="6"/>
@@ -2749,24 +2971,21 @@
         <v>97000000000022</v>
       </c>
       <c r="C23" s="3" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
         <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
         <v>Report Modify Budget Summary</v>
       </c>
       <c r="F23" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000022</v>
       </c>
-      <c r="H23" s="4" t="str">
-        <f>D23</f>
-        <v>Report Modify Budget Summary</v>
-      </c>
+      <c r="H23" s="4"/>
       <c r="I23" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Report Modify Budget Summary</v>
+        <v>Execute</v>
       </c>
       <c r="J23" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2781,12 +3000,12 @@
       </c>
       <c r="O23" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000022, 'ReportModifyBudgetSummary', 'Report Modify Budget Summary', 'ReportModifyBudgetSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000022, 'ReportModifyBudgetSummary', 'Execute', 'ReportModifyBudgetSummary');</v>
       </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000022'::varchar,'key', 'ReportModifyBudgetSummary'::varchar,'caption', 'Report Modify Budget Summary'::varchar,'URLPath', 'ReportModifyBudgetSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000022'::varchar,'key', 'ReportModifyBudgetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportModifyBudgetSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="24" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2795,15 +3014,15 @@
         <v>97000000000023</v>
       </c>
       <c r="C24" s="3" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.Work.Transaction</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ProgressBudget.Transaction</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Work</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Progress Budget</v>
       </c>
       <c r="F24" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000023</v>
       </c>
       <c r="H24" s="4"/>
@@ -2815,62 +3034,62 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K24" s="18"/>
+      <c r="K24" s="18" t="s">
+        <v>56</v>
+      </c>
       <c r="M24" s="6">
         <f t="shared" si="6"/>
         <v>256000000000023</v>
       </c>
       <c r="O24" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000023, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000023, 'Execute', 'Execute', 'BudgetProgress?var=1');</v>
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000023'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000023'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BudgetProgress?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="25" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <f t="shared" si="2"/>
         <v>97000000000024</v>
       </c>
-      <c r="C25" s="11" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
-      </c>
-      <c r="D25" s="11" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Cost Financial Structure</v>
-      </c>
-      <c r="F25" s="20">
-        <f t="shared" si="8"/>
+      <c r="C25" s="3" t="str">
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ProgressBudget.Report.Resume</v>
+      </c>
+      <c r="D25" s="3" t="str">
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Progress Budget Summary</v>
+      </c>
+      <c r="F25" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000024</v>
       </c>
-      <c r="H25" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="11" t="str">
+      <c r="H25" s="4"/>
+      <c r="I25" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Report Modify Budget Summary</v>
-      </c>
-      <c r="J25" s="11" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="J25" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportCostFinancialStructure</v>
-      </c>
-      <c r="K25" s="19"/>
+        <v>ReportProgressBudgetSummary</v>
+      </c>
+      <c r="K25" s="18"/>
       <c r="M25" s="6">
         <f t="shared" si="6"/>
         <v>256000000000024</v>
       </c>
       <c r="O25" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000024, 'ReportCostFinancialStructure', 'Report Modify Budget Summary', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000024, 'ReportProgressBudgetSummary', 'Execute', null);</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000024'::varchar,'key', 'ReportCostFinancialStructure'::varchar,'caption', 'Report Modify Budget Summary'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000024'::varchar,'key', 'ReportProgressBudgetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="26" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2879,15 +3098,15 @@
         <v>97000000000025</v>
       </c>
       <c r="C26" s="3" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.SCurve.Report.Resume</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Blood Aglutinogen Type</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>S-Curve Summary</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000025</v>
       </c>
       <c r="H26" s="4"/>
@@ -2897,7 +3116,7 @@
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>S-CurveSummary</v>
       </c>
       <c r="K26" s="18"/>
       <c r="M26" s="6">
@@ -2906,12 +3125,12 @@
       </c>
       <c r="O26" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000025, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000025, 'S-CurveSummary', 'Execute', null);</v>
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000025'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000025'::varchar,'key', 'S-CurveSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="27" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -2920,15 +3139,15 @@
         <v>97000000000026</v>
       </c>
       <c r="C27" s="3" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Person.Transaction</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Person</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Work</v>
       </c>
       <c r="F27" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000026</v>
       </c>
       <c r="H27" s="4"/>
@@ -2956,20 +3175,20 @@
       </c>
     </row>
     <row r="28" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <f t="shared" si="2"/>
         <v>97000000000027</v>
       </c>
-      <c r="C28" s="3" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Religion.Transaction</v>
-      </c>
-      <c r="D28" s="3" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Religion</v>
-      </c>
-      <c r="F28" s="17">
-        <f t="shared" si="8"/>
+      <c r="C28" s="11" t="str">
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+      </c>
+      <c r="D28" s="11" t="str">
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Cost Financial Structure</v>
+      </c>
+      <c r="F28" s="20">
+        <f t="shared" si="0"/>
         <v>97000000000027</v>
       </c>
       <c r="H28" s="4"/>
@@ -2979,21 +3198,21 @@
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
-      </c>
-      <c r="K28" s="18"/>
+        <v>ReportCostFinancialStructure</v>
+      </c>
+      <c r="K28" s="19"/>
       <c r="M28" s="6">
         <f t="shared" si="6"/>
         <v>256000000000027</v>
       </c>
       <c r="O28" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000027, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000027, 'ReportCostFinancialStructure', 'Execute', null);</v>
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000027'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000027'::varchar,'key', 'ReportCostFinancialStructure'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="29" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3002,15 +3221,15 @@
         <v>97000000000028</v>
       </c>
       <c r="C29" s="3" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.UserRole.Transaction</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="D29" s="3" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Role</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Blood Aglutinogen Type</v>
       </c>
       <c r="F29" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000028</v>
       </c>
       <c r="H29" s="4"/>
@@ -3043,15 +3262,15 @@
         <v>97000000000029</v>
       </c>
       <c r="C30" s="3" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="D30" s="3" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Department</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Person</v>
       </c>
       <c r="F30" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000029</v>
       </c>
       <c r="H30" s="4"/>
@@ -3084,15 +3303,15 @@
         <v>97000000000030</v>
       </c>
       <c r="C31" s="3" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="D31" s="3" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Person Work Time Sheet</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Privilege Menu</v>
       </c>
       <c r="F31" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000030</v>
       </c>
       <c r="H31" s="4"/>
@@ -3104,19 +3323,21 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K31" s="18"/>
+      <c r="K31" s="18" t="s">
+        <v>61</v>
+      </c>
       <c r="M31" s="6">
         <f t="shared" si="6"/>
         <v>256000000000030</v>
       </c>
       <c r="O31" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000030, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000030, 'Execute', 'Execute', 'PrivilegeMenu?var=1');</v>
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000030'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000030'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PrivilegeMenu?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="32" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3125,15 +3346,15 @@
         <v>97000000000031</v>
       </c>
       <c r="C32" s="3" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="D32" s="3" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Person Work Time Sheet Summary</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Religion</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000031</v>
       </c>
       <c r="H32" s="4"/>
@@ -3143,23 +3364,21 @@
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>PersonWorkTimeSheetSummary</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>54</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K32" s="18"/>
       <c r="M32" s="6">
         <f t="shared" si="6"/>
         <v>256000000000031</v>
       </c>
       <c r="O32" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000031, 'PersonWorkTimeSheetSummary', 'Execute', 'ReportTimesheetSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000031, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000031'::varchar,'key', 'PersonWorkTimeSheetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTimesheetSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000031'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="33" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3168,15 +3387,15 @@
         <v>97000000000032</v>
       </c>
       <c r="C33" s="3" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.User.Transaction</v>
       </c>
       <c r="D33" s="3" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sallary Allocation</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>User</v>
       </c>
       <c r="F33" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000032</v>
       </c>
       <c r="H33" s="4"/>
@@ -3204,44 +3423,44 @@
       </c>
     </row>
     <row r="34" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <f t="shared" si="2"/>
         <v>97000000000033</v>
       </c>
-      <c r="C34" s="11" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
-      </c>
-      <c r="D34" s="11" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sallary Allocation Summary</v>
-      </c>
-      <c r="F34" s="20">
-        <f t="shared" si="8"/>
+      <c r="C34" s="3" t="str">
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Role</v>
+      </c>
+      <c r="F34" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000033</v>
       </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="11" t="str">
+      <c r="H34" s="4"/>
+      <c r="I34" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J34" s="11" t="str">
+      <c r="J34" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>SallaryAllocationSummary</v>
-      </c>
-      <c r="K34" s="19"/>
+        <v>Execute</v>
+      </c>
+      <c r="K34" s="18"/>
       <c r="M34" s="6">
         <f t="shared" si="6"/>
         <v>256000000000033</v>
       </c>
       <c r="O34" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000033, 'SallaryAllocationSummary', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000033, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000033'::varchar,'key', 'SallaryAllocationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000033'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="35" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3250,15 +3469,15 @@
         <v>97000000000034</v>
       </c>
       <c r="C35" s="3" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="D35" s="3" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Warehouse</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Workflow</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000034</v>
       </c>
       <c r="H35" s="4"/>
@@ -3270,19 +3489,21 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K35" s="18"/>
+      <c r="K35" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="M35" s="6">
         <f t="shared" si="6"/>
         <v>256000000000034</v>
       </c>
       <c r="O35" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000034, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000034, 'Execute', 'Execute', 'Workflow?var=1');</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000034'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000034'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Workflow?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="36" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3291,15 +3512,15 @@
         <v>97000000000035</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Product Type</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Department</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000035</v>
       </c>
       <c r="H36" s="4"/>
@@ -3332,15 +3553,15 @@
         <v>97000000000036</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Product.Transaction</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="D37" s="3" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Product</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Person Work Time Sheet</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000036</v>
       </c>
       <c r="H37" s="4"/>
@@ -3352,19 +3573,21 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K37" s="18"/>
+      <c r="K37" s="18" t="s">
+        <v>63</v>
+      </c>
       <c r="M37" s="6">
         <f t="shared" si="6"/>
         <v>256000000000036</v>
       </c>
       <c r="O37" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000036, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000036, 'Execute', 'Execute', 'Timesheet?var=1');</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000036'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000036'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Timesheet?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="38" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3373,15 +3596,15 @@
         <v>97000000000037</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="D38" s="3" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Delivery Order</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="F38" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000037</v>
       </c>
       <c r="H38" s="4"/>
@@ -3391,10 +3614,10 @@
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>PersonWorkTimeSheetSummary</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="M38" s="6">
         <f t="shared" si="6"/>
@@ -3402,12 +3625,12 @@
       </c>
       <c r="O38" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000037, 'Execute', 'Execute', 'DeliveryOrder?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000037, 'PersonWorkTimeSheetSummary', 'Execute', 'ReportTimesheetSummary');</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000037'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'DeliveryOrder?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000037'::varchar,'key', 'PersonWorkTimeSheetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTimesheetSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="39" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3416,15 +3639,15 @@
         <v>97000000000038</v>
       </c>
       <c r="C39" s="3" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="D39" s="3" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report DO Summary</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sallary Allocation</v>
       </c>
       <c r="F39" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000038</v>
       </c>
       <c r="H39" s="4"/>
@@ -3434,40 +3657,38 @@
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportDOSummary</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>10</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K39" s="18"/>
       <c r="M39" s="6">
         <f t="shared" si="6"/>
         <v>256000000000038</v>
       </c>
       <c r="O39" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000038, 'ReportDOSummary', 'Execute', 'ReportDOSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000038, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000038'::varchar,'key', 'ReportDOSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDOSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000038'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="40" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="7">
+      <c r="B40" s="9">
         <f t="shared" si="2"/>
         <v>97000000000039</v>
       </c>
-      <c r="C40" s="3" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
-      </c>
-      <c r="D40" s="3" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report DO to Material Receive</v>
-      </c>
-      <c r="F40" s="17">
-        <f t="shared" si="8"/>
+      <c r="C40" s="11" t="str">
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+      </c>
+      <c r="D40" s="11" t="str">
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sallary Allocation Summary</v>
+      </c>
+      <c r="F40" s="20">
+        <f t="shared" si="0"/>
         <v>97000000000039</v>
       </c>
       <c r="H40" s="4"/>
@@ -3477,23 +3698,21 @@
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportDOtoMaterialReceive</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>56</v>
-      </c>
+        <v>SallaryAllocationSummary</v>
+      </c>
+      <c r="K40" s="19"/>
       <c r="M40" s="6">
         <f t="shared" si="6"/>
         <v>256000000000039</v>
       </c>
       <c r="O40" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000039, 'ReportDOtoMaterialReceive', 'Execute', 'ReportDoToMaterialReceive');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000039, 'SallaryAllocationSummary', 'Execute', null);</v>
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000039'::varchar,'key', 'ReportDOtoMaterialReceive'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDoToMaterialReceive'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000039'::varchar,'key', 'SallaryAllocationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="41" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3502,15 +3721,15 @@
         <v>97000000000040</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="D41" s="3" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Material Receive</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Product</v>
       </c>
       <c r="F41" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000040</v>
       </c>
       <c r="H41" s="4"/>
@@ -3523,7 +3742,7 @@
         <v>Execute</v>
       </c>
       <c r="K41" s="18" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="6"/>
@@ -3531,12 +3750,12 @@
       </c>
       <c r="O41" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000040, 'Execute', 'Execute', 'MaterialReceive?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000040, 'Execute', 'Execute', 'Product?var=1');</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000040'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReceive?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000040'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Product?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="42" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3545,15 +3764,15 @@
         <v>97000000000041</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="D42" s="3" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Material Receive Summary</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Product Type</v>
       </c>
       <c r="F42" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000041</v>
       </c>
       <c r="H42" s="4"/>
@@ -3563,23 +3782,21 @@
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportMaterialReceiveSummary</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>55</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K42" s="18"/>
       <c r="M42" s="6">
         <f t="shared" si="6"/>
         <v>256000000000041</v>
       </c>
       <c r="O42" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000041, 'ReportMaterialReceiveSummary', 'Execute', 'ReportMaterialReceiveSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000041, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000041'::varchar,'key', 'ReportMaterialReceiveSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMaterialReceiveSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000041'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="43" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3588,15 +3805,15 @@
         <v>97000000000042</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="D43" s="3" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Material Receive to Material Return</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Warehouse</v>
       </c>
       <c r="F43" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000042</v>
       </c>
       <c r="H43" s="4"/>
@@ -3606,23 +3823,21 @@
       </c>
       <c r="J43" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportMaterialReceivetoMaterialReturn</v>
-      </c>
-      <c r="K43" s="18" t="s">
-        <v>57</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K43" s="18"/>
       <c r="M43" s="6">
         <f t="shared" si="6"/>
         <v>256000000000042</v>
       </c>
       <c r="O43" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000042, 'ReportMaterialReceivetoMaterialReturn', 'Execute', 'ReportMatReceivetoMatReturn');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000042, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000042'::varchar,'key', 'ReportMaterialReceivetoMaterialReturn'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMatReceivetoMatReturn'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000042'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="44" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3631,15 +3846,15 @@
         <v>97000000000043</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Work.Transaction</v>
       </c>
       <c r="D44" s="3" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Material Return</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Work</v>
       </c>
       <c r="F44" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000043</v>
       </c>
       <c r="H44" s="4"/>
@@ -3651,51 +3866,49 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K44" s="18" t="s">
-        <v>14</v>
-      </c>
+      <c r="K44" s="18"/>
       <c r="M44" s="6">
         <f t="shared" si="6"/>
         <v>256000000000043</v>
       </c>
       <c r="O44" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000043, 'Execute', 'Execute', 'MaterialReturn?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000043, 'Execute', 'Execute', null);</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000043'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReturn?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000043'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="45" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="9">
+      <c r="B45" s="7">
         <f t="shared" si="2"/>
         <v>97000000000044</v>
       </c>
-      <c r="C45" s="11" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
-      </c>
-      <c r="D45" s="11" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Material Return Summary</v>
-      </c>
-      <c r="F45" s="20">
-        <f t="shared" si="8"/>
+      <c r="C45" s="3" t="str">
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Delivery Order</v>
+      </c>
+      <c r="F45" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000044</v>
       </c>
-      <c r="H45" s="14"/>
-      <c r="I45" s="11" t="str">
+      <c r="H45" s="4"/>
+      <c r="I45" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J45" s="11" t="str">
+      <c r="J45" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportMaterialReturnSummary</v>
-      </c>
-      <c r="K45" s="19" t="s">
-        <v>13</v>
+        <v>Execute</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>10</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="6"/>
@@ -3703,12 +3916,12 @@
       </c>
       <c r="O45" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000044, 'ReportMaterialReturnSummary', 'Execute', 'ReportMatReturnSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000044, 'Execute', 'Execute', 'DeliveryOrder?var=1');</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000044'::varchar,'key', 'ReportMaterialReturnSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMatReturnSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000044'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'DeliveryOrder?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="46" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3717,15 +3930,15 @@
         <v>97000000000045</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="D46" s="3" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Advance Request</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report DO Summary</v>
       </c>
       <c r="F46" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000045</v>
       </c>
       <c r="H46" s="4"/>
@@ -3735,10 +3948,10 @@
       </c>
       <c r="J46" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>ReportDOSummary</v>
       </c>
       <c r="K46" s="18" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="M46" s="6">
         <f t="shared" si="6"/>
@@ -3746,12 +3959,12 @@
       </c>
       <c r="O46" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000045, 'Execute', 'Execute', 'AdvanceRequest?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000045, 'ReportDOSummary', 'Execute', 'ReportDeliveryOrderSummary');</v>
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000045'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceRequest?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000045'::varchar,'key', 'ReportDOSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDeliveryOrderSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="47" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3760,15 +3973,15 @@
         <v>97000000000046</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="D47" s="3" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Advance Summary</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report DO to Material Receive</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000046</v>
       </c>
       <c r="H47" s="4"/>
@@ -3778,10 +3991,10 @@
       </c>
       <c r="J47" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportAdvanceSummary</v>
+        <v>ReportDOtoMaterialReceive</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="M47" s="6">
         <f t="shared" si="6"/>
@@ -3789,12 +4002,12 @@
       </c>
       <c r="O47" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000046, 'ReportAdvanceSummary', 'Execute', 'ReportAdvanceSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000046, 'ReportDOtoMaterialReceive', 'Execute', 'ReportDOToMaterialReceive');</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000046'::varchar,'key', 'ReportAdvanceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000046'::varchar,'key', 'ReportDOtoMaterialReceive'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDOToMaterialReceive'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="48" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3803,15 +4016,15 @@
         <v>97000000000047</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="D48" s="3" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Advance to Advance Settlement</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Material Receive</v>
       </c>
       <c r="F48" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000047</v>
       </c>
       <c r="H48" s="4"/>
@@ -3821,10 +4034,10 @@
       </c>
       <c r="J48" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportAdvancetoAdvanceSettlement</v>
+        <v>Execute</v>
       </c>
       <c r="K48" s="18" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="M48" s="6">
         <f t="shared" si="6"/>
@@ -3832,12 +4045,12 @@
       </c>
       <c r="O48" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000047, 'ReportAdvancetoAdvanceSettlement', 'Execute', 'ReportAdvanceToASF');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000047, 'Execute', 'Execute', 'MaterialReceive?var=1');</v>
       </c>
       <c r="P48" s="1"/>
       <c r="Q48" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000047'::varchar,'key', 'ReportAdvancetoAdvanceSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceToASF'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000047'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReceive?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="49" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3846,15 +4059,15 @@
         <v>97000000000048</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="D49" s="3" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>AdvanceSettlement</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Material Receive Summary</v>
       </c>
       <c r="F49" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000048</v>
       </c>
       <c r="H49" s="4"/>
@@ -3864,10 +4077,10 @@
       </c>
       <c r="J49" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>ReportMaterialReceiveSummary</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="M49" s="6">
         <f t="shared" si="6"/>
@@ -3875,12 +4088,12 @@
       </c>
       <c r="O49" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000048, 'Execute', 'Execute', 'AdvanceSettlement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000048, 'ReportMaterialReceiveSummary', 'Execute', 'ReportMaterialReceiveSummary');</v>
       </c>
       <c r="P49" s="1"/>
       <c r="Q49" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000048'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceSettlement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000048'::varchar,'key', 'ReportMaterialReceiveSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMaterialReceiveSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="50" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3889,15 +4102,15 @@
         <v>97000000000049</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="D50" s="3" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Advance Settlement Summary</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Material Receive to Material Return</v>
       </c>
       <c r="F50" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000049</v>
       </c>
       <c r="H50" s="4"/>
@@ -3907,10 +4120,10 @@
       </c>
       <c r="J50" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportAdvanceSettlementSummary</v>
+        <v>ReportMaterialReceivetoMaterialReturn</v>
       </c>
       <c r="K50" s="18" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="M50" s="6">
         <f t="shared" si="6"/>
@@ -3918,12 +4131,12 @@
       </c>
       <c r="O50" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000049, 'ReportAdvanceSettlementSummary', 'Execute', 'ReportAdvanceSettlementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000049, 'ReportMaterialReceivetoMaterialReturn', 'Execute', 'ReportMatReceivetoMatReturn');</v>
       </c>
       <c r="P50" s="1"/>
       <c r="Q50" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000049'::varchar,'key', 'ReportAdvanceSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSettlementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000049'::varchar,'key', 'ReportMaterialReceivetoMaterialReturn'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMatReceivetoMatReturn'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="51" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3932,15 +4145,15 @@
         <v>97000000000050</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="D51" s="3" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>BusinessTrip Request</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Material Return</v>
       </c>
       <c r="F51" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000050</v>
       </c>
       <c r="H51" s="4"/>
@@ -3953,7 +4166,7 @@
         <v>Execute</v>
       </c>
       <c r="K51" s="18" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" si="6"/>
@@ -3961,12 +4174,12 @@
       </c>
       <c r="O51" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000050, 'Execute', 'Execute', 'BusinessTripRequest?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000050, 'Execute', 'Execute', 'MaterialReturn?var=1');</v>
       </c>
       <c r="P51" s="1"/>
       <c r="Q51" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000050'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripRequest?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000050'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'MaterialReturn?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="52" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3975,15 +4188,15 @@
         <v>97000000000051</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="D52" s="3" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report BusinessTrip Request Summary</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Material Return Summary</v>
       </c>
       <c r="F52" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000051</v>
       </c>
       <c r="H52" s="4"/>
@@ -3993,10 +4206,10 @@
       </c>
       <c r="J52" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportBusinessTripRequestSummary</v>
+        <v>ReportMaterialReturnSummary</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="M52" s="6">
         <f t="shared" si="6"/>
@@ -4004,12 +4217,12 @@
       </c>
       <c r="O52" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000051, 'ReportBusinessTripRequestSummary', 'Execute', 'ReportBusinessTripRequestSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000051, 'ReportMaterialReturnSummary', 'Execute', 'ReportMaterialReturnSummary');</v>
       </c>
       <c r="P52" s="1"/>
       <c r="Q52" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000051'::varchar,'key', 'ReportBusinessTripRequestSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripRequestSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000051'::varchar,'key', 'ReportMaterialReturnSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportMaterialReturnSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="53" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4018,15 +4231,15 @@
         <v>97000000000052</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</v>
       </c>
       <c r="D53" s="3" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report BusinessTrip to BusinessTrip Settlement</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Stock Opname</v>
       </c>
       <c r="F53" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000052</v>
       </c>
       <c r="H53" s="4"/>
@@ -4036,10 +4249,10 @@
       </c>
       <c r="J53" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportBusinessTriptoBusinessTripSettlement</v>
+        <v>Execute</v>
       </c>
       <c r="K53" s="18" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M53" s="6">
         <f t="shared" si="6"/>
@@ -4047,29 +4260,29 @@
       </c>
       <c r="O53" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000052, 'ReportBusinessTriptoBusinessTripSettlement', 'Execute', 'ReportBusinessTripToBSF');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000052, 'Execute', 'Execute', 'StockOpname?var=1');</v>
       </c>
       <c r="P53" s="1"/>
       <c r="Q53" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000052'::varchar,'key', 'ReportBusinessTriptoBusinessTripSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripToBSF'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000052'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'StockOpname?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="54" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="7">
+      <c r="B54" s="9">
         <f t="shared" si="2"/>
         <v>97000000000053</v>
       </c>
-      <c r="C54" s="3" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
-      </c>
-      <c r="D54" s="3" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>BusinessTrip Settlement</v>
-      </c>
-      <c r="F54" s="17">
-        <f t="shared" si="8"/>
+      <c r="C54" s="11" t="str">
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</v>
+      </c>
+      <c r="D54" s="11" t="str">
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Stock Opname Summary</v>
+      </c>
+      <c r="F54" s="20">
+        <f t="shared" si="0"/>
         <v>97000000000053</v>
       </c>
       <c r="H54" s="4"/>
@@ -4079,53 +4292,51 @@
       </c>
       <c r="J54" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>20</v>
-      </c>
+        <v>ReportStockOpnameSummary</v>
+      </c>
+      <c r="K54" s="19"/>
       <c r="M54" s="6">
         <f t="shared" si="6"/>
         <v>256000000000053</v>
       </c>
       <c r="O54" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000053, 'Execute', 'Execute', 'BusinessTripSettlement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000053, 'ReportStockOpnameSummary', 'Execute', null);</v>
       </c>
       <c r="P54" s="1"/>
       <c r="Q54" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000053'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripSettlement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000053'::varchar,'key', 'ReportStockOpnameSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="55" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="9">
+      <c r="B55" s="7">
         <f t="shared" si="2"/>
         <v>97000000000054</v>
       </c>
-      <c r="C55" s="11" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
-      </c>
-      <c r="D55" s="11" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report BusinessTrip Settlement Summary</v>
-      </c>
-      <c r="F55" s="20">
-        <f t="shared" si="8"/>
+      <c r="C55" s="3" t="str">
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Transaction</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Advance Request</v>
+      </c>
+      <c r="F55" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000054</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="11" t="str">
+      <c r="H55" s="4"/>
+      <c r="I55" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J55" s="11" t="str">
+      <c r="J55" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportBusinessTripSettlementSummary</v>
-      </c>
-      <c r="K55" s="19" t="s">
-        <v>19</v>
+        <v>Execute</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" si="6"/>
@@ -4133,12 +4344,12 @@
       </c>
       <c r="O55" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000054, 'ReportBusinessTripSettlementSummary', 'Execute', 'ReportBusinessTripSettlementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000054, 'Execute', 'Execute', 'AdvanceRequest?var=1');</v>
       </c>
       <c r="P55" s="1"/>
       <c r="Q55" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000054'::varchar,'key', 'ReportBusinessTripSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripSettlementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000054'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceRequest?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="56" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4147,15 +4358,15 @@
         <v>97000000000055</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="D56" s="3" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Supplier</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Advance Summary</v>
       </c>
       <c r="F56" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000055</v>
       </c>
       <c r="H56" s="4"/>
@@ -4165,10 +4376,10 @@
       </c>
       <c r="J56" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>ReportAdvanceSummary</v>
       </c>
       <c r="K56" s="18" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M56" s="6">
         <f t="shared" si="6"/>
@@ -4176,12 +4387,12 @@
       </c>
       <c r="O56" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000055, 'Execute', 'Execute', 'Supplier');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000055, 'ReportAdvanceSummary', 'Execute', 'ReportAdvanceSummary');</v>
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000055'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Supplier'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000055'::varchar,'key', 'ReportAdvanceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="57" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4190,15 +4401,15 @@
         <v>97000000000056</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D57" s="3" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Purchase Requisition</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="F57" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000056</v>
       </c>
       <c r="H57" s="4"/>
@@ -4208,10 +4419,10 @@
       </c>
       <c r="J57" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
+        <v>ReportAdvancetoAdvanceSettlement</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" si="6"/>
@@ -4219,12 +4430,12 @@
       </c>
       <c r="O57" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000056, 'Execute', 'Execute', 'PurchaseRequisition?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000056, 'ReportAdvancetoAdvanceSettlement', 'Execute', 'ReportAdvanceToASF');</v>
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000056'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseRequisition?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000056'::varchar,'key', 'ReportAdvancetoAdvanceSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceToASF'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="58" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4233,15 +4444,15 @@
         <v>97000000000057</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="D58" s="3" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Purchase Requisition Summary</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>AdvanceSettlement</v>
       </c>
       <c r="F58" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000057</v>
       </c>
       <c r="H58" s="4"/>
@@ -4251,10 +4462,10 @@
       </c>
       <c r="J58" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportPurchaseRequisitionSummary</v>
+        <v>Execute</v>
       </c>
       <c r="K58" s="18" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="6"/>
@@ -4262,12 +4473,12 @@
       </c>
       <c r="O58" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000057, 'ReportPurchaseRequisitionSummary', 'Execute', 'ReportPurchaseRequisitionSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000057, 'Execute', 'Execute', 'AdvanceSettlement?var=1');</v>
       </c>
       <c r="P58" s="1"/>
       <c r="Q58" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000057'::varchar,'key', 'ReportPurchaseRequisitionSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000057'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AdvanceSettlement?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="59" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4276,15 +4487,15 @@
         <v>97000000000058</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D59" s="3" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Advance Settlement Summary</v>
       </c>
       <c r="F59" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000058</v>
       </c>
       <c r="H59" s="4"/>
@@ -4294,10 +4505,10 @@
       </c>
       <c r="J59" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportPurchaseRequisitionToPurchaseOrder</v>
+        <v>ReportAdvanceSettlementSummary</v>
       </c>
       <c r="K59" s="18" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" si="6"/>
@@ -4305,12 +4516,12 @@
       </c>
       <c r="O59" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000058, 'ReportPurchaseRequisitionToPurchaseOrder', 'Execute', 'ReportPurchaseRequisitionToPurchaseOrder');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000058, 'ReportAdvanceSettlementSummary', 'Execute', 'ReportAdvanceSettlementSummary');</v>
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000058'::varchar,'key', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000058'::varchar,'key', 'ReportAdvanceSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAdvanceSettlementSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="60" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4319,15 +4530,15 @@
         <v>97000000000059</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="D60" s="3" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Purchase Order</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>BusinessTrip Request</v>
       </c>
       <c r="F60" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000059</v>
       </c>
       <c r="H60" s="4"/>
@@ -4340,7 +4551,7 @@
         <v>Execute</v>
       </c>
       <c r="K60" s="18" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M60" s="6">
         <f t="shared" si="6"/>
@@ -4348,12 +4559,12 @@
       </c>
       <c r="O60" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000059, 'Execute', 'Execute', 'PurchaseOrder?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000059, 'Execute', 'Execute', 'BusinessTripRequest?var=1');</v>
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000059'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseOrder?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000059'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripRequest?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="61" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4362,15 +4573,15 @@
         <v>97000000000060</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="D61" s="3" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Report Purchase Order Summary</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="F61" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000060</v>
       </c>
       <c r="H61" s="4"/>
@@ -4380,10 +4591,10 @@
       </c>
       <c r="J61" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>ReportPurchaseOrderSummary</v>
+        <v>ReportBusinessTripRequestSummary</v>
       </c>
       <c r="K61" s="18" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M61" s="6">
         <f t="shared" si="6"/>
@@ -4391,42 +4602,42 @@
       </c>
       <c r="O61" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000060, 'ReportPurchaseOrderSummary', 'Execute', 'ReportPurchaseOrderSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000060, 'ReportBusinessTripRequestSummary', 'Execute', 'ReportBusinessTripRequestSummary');</v>
       </c>
       <c r="P61" s="1"/>
       <c r="Q61" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000060'::varchar,'key', 'ReportPurchaseOrderSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseOrderSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000060'::varchar,'key', 'ReportBusinessTripRequestSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripRequestSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="62" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="9">
+      <c r="B62" s="7">
         <f t="shared" si="2"/>
         <v>97000000000061</v>
       </c>
-      <c r="C62" s="11" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
-      </c>
-      <c r="D62" s="11" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Purchase Order to Account Payable</v>
-      </c>
-      <c r="F62" s="20">
-        <f t="shared" si="8"/>
+      <c r="C62" s="3" t="str">
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
+      </c>
+      <c r="F62" s="17">
+        <f t="shared" si="0"/>
         <v>97000000000061</v>
       </c>
-      <c r="H62" s="14"/>
-      <c r="I62" s="11" t="str">
+      <c r="H62" s="4"/>
+      <c r="I62" s="3" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J62" s="11" t="str">
+      <c r="J62" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>PurchaseOrdertoAccountPayable</v>
-      </c>
-      <c r="K62" s="19" t="s">
-        <v>45</v>
+        <v>ReportBusinessTriptoBusinessTripSettlement</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="M62" s="6">
         <f t="shared" si="6"/>
@@ -4434,12 +4645,12 @@
       </c>
       <c r="O62" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000061, 'PurchaseOrdertoAccountPayable', 'Execute', 'ReportPOtoAP');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000061, 'ReportBusinessTriptoBusinessTripSettlement', 'Execute', 'ReportBusinessTripToBSF');</v>
       </c>
       <c r="P62" s="1"/>
       <c r="Q62" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000061'::varchar,'key', 'PurchaseOrdertoAccountPayable'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPOtoAP'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000061'::varchar,'key', 'ReportBusinessTriptoBusinessTripSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripToBSF'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="63" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4448,15 +4659,15 @@
         <v>97000000000062</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Bank.Transaction</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="D63" s="3" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Bank</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>BusinessTrip Settlement</v>
       </c>
       <c r="F63" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000062</v>
       </c>
       <c r="H63" s="4"/>
@@ -4468,36 +4679,38 @@
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K63" s="18"/>
+      <c r="K63" s="18" t="s">
+        <v>18</v>
+      </c>
       <c r="M63" s="6">
         <f t="shared" si="6"/>
         <v>256000000000062</v>
       </c>
       <c r="O63" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000062, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000062, 'Execute', 'Execute', 'BusinessTripSettlement?var=1');</v>
       </c>
       <c r="P63" s="1"/>
       <c r="Q63" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000062'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000062'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'BusinessTripSettlement?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="64" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="7">
+      <c r="B64" s="9">
         <f t="shared" si="2"/>
         <v>97000000000063</v>
       </c>
-      <c r="C64" s="3" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.BankAccount.Transaction</v>
-      </c>
-      <c r="D64" s="3" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Bank Account</v>
-      </c>
-      <c r="F64" s="17">
-        <f t="shared" si="8"/>
+      <c r="C64" s="11" t="str">
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+      </c>
+      <c r="D64" s="11" t="str">
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report BusinessTrip Settlement Summary</v>
+      </c>
+      <c r="F64" s="20">
+        <f t="shared" si="0"/>
         <v>97000000000063</v>
       </c>
       <c r="H64" s="4"/>
@@ -4507,21 +4720,23 @@
       </c>
       <c r="J64" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Execute</v>
-      </c>
-      <c r="K64" s="18"/>
+        <v>ReportBusinessTripSettlementSummary</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="M64" s="6">
         <f t="shared" si="6"/>
         <v>256000000000063</v>
       </c>
       <c r="O64" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000063, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000063, 'ReportBusinessTripSettlementSummary', 'Execute', 'ReportBusinessTripSettlementSummary');</v>
       </c>
       <c r="P64" s="1"/>
       <c r="Q64" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000063'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000063'::varchar,'key', 'ReportBusinessTripSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportBusinessTripSettlementSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="65" spans="2:17" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -4530,39 +4745,41 @@
         <v>97000000000064</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="D65" s="3" t="str">
-        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Currency</v>
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Supplier</v>
       </c>
       <c r="F65" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="0"/>
         <v>97000000000064</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="3" t="str">
-        <f t="shared" ref="I65:I98" si="9">IF(EXACT(F65, ""), "", IF(EXACT(H65, ""), "Execute", H65))</f>
+        <f t="shared" ref="I65:I98" si="8">IF(EXACT(F65, ""), "", IF(EXACT(H65, ""), "Execute", H65))</f>
         <v>Execute</v>
       </c>
       <c r="J65" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K65" s="18"/>
+      <c r="K65" s="18" t="s">
+        <v>69</v>
+      </c>
       <c r="M65" s="6">
         <f t="shared" si="6"/>
         <v>256000000000064</v>
       </c>
       <c r="O65" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000064, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000064, 'Execute', 'Execute', 'Supplier?var=1');</v>
       </c>
       <c r="P65" s="1"/>
       <c r="Q65" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000064'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000064'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Supplier?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="66" spans="2:17" x14ac:dyDescent="0.2">
@@ -4571,20 +4788,20 @@
         <v>97000000000065</v>
       </c>
       <c r="C66" s="3" t="str">
-        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.SupplierCategory.Transaction</v>
       </c>
       <c r="D66" s="3" t="str">
-        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Exchange Rate</v>
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Supplier Category</v>
       </c>
       <c r="F66" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F66:F98" si="9">IF(EXACT(B66, ""), F65, B66)</f>
         <v>97000000000065</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J66" s="3" t="str">
@@ -4593,57 +4810,61 @@
 )</f>
         <v>Execute</v>
       </c>
-      <c r="K66" s="18"/>
+      <c r="K66" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="M66" s="6">
         <f t="shared" si="6"/>
         <v>256000000000065</v>
       </c>
       <c r="O66" s="15" t="str">
         <f t="shared" si="4"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000065, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000065, 'Execute', 'Execute', 'CategorySupplier?var=1');</v>
       </c>
       <c r="Q66" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000065'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000065'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CategorySupplier?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B67" s="7">
-        <f t="shared" ref="B67:B98" si="11">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
+        <f t="shared" ref="B67:B119" si="11">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
         <v>97000000000066</v>
       </c>
       <c r="C67" s="3" t="str">
-        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</v>
       </c>
       <c r="D67" s="3" t="str">
-        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Exchange Rate Summary</v>
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Supplier Sub Category</v>
       </c>
       <c r="F67" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000066</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J67" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>ExchangeRateSummary</v>
-      </c>
-      <c r="K67" s="18"/>
+        <v>Execute</v>
+      </c>
+      <c r="K67" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="M67" s="6">
         <f t="shared" si="6"/>
         <v>256000000000066</v>
       </c>
       <c r="O67" s="15" t="str">
-        <f t="shared" ref="O67:O98" si="12">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F67, ""), "null", CONCATENATE($F67)), ", ", IF(EXACT($F67, ""),"null", CONCATENATE("'", $J67, "'")), ", ", IF(EXACT($F67, ""), "null", CONCATENATE("'", $I67, "'")), ", ", IF(EXACT($K67, ""), "null", CONCATENATE("'", $K67, "'")), ");")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000066, 'ExchangeRateSummary', 'Execute', null);</v>
+        <f t="shared" ref="O67:O116" si="12">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuAction_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($F67, ""), "null", CONCATENATE($F67)), ", ", IF(EXACT($F67, ""),"null", CONCATENATE("'", $J67, "'")), ", ", IF(EXACT($F67, ""), "null", CONCATENATE("'", $I67, "'")), ", ", IF(EXACT($K67, ""), "null", CONCATENATE("'", $K67, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000066, 'Execute', 'Execute', 'SpecializationSupplier?var=1');</v>
       </c>
       <c r="Q67" s="1" t="str">
-        <f t="shared" ref="Q67:Q98" si="13">CONCATENATE(
+        <f t="shared" ref="Q67:Q116" si="13">CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -4659,7 +4880,7 @@
 "'caption', ", IF(EXACT($I67, ""), "null", CONCATENATE("'", SUBSTITUTE($I67, "'", "\'"), "'")), "::varchar,",
 "'URLPath', ", IF(EXACT($K67, ""), "null", CONCATENATE("'", SUBSTITUTE($K67, "'", "\'"), "'")), "::varchar",
 ")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000066'::varchar,'key', 'ExchangeRateSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000066'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'SpecializationSupplier?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.2">
@@ -4668,38 +4889,40 @@
         <v>97000000000067</v>
       </c>
       <c r="C68" s="3" t="str">
-        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="D68" s="3" t="str">
-        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Payment Term</v>
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Purchase Requisition</v>
       </c>
       <c r="F68" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000067</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J68" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K68" s="18"/>
+      <c r="K68" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="M68" s="6">
         <f t="shared" ref="M68:M98" si="14">IF(ISNUMBER(M67), M67+1, 256000000000001)</f>
         <v>256000000000067</v>
       </c>
       <c r="O68" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000067, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000067, 'Execute', 'Execute', 'PurchaseRequisition?var=1');</v>
       </c>
       <c r="Q68" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000067'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000067'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseRequisition?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.2">
@@ -4708,38 +4931,40 @@
         <v>97000000000068</v>
       </c>
       <c r="C69" s="3" t="str">
-        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.General.MasterData.Period.Transaction</v>
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="D69" s="3" t="str">
-        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Period</v>
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="F69" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000068</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J69" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>Execute</v>
-      </c>
-      <c r="K69" s="18"/>
+        <v>ReportPurchaseRequisitionSummary</v>
+      </c>
+      <c r="K69" s="18" t="s">
+        <v>21</v>
+      </c>
       <c r="M69" s="6">
         <f t="shared" si="14"/>
         <v>256000000000068</v>
       </c>
       <c r="O69" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000068, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000068, 'ReportPurchaseRequisitionSummary', 'Execute', 'ReportPurchaseRequisitionSummary');</v>
       </c>
       <c r="Q69" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000068'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000068'::varchar,'key', 'ReportPurchaseRequisitionSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.2">
@@ -4748,38 +4973,40 @@
         <v>97000000000069</v>
       </c>
       <c r="C70" s="3" t="str">
-        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="D70" s="3" t="str">
-        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Asset Category</v>
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="F70" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000069</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J70" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>Execute</v>
-      </c>
-      <c r="K70" s="18"/>
+        <v>ReportPurchaseRequisitionToPurchaseOrder</v>
+      </c>
+      <c r="K70" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="M70" s="6">
         <f t="shared" si="14"/>
         <v>256000000000069</v>
       </c>
       <c r="O70" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000069, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000069, 'ReportPurchaseRequisitionToPurchaseOrder', 'Execute', 'ReportPurchaseRequisitionToPurchaseOrder');</v>
       </c>
       <c r="Q70" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000069'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000069'::varchar,'key', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseRequisitionToPurchaseOrder'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.2">
@@ -4788,38 +5015,40 @@
         <v>97000000000070</v>
       </c>
       <c r="C71" s="3" t="str">
-        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="D71" s="3" t="str">
-        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Chart of Account</v>
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Purchase Order</v>
       </c>
       <c r="F71" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000070</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J71" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K71" s="18"/>
+      <c r="K71" s="18" t="s">
+        <v>25</v>
+      </c>
       <c r="M71" s="6">
         <f t="shared" si="14"/>
         <v>256000000000070</v>
       </c>
       <c r="O71" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000070, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000070, 'Execute', 'Execute', 'PurchaseOrder?var=1');</v>
       </c>
       <c r="Q71" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000070'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000070'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'PurchaseOrder?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.2">
@@ -4828,78 +5057,84 @@
         <v>97000000000071</v>
       </c>
       <c r="C72" s="3" t="str">
-        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="D72" s="3" t="str">
-        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Depreciation Method</v>
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Purchase Order Summary</v>
       </c>
       <c r="F72" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000071</v>
       </c>
+      <c r="G72" s="16"/>
       <c r="H72" s="4"/>
       <c r="I72" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J72" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>Execute</v>
-      </c>
-      <c r="K72" s="18"/>
+        <v>ReportPurchaseOrderSummary</v>
+      </c>
+      <c r="K72" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="M72" s="6">
         <f t="shared" si="14"/>
         <v>256000000000071</v>
       </c>
       <c r="O72" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000071, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000071, 'ReportPurchaseOrderSummary', 'Execute', 'ReportPurchaseOrderSummary');</v>
       </c>
       <c r="Q72" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000071'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000071'::varchar,'key', 'ReportPurchaseOrderSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPurchaseOrderSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B73" s="7">
+      <c r="B73" s="9">
         <f t="shared" si="11"/>
         <v>97000000000072</v>
       </c>
-      <c r="C73" s="3" t="str">
-        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
-      </c>
-      <c r="D73" s="3" t="str">
-        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Depreciation Rate Years</v>
-      </c>
-      <c r="F73" s="17">
-        <f t="shared" si="8"/>
+      <c r="C73" s="11" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="D73" s="11" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Report Purchase Order to Account Payable Summary</v>
+      </c>
+      <c r="F73" s="20">
+        <f t="shared" si="9"/>
         <v>97000000000072</v>
       </c>
+      <c r="G73" s="16"/>
       <c r="H73" s="4"/>
       <c r="I73" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J73" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>Execute</v>
-      </c>
-      <c r="K73" s="18"/>
+        <v>ReportPurchaseOrdertoAccountPayableSummary</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>41</v>
+      </c>
       <c r="M73" s="6">
         <f t="shared" si="14"/>
         <v>256000000000072</v>
       </c>
       <c r="O73" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000072, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000072, 'ReportPurchaseOrdertoAccountPayableSummary', 'Execute', 'ReportPOtoAP');</v>
       </c>
       <c r="Q73" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000072'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000072'::varchar,'key', 'ReportPurchaseOrdertoAccountPayableSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPOtoAP'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.2">
@@ -4908,20 +5143,20 @@
         <v>97000000000073</v>
       </c>
       <c r="C74" s="3" t="str">
-        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="D74" s="3" t="str">
-        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Value Added Tax</v>
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Bank</v>
       </c>
       <c r="F74" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000073</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J74" s="3" t="str">
@@ -4948,20 +5183,20 @@
         <v>97000000000074</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="D75" s="3" t="str">
-        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>General Journal</v>
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Bank Account</v>
       </c>
       <c r="F75" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000074</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J75" s="3" t="str">
@@ -4988,40 +5223,38 @@
         <v>97000000000075</v>
       </c>
       <c r="C76" s="3" t="str">
-        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Currency.Transaction</v>
       </c>
       <c r="D76" s="3" t="str">
-        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>General Journal Summary</v>
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Currency</v>
       </c>
       <c r="F76" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000075</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J76" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>GeneralJournalSummary</v>
-      </c>
-      <c r="K76" s="18" t="s">
-        <v>50</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K76" s="18"/>
       <c r="M76" s="6">
         <f t="shared" si="14"/>
         <v>256000000000075</v>
       </c>
       <c r="O76" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000075, 'GeneralJournalSummary', 'Execute', 'ReportGeneralJournalSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000075, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q76" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000075'::varchar,'key', 'GeneralJournalSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportGeneralJournalSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000075'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="77" spans="2:17" x14ac:dyDescent="0.2">
@@ -5030,40 +5263,38 @@
         <v>97000000000076</v>
       </c>
       <c r="C77" s="3" t="str">
-        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
       </c>
       <c r="D77" s="3" t="str">
-        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Reimbursement</v>
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Exchange Rate</v>
       </c>
       <c r="F77" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97000000000076</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J77" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K77" s="18" t="s">
-        <v>29</v>
-      </c>
+      <c r="K77" s="18"/>
       <c r="M77" s="6">
         <f t="shared" si="14"/>
         <v>256000000000076</v>
       </c>
       <c r="O77" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000076, 'Execute', 'Execute', 'Reimbursement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000076, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q77" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000076'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Reimbursement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000076'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="78" spans="2:17" x14ac:dyDescent="0.2">
@@ -5072,40 +5303,38 @@
         <v>97000000000077</v>
       </c>
       <c r="C78" s="3" t="str">
-        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
       </c>
       <c r="D78" s="3" t="str">
-        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Reimbursement Summary</v>
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Exchange Rate Summary</v>
       </c>
       <c r="F78" s="17">
-        <f t="shared" ref="F78:F98" si="15">IF(EXACT(B78, ""), F77, B78)</f>
+        <f t="shared" si="9"/>
         <v>97000000000077</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J78" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>ReimbursementSummary</v>
-      </c>
-      <c r="K78" s="18" t="s">
-        <v>30</v>
-      </c>
+        <v>ExchangeRateSummary</v>
+      </c>
+      <c r="K78" s="18"/>
       <c r="M78" s="6">
         <f t="shared" si="14"/>
         <v>256000000000077</v>
       </c>
       <c r="O78" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000077, 'ReimbursementSummary', 'Execute', 'ReportReimbursementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000077, 'ExchangeRateSummary', 'Execute', null);</v>
       </c>
       <c r="Q78" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000077'::varchar,'key', 'ReimbursementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportReimbursementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000077'::varchar,'key', 'ExchangeRateSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="79" spans="2:17" x14ac:dyDescent="0.2">
@@ -5114,40 +5343,38 @@
         <v>97000000000078</v>
       </c>
       <c r="C79" s="3" t="str">
-        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
       </c>
       <c r="D79" s="3" t="str">
-        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Reimbursement to Debit Note</v>
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Payment Term</v>
       </c>
       <c r="F79" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000078</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J79" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>ReimbursementtoDebitNote</v>
-      </c>
-      <c r="K79" s="18" t="s">
-        <v>33</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K79" s="18"/>
       <c r="M79" s="6">
         <f t="shared" si="14"/>
         <v>256000000000078</v>
       </c>
       <c r="O79" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000078, 'ReimbursementtoDebitNote', 'Execute', 'ReportRemToDN');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000078, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q79" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000078'::varchar,'key', 'ReimbursementtoDebitNote'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportRemToDN'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000078'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="80" spans="2:17" x14ac:dyDescent="0.2">
@@ -5156,40 +5383,38 @@
         <v>97000000000079</v>
       </c>
       <c r="C80" s="3" t="str">
-        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.General.MasterData.Period.Transaction</v>
       </c>
       <c r="D80" s="3" t="str">
-        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Debit Note</v>
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Period</v>
       </c>
       <c r="F80" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000079</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J80" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K80" s="18" t="s">
-        <v>31</v>
-      </c>
+      <c r="K80" s="18"/>
       <c r="M80" s="6">
         <f t="shared" si="14"/>
         <v>256000000000079</v>
       </c>
       <c r="O80" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000079, 'Execute', 'Execute', 'DebitNote?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000079, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q80" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000079'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'DebitNote?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000079'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="81" spans="2:17" x14ac:dyDescent="0.2">
@@ -5198,40 +5423,38 @@
         <v>97000000000080</v>
       </c>
       <c r="C81" s="3" t="str">
-        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
       </c>
       <c r="D81" s="3" t="str">
-        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Debit Note Summary</v>
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Asset Category</v>
       </c>
       <c r="F81" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000080</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J81" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>DebitNoteSummary</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>32</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K81" s="18"/>
       <c r="M81" s="6">
         <f t="shared" si="14"/>
         <v>256000000000080</v>
       </c>
       <c r="O81" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000080, 'DebitNoteSummary', 'Execute', 'ReportDebitNoteSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000080, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q81" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000080'::varchar,'key', 'DebitNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDebitNoteSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000080'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="82" spans="2:17" x14ac:dyDescent="0.2">
@@ -5240,40 +5463,38 @@
         <v>97000000000081</v>
       </c>
       <c r="C82" s="3" t="str">
-        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
       </c>
       <c r="D82" s="3" t="str">
-        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Credit Note</v>
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Chart of Account</v>
       </c>
       <c r="F82" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000081</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J82" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K82" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="K82" s="18"/>
       <c r="M82" s="6">
         <f t="shared" si="14"/>
         <v>256000000000081</v>
       </c>
       <c r="O82" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000081, 'Execute', 'Execute', 'CreditNote?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000081, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q82" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000081'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CreditNote?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000081'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="83" spans="2:17" x14ac:dyDescent="0.2">
@@ -5282,40 +5503,38 @@
         <v>97000000000082</v>
       </c>
       <c r="C83" s="3" t="str">
-        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
       </c>
       <c r="D83" s="3" t="str">
-        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Credit Note Summary</v>
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Depreciation Method</v>
       </c>
       <c r="F83" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000082</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J83" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>CreditNoteSummary</v>
-      </c>
-      <c r="K83" s="18" t="s">
-        <v>35</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K83" s="18"/>
       <c r="M83" s="6">
         <f t="shared" si="14"/>
         <v>256000000000082</v>
       </c>
       <c r="O83" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000082, 'CreditNoteSummary', 'Execute', 'ReportCreditNoteSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000082, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q83" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000082'::varchar,'key', 'CreditNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportCreditNoteSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000082'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="84" spans="2:17" x14ac:dyDescent="0.2">
@@ -5324,40 +5543,38 @@
         <v>97000000000083</v>
       </c>
       <c r="C84" s="3" t="str">
-        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Transaction</v>
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
       </c>
       <c r="D84" s="3" t="str">
-        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Loan</v>
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Depreciation Rate Years</v>
       </c>
       <c r="F84" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000083</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J84" s="3" t="str">
         <f t="shared" si="10"/>
         <v>Execute</v>
       </c>
-      <c r="K84" s="18" t="s">
-        <v>36</v>
-      </c>
+      <c r="K84" s="18"/>
       <c r="M84" s="6">
         <f t="shared" si="14"/>
         <v>256000000000083</v>
       </c>
       <c r="O84" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000083, 'Execute', 'Execute', 'Loan?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000083, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q84" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000083'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Loan?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000083'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="85" spans="2:17" x14ac:dyDescent="0.2">
@@ -5366,40 +5583,38 @@
         <v>97000000000084</v>
       </c>
       <c r="C85" s="3" t="str">
-        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Report.DataList</v>
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
       </c>
       <c r="D85" s="3" t="str">
-        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Loan Summary</v>
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Value Added Tax</v>
       </c>
       <c r="F85" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000084</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J85" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>LoanSummary</v>
-      </c>
-      <c r="K85" s="18" t="s">
-        <v>37</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K85" s="18"/>
       <c r="M85" s="6">
         <f t="shared" si="14"/>
         <v>256000000000084</v>
       </c>
       <c r="O85" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000084, 'LoanSummary', 'Execute', 'ReportLoanSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000084, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q85" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000084'::varchar,'key', 'LoanSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000084'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="86" spans="2:17" x14ac:dyDescent="0.2">
@@ -5408,40 +5623,38 @@
         <v>97000000000085</v>
       </c>
       <c r="C86" s="3" t="str">
-        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
       </c>
       <c r="D86" s="3" t="str">
-        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Loan to Loan Settlement</v>
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Balance Sheet</v>
       </c>
       <c r="F86" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000085</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J86" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>LoantoLoanSettlement</v>
-      </c>
-      <c r="K86" s="18" t="s">
-        <v>40</v>
-      </c>
+        <v>BalanceSheet</v>
+      </c>
+      <c r="K86" s="18"/>
       <c r="M86" s="6">
         <f t="shared" si="14"/>
         <v>256000000000085</v>
       </c>
       <c r="O86" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000085, 'LoantoLoanSettlement', 'Execute', 'ReportLoantoLoanSettlement');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000085, 'BalanceSheet', 'Execute', null);</v>
       </c>
       <c r="Q86" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000085'::varchar,'key', 'LoantoLoanSettlement'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoantoLoanSettlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000085'::varchar,'key', 'BalanceSheet'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="87" spans="2:17" x14ac:dyDescent="0.2">
@@ -5450,20 +5663,20 @@
         <v>97000000000086</v>
       </c>
       <c r="C87" s="3" t="str">
-        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
       </c>
       <c r="D87" s="3" t="str">
-        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Loan Settlement</v>
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>General Journal</v>
       </c>
       <c r="F87" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000086</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J87" s="3" t="str">
@@ -5471,7 +5684,7 @@
         <v>Execute</v>
       </c>
       <c r="K87" s="18" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M87" s="6">
         <f t="shared" si="14"/>
@@ -5479,11 +5692,11 @@
       </c>
       <c r="O87" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000086, 'Execute', 'Execute', 'LoanSettlement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000086, 'Execute', 'Execute', 'GeneralJournal?var=1');</v>
       </c>
       <c r="Q87" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000086'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'LoanSettlement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000086'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'GeneralJournal?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="88" spans="2:17" x14ac:dyDescent="0.2">
@@ -5492,28 +5705,28 @@
         <v>97000000000087</v>
       </c>
       <c r="C88" s="3" t="str">
-        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
       </c>
       <c r="D88" s="3" t="str">
-        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Loan Settlement Summary</v>
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>General Journal Summary</v>
       </c>
       <c r="F88" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000087</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J88" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>LoanSettlementSummary</v>
+        <v>GeneralJournalSummary</v>
       </c>
       <c r="K88" s="18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M88" s="6">
         <f t="shared" si="14"/>
@@ -5521,11 +5734,11 @@
       </c>
       <c r="O88" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000087, 'LoanSettlementSummary', 'Execute', 'ReportLoanSettlementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000087, 'GeneralJournalSummary', 'Execute', 'ReportGeneralJournalSummary');</v>
       </c>
       <c r="Q88" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000087'::varchar,'key', 'LoanSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSettlementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000087'::varchar,'key', 'GeneralJournalSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportGeneralJournalSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="89" spans="2:17" x14ac:dyDescent="0.2">
@@ -5534,28 +5747,28 @@
         <v>97000000000088</v>
       </c>
       <c r="C89" s="3" t="str">
-        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
       </c>
       <c r="D89" s="3" t="str">
-        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Cash &amp; Bank</v>
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>General Ledger Summary</v>
       </c>
       <c r="F89" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000088</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J89" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>Execute</v>
+        <v>GeneralLedgerSummary</v>
       </c>
       <c r="K89" s="18" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M89" s="6">
         <f t="shared" si="14"/>
@@ -5563,11 +5776,11 @@
       </c>
       <c r="O89" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000088, 'Execute', 'Execute', 'Journal?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000088, 'GeneralLedgerSummary', 'Execute', 'ReportGeneralLedger');</v>
       </c>
       <c r="Q89" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000088'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Journal?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000088'::varchar,'key', 'GeneralLedgerSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportGeneralLedger'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.2">
@@ -5576,42 +5789,40 @@
         <v>97000000000089</v>
       </c>
       <c r="C90" s="3" t="str">
-        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
       </c>
       <c r="D90" s="3" t="str">
-        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Cash &amp; Bank Summary</v>
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Profit Loss Summary</v>
       </c>
       <c r="F90" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000089</v>
       </c>
       <c r="H90" s="4"/>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J90" s="3" t="str">
         <f>IF(EXACT(F90, ""), "",
 SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C90)), D90, IF(EXACT(H90, ""), "Execute", H90)), " ", ""), "&amp;", "")
 )</f>
-        <v>CashBankSummary</v>
-      </c>
-      <c r="K90" s="18" t="s">
-        <v>42</v>
-      </c>
+        <v>ProfitLossSummary</v>
+      </c>
+      <c r="K90" s="18"/>
       <c r="M90" s="6">
         <f t="shared" si="14"/>
         <v>256000000000089</v>
       </c>
       <c r="O90" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000089, 'CashBankSummary', 'Execute', 'ReportPaymentJournal');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000089, 'ProfitLossSummary', 'Execute', null);</v>
       </c>
       <c r="Q90" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000089'::varchar,'key', 'CashBankSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPaymentJournal'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000089'::varchar,'key', 'ProfitLossSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="91" spans="2:17" x14ac:dyDescent="0.2">
@@ -5620,30 +5831,30 @@
         <v>97000000000090</v>
       </c>
       <c r="C91" s="3" t="str">
-        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
       </c>
       <c r="D91" s="3" t="str">
-        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Account Payable</v>
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Cash &amp; Bank</v>
       </c>
       <c r="F91" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000090</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J91" s="3" t="str">
-        <f t="shared" ref="J91:J98" si="16">IF(EXACT(F91, ""), "",
+        <f t="shared" ref="J91:J98" si="15">IF(EXACT(F91, ""), "",
 SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C91)), D91, IF(EXACT(H91, ""), "Execute", H91)), " ", ""), "&amp;", "")
 )</f>
         <v>Execute</v>
       </c>
       <c r="K91" s="18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M91" s="6">
         <f t="shared" si="14"/>
@@ -5651,11 +5862,11 @@
       </c>
       <c r="O91" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000090, 'Execute', 'Execute', 'AccountPayable?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000090, 'Execute', 'Execute', 'Journal?var=1');</v>
       </c>
       <c r="Q91" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000090'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AccountPayable?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000090'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Journal?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="92" spans="2:17" x14ac:dyDescent="0.2">
@@ -5664,28 +5875,28 @@
         <v>97000000000091</v>
       </c>
       <c r="C92" s="3" t="str">
-        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
       </c>
       <c r="D92" s="3" t="str">
-        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Account Payable Summary</v>
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Cash &amp; Bank Summary</v>
       </c>
       <c r="F92" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000091</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J92" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>AccountPayableSummary</v>
+        <f t="shared" si="15"/>
+        <v>CashBankSummary</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M92" s="6">
         <f t="shared" si="14"/>
@@ -5693,11 +5904,11 @@
       </c>
       <c r="O92" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000091, 'AccountPayableSummary', 'Execute', 'ReportAccountPayableSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000091, 'CashBankSummary', 'Execute', 'ReportPaymentJournal');</v>
       </c>
       <c r="Q92" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000091'::varchar,'key', 'AccountPayableSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAccountPayableSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000091'::varchar,'key', 'CashBankSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportPaymentJournal'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="93" spans="2:17" x14ac:dyDescent="0.2">
@@ -5706,38 +5917,40 @@
         <v>97000000000092</v>
       </c>
       <c r="C93" s="3" t="str">
-        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
       </c>
       <c r="D93" s="3" t="str">
-        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sales Invoice</v>
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Credit Note</v>
       </c>
       <c r="F93" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000092</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J93" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Execute</v>
-      </c>
-      <c r="K93" s="18"/>
+        <f t="shared" si="15"/>
+        <v>Execute</v>
+      </c>
+      <c r="K93" s="18" t="s">
+        <v>30</v>
+      </c>
       <c r="M93" s="6">
         <f t="shared" si="14"/>
         <v>256000000000092</v>
       </c>
       <c r="O93" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000092, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000092, 'Execute', 'Execute', 'CreditNote?var=1');</v>
       </c>
       <c r="Q93" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000092'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000092'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CreditNote?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="94" spans="2:17" x14ac:dyDescent="0.2">
@@ -5746,28 +5959,28 @@
         <v>97000000000093</v>
       </c>
       <c r="C94" s="3" t="str">
-        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
       </c>
       <c r="D94" s="3" t="str">
-        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sales Invoice Summary</v>
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Credit Note Summary</v>
       </c>
       <c r="F94" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000093</v>
       </c>
       <c r="H94" s="4"/>
       <c r="I94" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J94" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>SalesInvoiceSummary</v>
+        <f t="shared" si="15"/>
+        <v>CreditNoteSummary</v>
       </c>
       <c r="K94" s="18" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="M94" s="6">
         <f t="shared" si="14"/>
@@ -5775,11 +5988,11 @@
       </c>
       <c r="O94" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000093, 'SalesInvoiceSummary', 'Execute', 'ReportInvoiceSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000093, 'CreditNoteSummary', 'Execute', 'ReportCreditNoteSummary');</v>
       </c>
       <c r="Q94" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000093'::varchar,'key', 'SalesInvoiceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportInvoiceSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000093'::varchar,'key', 'CreditNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportCreditNoteSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="95" spans="2:17" x14ac:dyDescent="0.2">
@@ -5788,40 +6001,38 @@
         <v>97000000000094</v>
       </c>
       <c r="C95" s="3" t="str">
-        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
       </c>
       <c r="D95" s="3" t="str">
-        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Sales Invoice to Credit Note</v>
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Debit Note</v>
       </c>
       <c r="F95" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000094</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J95" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>SalesInvoicetoCreditNote</v>
-      </c>
-      <c r="K95" s="18" t="s">
-        <v>52</v>
-      </c>
+        <f t="shared" si="15"/>
+        <v>Execute</v>
+      </c>
+      <c r="K95" s="18"/>
       <c r="M95" s="6">
         <f t="shared" si="14"/>
         <v>256000000000094</v>
       </c>
       <c r="O95" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000094, 'SalesInvoicetoCreditNote', 'Execute', 'ReportInvoiceToCN');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000094, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q95" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000094'::varchar,'key', 'SalesInvoicetoCreditNote'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportInvoiceToCN'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000094'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="96" spans="2:17" x14ac:dyDescent="0.2">
@@ -5830,38 +6041,40 @@
         <v>97000000000095</v>
       </c>
       <c r="C96" s="3" t="str">
-        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
       </c>
       <c r="D96" s="3" t="str">
-        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Tax Reconciliation</v>
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Debit Note Summary</v>
       </c>
       <c r="F96" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>97000000000095</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
       <c r="J96" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Execute</v>
-      </c>
-      <c r="K96" s="18"/>
+        <f t="shared" si="15"/>
+        <v>DebitNoteSummary</v>
+      </c>
+      <c r="K96" s="18" t="s">
+        <v>28</v>
+      </c>
       <c r="M96" s="6">
         <f t="shared" si="14"/>
         <v>256000000000095</v>
       </c>
       <c r="O96" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000095, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000095, 'DebitNoteSummary', 'Execute', 'ReportDebitNoteSummary');</v>
       </c>
       <c r="Q96" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000095'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000095'::varchar,'key', 'DebitNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportDebitNoteSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="97" spans="2:17" x14ac:dyDescent="0.2">
@@ -5869,81 +6082,669 @@
         <f t="shared" si="11"/>
         <v>97000000000096</v>
       </c>
-      <c r="C97" s="11" t="str">
-        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
-      </c>
-      <c r="D97" s="11" t="str">
-        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Tax Reconciliation Summary</v>
-      </c>
-      <c r="F97" s="20">
+      <c r="C97" s="3" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
+      </c>
+      <c r="D97" s="3" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Fixed Asset</v>
+      </c>
+      <c r="F97" s="17">
+        <f t="shared" si="9"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="H97" s="4"/>
+      <c r="I97" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J97" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>97000000000096</v>
-      </c>
-      <c r="H97" s="14"/>
-      <c r="I97" s="11" t="str">
-        <f t="shared" si="9"/>
-        <v>Execute</v>
-      </c>
-      <c r="J97" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>TaxReconciliationSummary</v>
-      </c>
-      <c r="K97" s="19" t="s">
-        <v>53</v>
-      </c>
+        <v>Execute</v>
+      </c>
+      <c r="K97" s="18"/>
       <c r="M97" s="6">
         <f t="shared" si="14"/>
         <v>256000000000096</v>
       </c>
       <c r="O97" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000096, 'TaxReconciliationSummary', 'Execute', 'ReportTaxReconSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000096, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q97" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000096'::varchar,'key', 'TaxReconciliationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTaxReconSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000096'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="98" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B98" s="9">
+      <c r="B98" s="7">
         <f t="shared" si="11"/>
         <v>97000000000097</v>
       </c>
-      <c r="C98" s="22" t="str">
-        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1120, 2, FALSE)</f>
-        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
-      </c>
-      <c r="D98" s="22" t="str">
-        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1120, 3, FALSE)</f>
-        <v>Customer</v>
-      </c>
-      <c r="F98" s="23">
+      <c r="C98" s="3" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
+      </c>
+      <c r="D98" s="3" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Fixed Asset Summary</v>
+      </c>
+      <c r="F98" s="17">
+        <f t="shared" si="9"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="H98" s="4"/>
+      <c r="I98" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Execute</v>
+      </c>
+      <c r="J98" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>97000000000097</v>
-      </c>
-      <c r="H98" s="26"/>
-      <c r="I98" s="22" t="str">
-        <f t="shared" si="9"/>
-        <v>Execute</v>
-      </c>
-      <c r="J98" s="22" t="str">
-        <f t="shared" si="16"/>
-        <v>Execute</v>
-      </c>
-      <c r="K98" s="27"/>
+        <v>FixedAssetSummary</v>
+      </c>
+      <c r="K98" s="18"/>
       <c r="M98" s="6">
         <f t="shared" si="14"/>
         <v>256000000000097</v>
       </c>
       <c r="O98" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000097, 'Execute', 'Execute', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000097, 'FixedAssetSummary', 'Execute', null);</v>
       </c>
       <c r="Q98" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000097'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000097'::varchar,'key', 'FixedAssetSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B99" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000098</v>
+      </c>
+      <c r="C99" s="3" t="str">
+        <f>VLOOKUP($B99, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Transaction</v>
+      </c>
+      <c r="D99" s="3" t="str">
+        <f>VLOOKUP($B99, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Loan</v>
+      </c>
+      <c r="F99" s="17">
+        <f t="shared" ref="F99:F117" si="16">IF(EXACT(B99, ""), F98, B99)</f>
+        <v>97000000000098</v>
+      </c>
+      <c r="K99" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M99" s="6">
+        <f>IF(ISNUMBER(M98), M98+1, 256000000000001)</f>
+        <v>256000000000098</v>
+      </c>
+      <c r="O99" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000098, '', '', 'Loan?var=1');</v>
+      </c>
+      <c r="Q99" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000098'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Loan?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B100" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000099</v>
+      </c>
+      <c r="C100" s="3" t="str">
+        <f>VLOOKUP($B100, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      </c>
+      <c r="D100" s="3" t="str">
+        <f>VLOOKUP($B100, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Loan Summary</v>
+      </c>
+      <c r="F100" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000099</v>
+      </c>
+      <c r="K100" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="M100" s="6">
+        <f t="shared" ref="M100:M116" si="17">IF(ISNUMBER(M99), M99+1, 256000000000001)</f>
+        <v>256000000000099</v>
+      </c>
+      <c r="O100" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000099, '', '', 'ReportLoanSummary');</v>
+      </c>
+      <c r="Q100" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000099'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoanSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B101" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000100</v>
+      </c>
+      <c r="C101" s="3" t="str">
+        <f>VLOOKUP($B101, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D101" s="3" t="str">
+        <f>VLOOKUP($B101, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Loan to Loan Settlement Summary</v>
+      </c>
+      <c r="F101" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000100</v>
+      </c>
+      <c r="K101" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M101" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000100</v>
+      </c>
+      <c r="O101" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000100, '', '', 'ReportLoantoLoanSettlement');</v>
+      </c>
+      <c r="Q101" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000100'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoantoLoanSettlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B102" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000101</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <f>VLOOKUP($B102, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="D102" s="3" t="str">
+        <f>VLOOKUP($B102, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="F102" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000101</v>
+      </c>
+      <c r="K102" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M102" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000101</v>
+      </c>
+      <c r="O102" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000101, '', '', 'LoanSettlement?var=1');</v>
+      </c>
+      <c r="Q102" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000101'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'LoanSettlement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B103" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000102</v>
+      </c>
+      <c r="C103" s="3" t="str">
+        <f>VLOOKUP($B103, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D103" s="3" t="str">
+        <f>VLOOKUP($B103, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="F103" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000102</v>
+      </c>
+      <c r="K103" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M103" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000102</v>
+      </c>
+      <c r="O103" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000102, '', '', 'ReportLoanSettlementSummary');</v>
+      </c>
+      <c r="Q103" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000102'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoanSettlementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B104" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000103</v>
+      </c>
+      <c r="C104" s="3" t="str">
+        <f>VLOOKUP($B104, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+      </c>
+      <c r="D104" s="3" t="str">
+        <f>VLOOKUP($B104, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Account Payable</v>
+      </c>
+      <c r="F104" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000103</v>
+      </c>
+      <c r="K104" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M104" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000103</v>
+      </c>
+      <c r="O104" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000103, '', '', 'AccountPayable?var=1');</v>
+      </c>
+      <c r="Q104" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000103'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'AccountPayable?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B105" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000104</v>
+      </c>
+      <c r="C105" s="3" t="str">
+        <f>VLOOKUP($B105, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="D105" s="3" t="str">
+        <f>VLOOKUP($B105, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Account Payable Summary</v>
+      </c>
+      <c r="F105" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000104</v>
+      </c>
+      <c r="K105" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="M105" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000104</v>
+      </c>
+      <c r="O105" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000104, '', '', 'ReportAccountPayableSummary');</v>
+      </c>
+      <c r="Q105" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000104'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportAccountPayableSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B106" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000105</v>
+      </c>
+      <c r="C106" s="3" t="str">
+        <f>VLOOKUP($B106, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="D106" s="3" t="str">
+        <f>VLOOKUP($B106, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Reimbursement</v>
+      </c>
+      <c r="F106" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000105</v>
+      </c>
+      <c r="K106" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000105</v>
+      </c>
+      <c r="O106" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000105, '', '', 'Reimbursement?var=1');</v>
+      </c>
+      <c r="Q106" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000105'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Reimbursement?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B107" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000106</v>
+      </c>
+      <c r="C107" s="3" t="str">
+        <f>VLOOKUP($B107, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="D107" s="3" t="str">
+        <f>VLOOKUP($B107, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="F107" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000106</v>
+      </c>
+      <c r="K107" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M107" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000106</v>
+      </c>
+      <c r="O107" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000106, '', '', 'ReportReimbursementSummary');</v>
+      </c>
+      <c r="Q107" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000106'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportReimbursementSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B108" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000107</v>
+      </c>
+      <c r="C108" s="3" t="str">
+        <f>VLOOKUP($B108, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="D108" s="3" t="str">
+        <f>VLOOKUP($B108, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Reimbursement to Debit Note Summary</v>
+      </c>
+      <c r="F108" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000107</v>
+      </c>
+      <c r="K108" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M108" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000107</v>
+      </c>
+      <c r="O108" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000107, '', '', 'ReportRemToDN');</v>
+      </c>
+      <c r="Q108" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000107'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportRemToDN'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B109" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000108</v>
+      </c>
+      <c r="C109" s="3" t="str">
+        <f>VLOOKUP($B109, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+      </c>
+      <c r="D109" s="3" t="str">
+        <f>VLOOKUP($B109, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="F109" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000108</v>
+      </c>
+      <c r="K109" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M109" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000108</v>
+      </c>
+      <c r="O109" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000108, '', '', 'Invoice?var=1');</v>
+      </c>
+      <c r="Q109" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000108'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Invoice?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B110" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000109</v>
+      </c>
+      <c r="C110" s="3" t="str">
+        <f>VLOOKUP($B110, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+      </c>
+      <c r="D110" s="3" t="str">
+        <f>VLOOKUP($B110, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="F110" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000109</v>
+      </c>
+      <c r="K110" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M110" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000109</v>
+      </c>
+      <c r="O110" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000109, '', '', 'ReportInvoiceSummary');</v>
+      </c>
+      <c r="Q110" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000109'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportInvoiceSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B111" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000110</v>
+      </c>
+      <c r="C111" s="3" t="str">
+        <f>VLOOKUP($B111, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+      </c>
+      <c r="D111" s="3" t="str">
+        <f>VLOOKUP($B111, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="F111" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000110</v>
+      </c>
+      <c r="K111" s="18"/>
+      <c r="M111" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000110</v>
+      </c>
+      <c r="O111" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000110, '', '', null);</v>
+      </c>
+      <c r="Q111" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000110'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B112" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000111</v>
+      </c>
+      <c r="C112" s="3" t="str">
+        <f>VLOOKUP($B112, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="D112" s="3" t="str">
+        <f>VLOOKUP($B112, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="F112" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000111</v>
+      </c>
+      <c r="K112" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M112" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000111</v>
+      </c>
+      <c r="O112" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000111, '', '', 'TaxRecon?var=1');</v>
+      </c>
+      <c r="Q112" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000111'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'TaxRecon?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B113" s="9">
+        <f t="shared" si="11"/>
+        <v>97000000000112</v>
+      </c>
+      <c r="C113" s="11" t="str">
+        <f>VLOOKUP($B113, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="D113" s="11" t="str">
+        <f>VLOOKUP($B113, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="F113" s="20">
+        <f t="shared" si="16"/>
+        <v>97000000000112</v>
+      </c>
+      <c r="K113" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M113" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000112</v>
+      </c>
+      <c r="O113" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000112, '', '', 'ReportTaxReconSummary');</v>
+      </c>
+      <c r="Q113" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000112'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportTaxReconSummary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B114" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000113</v>
+      </c>
+      <c r="C114" s="3" t="str">
+        <f>VLOOKUP($B114, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="D114" s="3" t="str">
+        <f>VLOOKUP($B114, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Customer</v>
+      </c>
+      <c r="F114" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000113</v>
+      </c>
+      <c r="K114" s="18"/>
+      <c r="M114" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000113</v>
+      </c>
+      <c r="O114" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000113, '', '', null);</v>
+      </c>
+      <c r="Q114" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000113'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', null::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B115" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000114</v>
+      </c>
+      <c r="C115" s="3" t="str">
+        <f>VLOOKUP($B115, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+      </c>
+      <c r="D115" s="3" t="str">
+        <f>VLOOKUP($B115, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Customer Order</v>
+      </c>
+      <c r="F115" s="17">
+        <f t="shared" si="16"/>
+        <v>97000000000114</v>
+      </c>
+      <c r="K115" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="M115" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000114</v>
+      </c>
+      <c r="O115" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000114, '', '', 'CustomerOrder?var=1');</v>
+      </c>
+      <c r="Q115" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000114'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'CustomerOrder?var=1'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B116" s="7">
+        <f t="shared" si="11"/>
+        <v>97000000000115</v>
+      </c>
+      <c r="C116" s="3" t="str">
+        <f>VLOOKUP($B116, [1]Main!$E$2:$G$1121, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+      </c>
+      <c r="D116" s="3" t="str">
+        <f>VLOOKUP($B116, [1]Main!$E$2:$G$1121, 3, FALSE)</f>
+        <v>Customer Order Summary</v>
+      </c>
+      <c r="F116" s="17">
+        <f t="shared" ref="F116" si="18">IF(EXACT(B116, ""), F115, B116)</f>
+        <v>97000000000115</v>
+      </c>
+      <c r="K116" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="M116" s="6">
+        <f t="shared" si="17"/>
+        <v>256000000000115</v>
+      </c>
+      <c r="O116" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000115, '', '', 'ReportCustomerOrderSummary');</v>
+      </c>
+      <c r="Q116" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000115'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportCustomerOrderSummary'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuAction.xlsx
@@ -2030,9 +2030,9 @@
     <col min="5" max="5" width="2.140625" style="16" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="40.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -2363,15 +2363,15 @@
         <v>97000000000007</v>
       </c>
       <c r="H8" s="14"/>
-      <c r="I8" s="3" t="str">
+      <c r="I8" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J8" s="3" t="str">
+      <c r="J8" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="19"/>
       <c r="M8" s="6">
         <f t="shared" si="6"/>
         <v>256000000000007</v>
@@ -2730,12 +2730,12 @@
         <f t="shared" si="0"/>
         <v>97000000000016</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="3" t="str">
+      <c r="H17" s="14"/>
+      <c r="I17" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J17" s="3" t="str">
+      <c r="J17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Execute</v>
       </c>
@@ -3191,12 +3191,12 @@
         <f t="shared" si="0"/>
         <v>97000000000027</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="3" t="str">
+      <c r="H28" s="14"/>
+      <c r="I28" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J28" s="3" t="str">
+      <c r="J28" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ReportCostFinancialStructure</v>
       </c>
@@ -3691,12 +3691,12 @@
         <f t="shared" si="0"/>
         <v>97000000000039</v>
       </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="3" t="str">
+      <c r="H40" s="14"/>
+      <c r="I40" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J40" s="3" t="str">
+      <c r="J40" s="11" t="str">
         <f t="shared" si="1"/>
         <v>SallaryAllocationSummary</v>
       </c>
@@ -4285,12 +4285,12 @@
         <f t="shared" si="0"/>
         <v>97000000000053</v>
       </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="3" t="str">
+      <c r="H54" s="14"/>
+      <c r="I54" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J54" s="3" t="str">
+      <c r="J54" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ReportStockOpnameSummary</v>
       </c>
@@ -4713,12 +4713,12 @@
         <f t="shared" si="0"/>
         <v>97000000000063</v>
       </c>
-      <c r="H64" s="4"/>
-      <c r="I64" s="3" t="str">
+      <c r="H64" s="14"/>
+      <c r="I64" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Execute</v>
       </c>
-      <c r="J64" s="3" t="str">
+      <c r="J64" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ReportBusinessTripSettlementSummary</v>
       </c>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B67" s="7">
-        <f t="shared" ref="B67:B119" si="11">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
+        <f t="shared" ref="B67:B116" si="11">IF(ISNUMBER(B66), B66+1, 97000000000001)</f>
         <v>97000000000066</v>
       </c>
       <c r="C67" s="3" t="str">
@@ -5112,12 +5112,12 @@
         <v>97000000000072</v>
       </c>
       <c r="G73" s="16"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="3" t="str">
+      <c r="H73" s="14"/>
+      <c r="I73" s="11" t="str">
         <f t="shared" si="8"/>
         <v>Execute</v>
       </c>
-      <c r="J73" s="3" t="str">
+      <c r="J73" s="11" t="str">
         <f t="shared" si="10"/>
         <v>ReportPurchaseOrdertoAccountPayableSummary</v>
       </c>
@@ -6171,8 +6171,19 @@
         <v>Loan</v>
       </c>
       <c r="F99" s="17">
-        <f t="shared" ref="F99:F117" si="16">IF(EXACT(B99, ""), F98, B99)</f>
+        <f t="shared" ref="F99:F115" si="16">IF(EXACT(B99, ""), F98, B99)</f>
         <v>97000000000098</v>
+      </c>
+      <c r="H99" s="4"/>
+      <c r="I99" s="3" t="str">
+        <f t="shared" ref="I99:I112" si="17">IF(EXACT(F99, ""), "", IF(EXACT(H99, ""), "Execute", H99))</f>
+        <v>Execute</v>
+      </c>
+      <c r="J99" s="3" t="str">
+        <f t="shared" ref="J99:J112" si="18">IF(EXACT(F99, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C99)), D99, IF(EXACT(H99, ""), "Execute", H99)), " ", ""), "&amp;", "")
+)</f>
+        <v>Execute</v>
       </c>
       <c r="K99" s="18" t="s">
         <v>32</v>
@@ -6183,11 +6194,11 @@
       </c>
       <c r="O99" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000098, '', '', 'Loan?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000098, 'Execute', 'Execute', 'Loan?var=1');</v>
       </c>
       <c r="Q99" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000098'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Loan?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000098'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Loan?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="100" spans="2:17" x14ac:dyDescent="0.2">
@@ -6207,20 +6218,29 @@
         <f t="shared" si="16"/>
         <v>97000000000099</v>
       </c>
+      <c r="H100" s="4"/>
+      <c r="I100" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J100" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>LoanSummary</v>
+      </c>
       <c r="K100" s="18" t="s">
         <v>33</v>
       </c>
       <c r="M100" s="6">
-        <f t="shared" ref="M100:M116" si="17">IF(ISNUMBER(M99), M99+1, 256000000000001)</f>
+        <f t="shared" ref="M100:M116" si="19">IF(ISNUMBER(M99), M99+1, 256000000000001)</f>
         <v>256000000000099</v>
       </c>
       <c r="O100" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000099, '', '', 'ReportLoanSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000099, 'LoanSummary', 'Execute', 'ReportLoanSummary');</v>
       </c>
       <c r="Q100" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000099'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoanSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000099'::varchar,'key', 'LoanSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="101" spans="2:17" x14ac:dyDescent="0.2">
@@ -6240,20 +6260,29 @@
         <f t="shared" si="16"/>
         <v>97000000000100</v>
       </c>
+      <c r="H101" s="4"/>
+      <c r="I101" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J101" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>LoantoLoanSettlementSummary</v>
+      </c>
       <c r="K101" s="18" t="s">
         <v>36</v>
       </c>
       <c r="M101" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000100</v>
       </c>
       <c r="O101" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000100, '', '', 'ReportLoantoLoanSettlement');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000100, 'LoantoLoanSettlementSummary', 'Execute', 'ReportLoantoLoanSettlement');</v>
       </c>
       <c r="Q101" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000100'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoantoLoanSettlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000100'::varchar,'key', 'LoantoLoanSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoantoLoanSettlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="102" spans="2:17" x14ac:dyDescent="0.2">
@@ -6273,20 +6302,29 @@
         <f t="shared" si="16"/>
         <v>97000000000101</v>
       </c>
+      <c r="H102" s="4"/>
+      <c r="I102" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J102" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>Execute</v>
+      </c>
       <c r="K102" s="18" t="s">
         <v>34</v>
       </c>
       <c r="M102" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000101</v>
       </c>
       <c r="O102" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000101, '', '', 'LoanSettlement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000101, 'Execute', 'Execute', 'LoanSettlement?var=1');</v>
       </c>
       <c r="Q102" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000101'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'LoanSettlement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000101'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'LoanSettlement?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="103" spans="2:17" x14ac:dyDescent="0.2">
@@ -6306,20 +6344,29 @@
         <f t="shared" si="16"/>
         <v>97000000000102</v>
       </c>
+      <c r="H103" s="4"/>
+      <c r="I103" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J103" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>LoanSettlementSummary</v>
+      </c>
       <c r="K103" s="18" t="s">
         <v>35</v>
       </c>
       <c r="M103" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000102</v>
       </c>
       <c r="O103" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000102, '', '', 'ReportLoanSettlementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000102, 'LoanSettlementSummary', 'Execute', 'ReportLoanSettlementSummary');</v>
       </c>
       <c r="Q103" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000102'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportLoanSettlementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000102'::varchar,'key', 'LoanSettlementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportLoanSettlementSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="104" spans="2:17" x14ac:dyDescent="0.2">
@@ -6339,20 +6386,29 @@
         <f t="shared" si="16"/>
         <v>97000000000103</v>
       </c>
+      <c r="H104" s="4"/>
+      <c r="I104" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J104" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>Execute</v>
+      </c>
       <c r="K104" s="18" t="s">
         <v>39</v>
       </c>
       <c r="M104" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000103</v>
       </c>
       <c r="O104" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000103, '', '', 'AccountPayable?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000103, 'Execute', 'Execute', 'AccountPayable?var=1');</v>
       </c>
       <c r="Q104" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000103'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'AccountPayable?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000103'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'AccountPayable?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="105" spans="2:17" x14ac:dyDescent="0.2">
@@ -6372,20 +6428,29 @@
         <f t="shared" si="16"/>
         <v>97000000000104</v>
       </c>
+      <c r="H105" s="4"/>
+      <c r="I105" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J105" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>AccountPayableSummary</v>
+      </c>
       <c r="K105" s="18" t="s">
         <v>40</v>
       </c>
       <c r="M105" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000104</v>
       </c>
       <c r="O105" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000104, '', '', 'ReportAccountPayableSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000104, 'AccountPayableSummary', 'Execute', 'ReportAccountPayableSummary');</v>
       </c>
       <c r="Q105" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000104'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportAccountPayableSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000104'::varchar,'key', 'AccountPayableSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportAccountPayableSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="106" spans="2:17" x14ac:dyDescent="0.2">
@@ -6405,20 +6470,29 @@
         <f t="shared" si="16"/>
         <v>97000000000105</v>
       </c>
+      <c r="H106" s="4"/>
+      <c r="I106" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J106" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>Execute</v>
+      </c>
       <c r="K106" s="18" t="s">
         <v>26</v>
       </c>
       <c r="M106" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000105</v>
       </c>
       <c r="O106" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000105, '', '', 'Reimbursement?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000105, 'Execute', 'Execute', 'Reimbursement?var=1');</v>
       </c>
       <c r="Q106" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000105'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Reimbursement?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000105'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Reimbursement?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="107" spans="2:17" x14ac:dyDescent="0.2">
@@ -6438,20 +6512,29 @@
         <f t="shared" si="16"/>
         <v>97000000000106</v>
       </c>
+      <c r="H107" s="4"/>
+      <c r="I107" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J107" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>ReimbursementSummary</v>
+      </c>
       <c r="K107" s="18" t="s">
         <v>27</v>
       </c>
       <c r="M107" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000106</v>
       </c>
       <c r="O107" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000106, '', '', 'ReportReimbursementSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000106, 'ReimbursementSummary', 'Execute', 'ReportReimbursementSummary');</v>
       </c>
       <c r="Q107" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000106'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportReimbursementSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000106'::varchar,'key', 'ReimbursementSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportReimbursementSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="108" spans="2:17" x14ac:dyDescent="0.2">
@@ -6471,20 +6554,29 @@
         <f t="shared" si="16"/>
         <v>97000000000107</v>
       </c>
+      <c r="H108" s="4"/>
+      <c r="I108" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J108" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>ReimbursementtoDebitNoteSummary</v>
+      </c>
       <c r="K108" s="18" t="s">
         <v>29</v>
       </c>
       <c r="M108" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000107</v>
       </c>
       <c r="O108" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000107, '', '', 'ReportRemToDN');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000107, 'ReimbursementtoDebitNoteSummary', 'Execute', 'ReportRemToDN');</v>
       </c>
       <c r="Q108" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000107'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportRemToDN'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000107'::varchar,'key', 'ReimbursementtoDebitNoteSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportRemToDN'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.2">
@@ -6504,20 +6596,29 @@
         <f t="shared" si="16"/>
         <v>97000000000108</v>
       </c>
+      <c r="H109" s="4"/>
+      <c r="I109" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J109" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>Execute</v>
+      </c>
       <c r="K109" s="18" t="s">
         <v>58</v>
       </c>
       <c r="M109" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000108</v>
       </c>
       <c r="O109" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000108, '', '', 'Invoice?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000108, 'Execute', 'Execute', 'Invoice?var=1');</v>
       </c>
       <c r="Q109" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000108'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'Invoice?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000108'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'Invoice?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="110" spans="2:17" x14ac:dyDescent="0.2">
@@ -6537,20 +6638,29 @@
         <f t="shared" si="16"/>
         <v>97000000000109</v>
       </c>
+      <c r="H110" s="4"/>
+      <c r="I110" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J110" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>SalesInvoiceSummary</v>
+      </c>
       <c r="K110" s="18" t="s">
         <v>46</v>
       </c>
       <c r="M110" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000109</v>
       </c>
       <c r="O110" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000109, '', '', 'ReportInvoiceSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000109, 'SalesInvoiceSummary', 'Execute', 'ReportInvoiceSummary');</v>
       </c>
       <c r="Q110" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000109'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportInvoiceSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000109'::varchar,'key', 'SalesInvoiceSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportInvoiceSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="111" spans="2:17" x14ac:dyDescent="0.2">
@@ -6570,18 +6680,27 @@
         <f t="shared" si="16"/>
         <v>97000000000110</v>
       </c>
+      <c r="H111" s="4"/>
+      <c r="I111" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J111" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>SalesInvoicetoCreditNote</v>
+      </c>
       <c r="K111" s="18"/>
       <c r="M111" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000110</v>
       </c>
       <c r="O111" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000110, '', '', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000110, 'SalesInvoicetoCreditNote', 'Execute', null);</v>
       </c>
       <c r="Q111" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000110'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000110'::varchar,'key', 'SalesInvoicetoCreditNote'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="112" spans="2:17" x14ac:dyDescent="0.2">
@@ -6601,20 +6720,29 @@
         <f t="shared" si="16"/>
         <v>97000000000111</v>
       </c>
+      <c r="H112" s="4"/>
+      <c r="I112" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v>Execute</v>
+      </c>
+      <c r="J112" s="3" t="str">
+        <f t="shared" si="18"/>
+        <v>Execute</v>
+      </c>
       <c r="K112" s="18" t="s">
         <v>59</v>
       </c>
       <c r="M112" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000111</v>
       </c>
       <c r="O112" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000111, '', '', 'TaxRecon?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000111, 'Execute', 'Execute', 'TaxRecon?var=1');</v>
       </c>
       <c r="Q112" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000111'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'TaxRecon?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000111'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'TaxRecon?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="113" spans="2:17" x14ac:dyDescent="0.2">
@@ -6634,20 +6762,31 @@
         <f t="shared" si="16"/>
         <v>97000000000112</v>
       </c>
+      <c r="H113" s="14"/>
+      <c r="I113" s="11" t="str">
+        <f t="shared" ref="I113:I116" si="20">IF(EXACT(F113, ""), "", IF(EXACT(H113, ""), "Execute", H113))</f>
+        <v>Execute</v>
+      </c>
+      <c r="J113" s="11" t="str">
+        <f t="shared" ref="J113:J116" si="21">IF(EXACT(F113, ""), "",
+SUBSTITUTE(SUBSTITUTE(IF(ISNUMBER(SEARCH(".Report.", C113)), D113, IF(EXACT(H113, ""), "Execute", H113)), " ", ""), "&amp;", "")
+)</f>
+        <v>TaxReconciliationSummary</v>
+      </c>
       <c r="K113" s="19" t="s">
         <v>47</v>
       </c>
       <c r="M113" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000112</v>
       </c>
       <c r="O113" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000112, '', '', 'ReportTaxReconSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000112, 'TaxReconciliationSummary', 'Execute', 'ReportTaxReconSummary');</v>
       </c>
       <c r="Q113" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000112'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportTaxReconSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000112'::varchar,'key', 'TaxReconciliationSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportTaxReconSummary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="114" spans="2:17" x14ac:dyDescent="0.2">
@@ -6667,18 +6806,27 @@
         <f t="shared" si="16"/>
         <v>97000000000113</v>
       </c>
+      <c r="H114" s="4"/>
+      <c r="I114" s="3" t="str">
+        <f t="shared" si="20"/>
+        <v>Execute</v>
+      </c>
+      <c r="J114" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>Execute</v>
+      </c>
       <c r="K114" s="18"/>
       <c r="M114" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000113</v>
       </c>
       <c r="O114" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000113, '', '', null);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000113, 'Execute', 'Execute', null);</v>
       </c>
       <c r="Q114" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000113'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', null::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000113'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', null::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="115" spans="2:17" x14ac:dyDescent="0.2">
@@ -6698,20 +6846,29 @@
         <f t="shared" si="16"/>
         <v>97000000000114</v>
       </c>
+      <c r="H115" s="4"/>
+      <c r="I115" s="3" t="str">
+        <f t="shared" si="20"/>
+        <v>Execute</v>
+      </c>
+      <c r="J115" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>Execute</v>
+      </c>
       <c r="K115" s="18" t="s">
         <v>72</v>
       </c>
       <c r="M115" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000114</v>
       </c>
       <c r="O115" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000114, '', '', 'CustomerOrder?var=1');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000114, 'Execute', 'Execute', 'CustomerOrder?var=1');</v>
       </c>
       <c r="Q115" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000114'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'CustomerOrder?var=1'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000114'::varchar,'key', 'Execute'::varchar,'caption', 'Execute'::varchar,'URLPath', 'CustomerOrder?var=1'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="116" spans="2:17" x14ac:dyDescent="0.2">
@@ -6728,23 +6885,32 @@
         <v>Customer Order Summary</v>
       </c>
       <c r="F116" s="17">
-        <f t="shared" ref="F116" si="18">IF(EXACT(B116, ""), F115, B116)</f>
+        <f t="shared" ref="F116" si="22">IF(EXACT(B116, ""), F115, B116)</f>
         <v>97000000000115</v>
+      </c>
+      <c r="H116" s="4"/>
+      <c r="I116" s="3" t="str">
+        <f t="shared" si="20"/>
+        <v>Execute</v>
+      </c>
+      <c r="J116" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>CustomerOrderSummary</v>
       </c>
       <c r="K116" s="18" t="s">
         <v>73</v>
       </c>
       <c r="M116" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>256000000000115</v>
       </c>
       <c r="O116" s="15" t="str">
         <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000115, '', '', 'ReportCustomerOrderSummary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuAction_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 97000000000115, 'CustomerOrderSummary', 'Execute', 'ReportCustomerOrderSummary');</v>
       </c>
       <c r="Q116" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000115'::varchar,'key', null::varchar,'caption', null::varchar,'URLPath', 'ReportCustomerOrderSummary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menu_RefID', '97000000000115'::varchar,'key', 'CustomerOrderSummary'::varchar,'caption', 'Execute'::varchar,'URLPath', 'ReportCustomerOrderSummary'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>
